--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5858" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{019F996B-6189-45D3-B90B-88FFFE9365F3}"/>
+  <xr:revisionPtr revIDLastSave="6002" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC938903-DE49-4841-B95D-86F9E4603AA7}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="292">
   <si>
     <t>Scholl</t>
   </si>
@@ -905,6 +905,48 @@
   <si>
     <t>Markovic</t>
   </si>
+  <si>
+    <t>Kirnbauer</t>
+  </si>
+  <si>
+    <t>Köstenbauer</t>
+  </si>
+  <si>
+    <t>Schwaighofer</t>
+  </si>
+  <si>
+    <t>Frauscher</t>
+  </si>
+  <si>
+    <t>Martinetz</t>
+  </si>
+  <si>
+    <t>Zetic</t>
+  </si>
+  <si>
+    <t>Sammer</t>
+  </si>
+  <si>
+    <t>Traun</t>
+  </si>
+  <si>
+    <t>Diakite</t>
+  </si>
+  <si>
+    <t>Krapf</t>
+  </si>
+  <si>
+    <t>Vorsager</t>
+  </si>
+  <si>
+    <t>Djezic</t>
+  </si>
+  <si>
+    <t>Ekereokosu</t>
+  </si>
+  <si>
+    <t>Zangerl</t>
+  </si>
 </sst>
 </file>
 
@@ -1171,6 +1213,9 @@
                 <c:pt idx="14">
                   <c:v>18.545454545454547</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1277,6 +1322,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1284,7 +1330,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -1435,13 +1480,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>19.636363636363637</c:v>
@@ -1450,33 +1495,36 @@
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>19.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
@@ -1587,6 +1635,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1594,7 +1643,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1733,52 +1781,52 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>18.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>18.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.181818181818183</c:v>
+                <c:pt idx="10">
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>18.545454545454547</c:v>
+                <c:pt idx="11">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19</c:v>
+                <c:pt idx="12">
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>18.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>18.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>18.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1887,6 +1935,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1894,7 +1943,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2033,55 +2081,61 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2191,6 +2245,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2198,7 +2253,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2337,49 +2391,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.90909090909091</c:v>
+                <c:pt idx="5">
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="9">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2488,6 +2542,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2495,7 +2550,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2644,55 +2698,58 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
+                <c:pt idx="36">
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="39">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="42">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="45">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="48">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>19.09090909090909</c:v>
+                <c:pt idx="51">
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2802,6 +2859,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2809,7 +2867,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2948,55 +3005,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0" formatCode="0.00">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>18.727272727272727</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
-                </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3106,6 +3166,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3113,7 +3174,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3250,55 +3310,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="62"/>
                 <c:pt idx="0" formatCode="0.00">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.00">
+                <c:pt idx="15" formatCode="0.00">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0.00">
-                  <c:v>20</c:v>
+                <c:pt idx="18" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.181818181818183</c:v>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.818181818181817</c:v>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="18" formatCode="0.00">
+                <c:pt idx="30" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3408,6 +3468,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3415,7 +3476,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3565,52 +3625,52 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
+                  <c:v>18.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>18.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.181818181818183</c:v>
+                <c:pt idx="10">
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>18.545454545454547</c:v>
+                <c:pt idx="11">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19</c:v>
+                <c:pt idx="12">
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>18.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="13">
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>18.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>18.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3718,6 +3778,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3725,7 +3786,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -3886,55 +3946,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0" formatCode="0.00">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>18.727272727272727</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
-                </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>19</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4042,6 +4105,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4049,7 +4113,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4210,55 +4273,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="65"/>
                 <c:pt idx="0" formatCode="0.00">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.00">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.00">
+                <c:pt idx="15" formatCode="0.00">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0.00">
-                  <c:v>20</c:v>
+                <c:pt idx="18" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.181818181818183</c:v>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.818181818181817</c:v>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="18" formatCode="0.00">
+                <c:pt idx="30" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4366,6 +4429,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4373,7 +4437,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4534,13 +4597,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>19.636363636363637</c:v>
@@ -4549,33 +4612,36 @@
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>19.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
@@ -4685,6 +4751,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4692,7 +4759,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -4875,55 +4941,61 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5031,6 +5103,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5038,7 +5111,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -5199,49 +5271,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.90909090909091</c:v>
+                <c:pt idx="5">
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="9">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5349,6 +5421,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5356,7 +5429,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -5527,55 +5599,58 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>20</c:v>
+                <c:pt idx="36">
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="39">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="42">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>19.90909090909091</c:v>
+                <c:pt idx="45">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="48">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>19.09090909090909</c:v>
+                <c:pt idx="51">
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5684,6 +5759,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="span"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5691,7 +5767,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:gradFill flip="none" rotWithShape="1">
@@ -5958,6 +6033,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5965,7 +6041,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15779,25 +15854,25 @@
       </c>
       <c r="B2" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>18.855614973262028</v>
+        <v>19.373737373737374</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3">
+        <f ca="1">JWR!N1</f>
+        <v>19.414772727272727</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B4" s="5">
         <f ca="1">'Altach Juniors'!N1</f>
-        <v>18.988636363636363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3">
-        <f ca="1">JWR!N1</f>
-        <v>19.406060606060603</v>
+        <v>19.47159090909091</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15806,7 +15881,7 @@
       </c>
       <c r="B5" s="5">
         <f ca="1">Rapid!N1</f>
-        <v>19.534759358288767</v>
+        <v>19.646464646464644</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15815,7 +15890,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.06666666666667</v>
+        <v>20.170454545454543</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15824,25 +15899,25 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.393939393939391</v>
+        <v>20.672727272727276</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">Sturm!N1</f>
-        <v>20.449197860962563</v>
+        <f ca="1">'Young Violets'!N1</f>
+        <v>20.684210526315791</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5">
-        <f ca="1">'Young Violets'!N1</f>
-        <v>20.502673796791445</v>
+        <f ca="1">Sturm!N1</f>
+        <v>20.689839572192511</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -15879,7 +15954,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.449197860962563</v>
+        <v>20.689839572192511</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -15944,15 +16019,15 @@
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
@@ -15968,7 +16043,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -16033,19 +16108,19 @@
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="1"/>
@@ -16057,7 +16132,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.09090909090909</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -16122,15 +16197,15 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
@@ -16146,7 +16221,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -16211,7 +16286,7 @@
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
@@ -16219,7 +16294,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
@@ -16235,7 +16310,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -16300,7 +16375,7 @@
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
@@ -16308,7 +16383,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
@@ -16324,7 +16399,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -16397,7 +16472,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
@@ -16405,7 +16480,7 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
@@ -16413,7 +16488,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P18" t="s">
         <v>67</v>
@@ -16493,7 +16568,7 @@
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
@@ -16517,7 +16592,7 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
@@ -16525,7 +16600,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P21" t="s">
         <v>57</v>
@@ -16602,7 +16677,7 @@
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
@@ -16618,7 +16693,7 @@
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="7"/>
@@ -16626,7 +16701,7 @@
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
@@ -16634,7 +16709,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P24" t="s">
         <v>76</v>
@@ -16711,7 +16786,7 @@
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="8"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
@@ -16735,7 +16810,7 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
@@ -16743,7 +16818,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>21.363636363636363</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="P27" t="s">
         <v>70</v>
@@ -16820,7 +16895,7 @@
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
@@ -16828,7 +16903,7 @@
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
@@ -16836,7 +16911,7 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="9"/>
@@ -16844,7 +16919,7 @@
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="9"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="9"/>
@@ -16852,7 +16927,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.454545454545453</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P30" t="s">
         <v>119</v>
@@ -16937,7 +17012,7 @@
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
@@ -16945,7 +17020,7 @@
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="10"/>
@@ -16953,7 +17028,7 @@
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="10"/>
@@ -16961,7 +17036,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P33" t="s">
         <v>149</v>
@@ -17046,7 +17121,7 @@
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
@@ -17054,7 +17129,7 @@
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="11"/>
@@ -17062,7 +17137,7 @@
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="11"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
@@ -17070,7 +17145,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P36" t="s">
         <v>184</v>
@@ -17135,7 +17210,7 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
         <f ca="1">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17163,7 +17238,7 @@
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
@@ -17171,7 +17246,7 @@
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="12"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
@@ -17179,7 +17254,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>20.818181818181817</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P39" t="s">
         <v>201</v>
@@ -17244,7 +17319,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
         <f ca="1">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17268,7 +17343,7 @@
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="13"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="13"/>
@@ -17280,7 +17355,7 @@
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
@@ -17288,7 +17363,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21.363636363636363</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="P42" t="s">
         <v>256</v>
@@ -17353,7 +17428,7 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
         <f ca="1">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17397,7 +17472,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -17442,7 +17517,7 @@
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
         <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17462,11 +17537,11 @@
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I48">
         <f t="shared" ca="1" si="15"/>
@@ -17486,7 +17561,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -17531,7 +17606,7 @@
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17551,7 +17626,7 @@
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
@@ -17575,7 +17650,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -17780,7 +17855,7 @@
       </c>
       <c r="Q2" s="8" cm="1">
         <f t="array" aca="1" ref="Q2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="R2" s="8" cm="1">
         <f t="array" aca="1" ref="R2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -17809,15 +17884,15 @@
       </c>
       <c r="B3" s="8" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="C3" s="8" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="D3" s="8" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="E3" s="8" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -17829,47 +17904,47 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="H3" s="8" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="J3" s="8" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="K3" s="8" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="L3" s="8" cm="1">
         <f t="array" aca="1" ref="L3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="M3" s="8" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -17898,67 +17973,67 @@
       </c>
       <c r="B4" s="5" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="C4" s="5" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="H4" s="5" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="I4" s="5" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="J4" s="5" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.727272727272727</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="K4" s="5" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.272727272727273</v>
+        <v>18.545454545454547</v>
       </c>
       <c r="L4" s="5" cm="1">
         <f t="array" aca="1" ref="L4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="M4" s="5" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="N4" s="5" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.727272727272727</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="O4" s="5" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.363636363636363</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="P4" s="5" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="Q4" s="5" cm="1">
         <f t="array" aca="1" ref="Q4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="R4" s="5" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -17987,39 +18062,39 @@
       </c>
       <c r="B5" s="5" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="C5" s="5" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="D5" s="5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="E5" s="5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="F5" s="5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="G5" s="5" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="H5" s="5" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="I5" s="5" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="K5" s="5" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18027,7 +18102,7 @@
       </c>
       <c r="L5" s="5" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="M5" s="5" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18035,31 +18110,31 @@
       </c>
       <c r="N5" s="5" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>21</v>
       </c>
       <c r="O5" s="5" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P5" s="5" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="Q5" s="5" cm="1">
         <f t="array" aca="1" ref="Q5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="R5" s="5" cm="1">
         <f t="array" aca="1" ref="R5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="S5" s="5" cm="1">
         <f t="array" aca="1" ref="S5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="T5" s="5" cm="1">
         <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18076,63 +18151,63 @@
       </c>
       <c r="B6" s="5" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="F6" s="5" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="G6" s="5" cm="1">
         <f t="array" aca="1" ref="G6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="H6" s="5" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="I6" s="5" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="J6" s="5" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="K6" s="5" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="L6" s="5" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="M6" s="5" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="N6" s="5" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="O6" s="5" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P6" s="5" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="Q6" s="5" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18165,75 +18240,75 @@
       </c>
       <c r="B7" s="5" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="C7" s="5" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="D7" s="5" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="E7" s="5" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="F7" s="5" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="I7" s="5" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="K7" s="5" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="L7" s="5" cm="1">
         <f t="array" aca="1" ref="L7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="M7" s="5" cm="1">
         <f t="array" aca="1" ref="M7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="N7" s="5" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="O7" s="5" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P7" s="5" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="Q7" s="5" cm="1">
         <f t="array" aca="1" ref="Q7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="R7" s="5" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="S7" s="5" cm="1">
         <f t="array" aca="1" ref="S7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="T7" s="5" cm="1">
         <f t="array" aca="1" ref="T7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18254,75 +18329,75 @@
       </c>
       <c r="B8" s="5" cm="1">
         <f t="array" aca="1" ref="B8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.636363636363637</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="C8" s="5" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="D8" s="5" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="E8" s="5" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="F8" s="5" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.727272727272727</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="G8" s="5" cm="1">
         <f t="array" aca="1" ref="G8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.636363636363637</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="K8" s="5" cm="1">
         <f t="array" aca="1" ref="K8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="L8" s="5" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="M8" s="5" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="N8" s="5" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="O8" s="5" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="P8" s="5" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="R8" s="5" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18343,71 +18418,71 @@
       </c>
       <c r="B9" s="5" cm="1">
         <f t="array" aca="1" ref="B9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="C9" s="5" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="D9" s="5" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="E9" s="5" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="F9" s="5" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
       <c r="G9" s="5" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="H9" s="5" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="I9" s="5" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="J9" s="5" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.363636363636363</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="K9" s="5" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="L9" s="5" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="M9" s="5" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="N9" s="5" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="O9" s="5" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.363636363636363</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="P9" s="5" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="Q9" s="5" cm="1">
         <f t="array" aca="1" ref="Q9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="R9" s="5" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="S9" s="5" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19046,6 +19121,7 @@
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5546875" style="1"/>
   </cols>
@@ -19053,7 +19129,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.406060606060603</v>
+        <v>19.414772727272727</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -20508,6 +20584,12 @@
       <c r="L44" t="s">
         <v>219</v>
       </c>
+      <c r="P44" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>37496</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
@@ -20558,23 +20640,150 @@
         <f ca="1">AVERAGE(B45:M45)</f>
         <v>18.545454545454547</v>
       </c>
+      <c r="P45" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>37129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>37139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>279</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
+        <v>191</v>
+      </c>
+      <c r="I47" t="s">
+        <v>261</v>
+      </c>
+      <c r="J47" t="s">
+        <v>83</v>
+      </c>
+      <c r="K47" t="s">
+        <v>166</v>
+      </c>
+      <c r="L47" t="s">
+        <v>280</v>
+      </c>
+      <c r="P47" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>39613</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N48" s="1"/>
-    </row>
-    <row r="51" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C48">
+        <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ca="1" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="E48">
+        <f t="shared" ca="1" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <f t="shared" ca="1" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="G48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="H48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="I48">
+        <f t="shared" ca="1" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="J48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="K48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="L48">
+        <f t="shared" ca="1" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="N48" s="1">
+        <f ca="1">AVERAGE(B48:M48)</f>
+        <v>19.545454545454547</v>
+      </c>
+      <c r="P48" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>39468</v>
+      </c>
+    </row>
+    <row r="49" spans="14:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>38486</v>
+      </c>
+    </row>
+    <row r="50" spans="14:17" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>38422</v>
+      </c>
+    </row>
+    <row r="51" spans="14:17" x14ac:dyDescent="0.3">
       <c r="N51" s="1"/>
     </row>
-    <row r="54" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="14:17" x14ac:dyDescent="0.3">
       <c r="N54" s="1"/>
     </row>
-    <row r="57" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="14:17" x14ac:dyDescent="0.3">
       <c r="N57" s="1"/>
     </row>
-    <row r="60" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="14:17" x14ac:dyDescent="0.3">
       <c r="N60" s="1"/>
     </row>
-    <row r="63" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="14:17" x14ac:dyDescent="0.3">
       <c r="N63" s="1"/>
     </row>
     <row r="66" spans="14:14" x14ac:dyDescent="0.3">
@@ -20601,7 +20810,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -20614,7 +20823,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.06666666666667</v>
+        <v>20.170454545454543</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -20674,11 +20883,11 @@
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
@@ -20702,7 +20911,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -20766,7 +20975,7 @@
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -20786,11 +20995,11 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -20854,7 +21063,7 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
@@ -20878,7 +21087,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -21114,7 +21323,7 @@
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
@@ -21142,7 +21351,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -21219,7 +21428,7 @@
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
@@ -21247,7 +21456,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -21327,7 +21536,7 @@
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="7"/>
@@ -21355,7 +21564,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P24" t="s">
         <v>87</v>
@@ -21435,7 +21644,7 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
@@ -21463,7 +21672,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P27" t="s">
         <v>35</v>
@@ -21543,7 +21752,7 @@
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
@@ -21571,7 +21780,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P30" t="s">
         <v>105</v>
@@ -21651,7 +21860,7 @@
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
@@ -21679,7 +21888,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P33" t="s">
         <v>152</v>
@@ -21759,7 +21968,7 @@
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
@@ -21775,7 +21984,7 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="11"/>
@@ -21787,7 +21996,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P36" t="s">
         <v>169</v>
@@ -21867,7 +22076,7 @@
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
@@ -21879,7 +22088,7 @@
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
@@ -21895,7 +22104,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P39" t="s">
         <v>252</v>
@@ -21963,7 +22172,7 @@
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
@@ -21975,7 +22184,7 @@
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
@@ -21987,7 +22196,7 @@
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
@@ -22003,13 +22212,21 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.818181818181817</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P42" t="s">
         <v>265</v>
       </c>
       <c r="Q42" s="6">
         <v>38062</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P43" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>39118</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -22049,6 +22266,12 @@
       <c r="L44" t="s">
         <v>37</v>
       </c>
+      <c r="P44" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>39260</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
@@ -22057,7 +22280,7 @@
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
@@ -22069,7 +22292,7 @@
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
@@ -22097,6 +22320,100 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
+        <v>20.09090909090909</v>
+      </c>
+      <c r="P45" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>39689</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" t="s">
+        <v>200</v>
+      </c>
+      <c r="E47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" t="s">
+        <v>285</v>
+      </c>
+      <c r="H47" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" t="s">
+        <v>286</v>
+      </c>
+      <c r="J47" t="s">
+        <v>6</v>
+      </c>
+      <c r="K47" t="s">
+        <v>287</v>
+      </c>
+      <c r="L47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C48">
+        <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="E48">
+        <f t="shared" ca="1" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <f t="shared" ca="1" si="15"/>
+        <v>24</v>
+      </c>
+      <c r="G48">
+        <f t="shared" ca="1" si="15"/>
+        <v>19</v>
+      </c>
+      <c r="H48">
+        <f t="shared" ca="1" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="I48">
+        <f t="shared" ca="1" si="15"/>
+        <v>18</v>
+      </c>
+      <c r="J48">
+        <f t="shared" ca="1" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="K48">
+        <f t="shared" ca="1" si="15"/>
+        <v>17</v>
+      </c>
+      <c r="L48">
+        <f t="shared" ca="1" si="15"/>
+        <v>20</v>
+      </c>
+      <c r="N48" s="1">
+        <f ca="1">AVERAGE(B48:M48)</f>
         <v>19.90909090909091</v>
       </c>
     </row>
@@ -22122,7 +22439,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>18.988636363636363</v>
+        <v>19.47159090909091</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -22174,7 +22491,7 @@
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
@@ -22182,11 +22499,11 @@
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
@@ -22206,11 +22523,11 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>18.545454545454547</v>
+        <v>18.90909090909091</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -22262,7 +22579,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
@@ -22270,11 +22587,11 @@
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -22294,11 +22611,11 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>19.181818181818183</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -22350,7 +22667,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
@@ -22358,11 +22675,11 @@
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
@@ -22374,7 +22691,7 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -22382,11 +22699,11 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>18.545454545454547</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -22438,7 +22755,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
@@ -22446,11 +22763,11 @@
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
@@ -22462,7 +22779,7 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
@@ -22474,7 +22791,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -22518,7 +22835,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <f ca="1">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22526,7 +22843,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="4"/>
@@ -22534,11 +22851,11 @@
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
@@ -22550,7 +22867,7 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="4"/>
@@ -22558,11 +22875,11 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -22606,7 +22923,7 @@
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
         <f ca="1">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22614,7 +22931,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="5"/>
@@ -22622,15 +22939,15 @@
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
@@ -22638,7 +22955,7 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
@@ -22646,11 +22963,11 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>18.818181818181817</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P18" t="s">
         <v>19</v>
@@ -22717,7 +23034,7 @@
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
         <f ca="1">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22725,7 +23042,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
@@ -22733,7 +23050,7 @@
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
@@ -22741,7 +23058,7 @@
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
@@ -22749,7 +23066,7 @@
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
@@ -22761,7 +23078,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.818181818181817</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P21" t="s">
         <v>90</v>
@@ -22825,7 +23142,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
         <f ca="1">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22841,7 +23158,7 @@
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="7"/>
@@ -22849,7 +23166,7 @@
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
@@ -22857,7 +23174,7 @@
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
@@ -22865,11 +23182,11 @@
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>18.90909090909091</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P24" t="s">
         <v>91</v>
@@ -22933,7 +23250,7 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
         <f ca="1">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22941,7 +23258,7 @@
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="8"/>
@@ -22949,7 +23266,7 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
@@ -22957,7 +23274,7 @@
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
@@ -22965,7 +23282,7 @@
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
@@ -22973,11 +23290,11 @@
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>18.727272727272727</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P27" t="s">
         <v>30</v>
@@ -23053,11 +23370,11 @@
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
@@ -23069,7 +23386,7 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="9"/>
@@ -23085,7 +23402,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>18.272727272727273</v>
+        <v>18.545454545454547</v>
       </c>
       <c r="P30" t="s">
         <v>121</v>
@@ -23149,7 +23466,7 @@
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
         <f ca="1">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23157,15 +23474,15 @@
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
@@ -23173,11 +23490,11 @@
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="10"/>
@@ -23185,7 +23502,7 @@
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="10"/>
@@ -23193,7 +23510,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.545454545454547</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P33" t="s">
         <v>158</v>
@@ -23257,7 +23574,7 @@
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
         <f ca="1">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23265,7 +23582,7 @@
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="11"/>
@@ -23273,7 +23590,7 @@
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
@@ -23281,7 +23598,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
@@ -23293,7 +23610,7 @@
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="11"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
@@ -23301,7 +23618,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.272727272727273</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P36" t="s">
         <v>189</v>
@@ -23365,15 +23682,15 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
         <f ca="1">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="12"/>
@@ -23381,7 +23698,7 @@
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
@@ -23389,7 +23706,7 @@
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
@@ -23401,15 +23718,15 @@
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="12"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>18.727272727272727</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P39" t="s">
         <v>212</v>
@@ -23473,7 +23790,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
         <f ca="1">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23481,7 +23798,7 @@
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42">
         <f t="shared" ca="1" si="13"/>
@@ -23489,7 +23806,7 @@
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
@@ -23509,15 +23826,15 @@
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>18.363636363636363</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="P42" t="s">
         <v>237</v>
@@ -23581,11 +23898,11 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
         <f ca="1">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
@@ -23597,7 +23914,7 @@
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
@@ -23605,7 +23922,7 @@
       </c>
       <c r="H45">
         <f t="shared" ca="1" si="14"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="14"/>
@@ -23617,15 +23934,15 @@
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.636363636363637</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -23669,11 +23986,11 @@
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
         <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
@@ -23685,7 +24002,7 @@
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
@@ -23693,7 +24010,7 @@
       </c>
       <c r="H48">
         <f t="shared" ca="1" si="15"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I48">
         <f t="shared" ca="1" si="15"/>
@@ -23705,15 +24022,15 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="15"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>19.545454545454547</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
   </sheetData>
@@ -23731,7 +24048,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.502673796791445</v>
+        <v>20.684210526315791</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -23796,7 +24113,7 @@
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
@@ -23804,7 +24121,7 @@
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
@@ -23820,7 +24137,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -23888,7 +24205,7 @@
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -23896,7 +24213,7 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
@@ -23912,7 +24229,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -23988,7 +24305,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
@@ -24004,7 +24321,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -24080,7 +24397,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
@@ -24096,7 +24413,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -24169,7 +24486,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
@@ -24185,7 +24502,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -24258,7 +24575,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
@@ -24274,7 +24591,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P18" t="s">
         <v>94</v>
@@ -24362,7 +24679,7 @@
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
@@ -24386,7 +24703,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P21" t="s">
         <v>38</v>
@@ -24487,7 +24804,7 @@
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
@@ -24495,7 +24812,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P24" t="s">
         <v>32</v>
@@ -24596,15 +24913,15 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P27" t="s">
         <v>22</v>
@@ -24798,7 +25115,7 @@
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
@@ -24822,7 +25139,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P33" t="s">
         <v>179</v>
@@ -25020,11 +25337,11 @@
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
@@ -25040,7 +25357,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>20.818181818181817</v>
+        <v>21</v>
       </c>
       <c r="P39" t="s">
         <v>248</v>
@@ -25109,7 +25426,7 @@
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
@@ -25145,11 +25462,11 @@
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P42" t="s">
         <v>272</v>
@@ -25218,7 +25535,7 @@
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
@@ -25254,11 +25571,25 @@
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
+      </c>
+      <c r="P45" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>38999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>35610</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -25307,7 +25638,7 @@
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
@@ -25323,7 +25654,7 @@
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48">
         <f t="shared" ca="1" si="15"/>
@@ -25347,7 +25678,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>21.09090909090909</v>
+        <v>21.272727272727273</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -25396,7 +25727,7 @@
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
@@ -25412,7 +25743,7 @@
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="16"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
@@ -25436,14 +25767,186 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.545454545454547</v>
-      </c>
+        <v>20.727272727272727</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" t="s">
+        <v>155</v>
+      </c>
+      <c r="I53" t="s">
+        <v>190</v>
+      </c>
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" t="s">
+        <v>277</v>
+      </c>
+      <c r="L53" t="s">
+        <v>288</v>
+      </c>
+      <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N54" s="1"/>
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>17</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>36</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>17</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>28</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>20.90909090909091</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" t="s">
+        <v>231</v>
+      </c>
+      <c r="E56" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" t="s">
+        <v>79</v>
+      </c>
+      <c r="H56" t="s">
+        <v>155</v>
+      </c>
+      <c r="I56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" t="s">
+        <v>271</v>
+      </c>
+      <c r="L56" t="s">
+        <v>288</v>
+      </c>
+      <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N57" s="1"/>
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>36</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>28</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>21.454545454545453</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N60" s="1"/>
@@ -25467,7 +25970,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.393939393939391</v>
+        <v>20.672727272727276</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -25539,11 +26042,11 @@
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
@@ -25551,11 +26054,11 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.727272727272727</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -25627,11 +26130,11 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="1"/>
@@ -25639,11 +26142,11 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.90909090909091</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -25715,11 +26218,11 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -25727,11 +26230,11 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.727272727272727</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -25803,11 +26306,11 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
@@ -25815,11 +26318,11 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="1">
         <f t="shared" ref="N12" ca="1" si="4">AVERAGE(B12:M12)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -25895,7 +26398,7 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="5"/>
@@ -25903,11 +26406,11 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:L15)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -25975,15 +26478,15 @@
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="6"/>
@@ -25991,11 +26494,11 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:L18)</f>
-        <v>19.90909090909091</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P18" t="s">
         <v>9</v>
@@ -26066,7 +26569,7 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="7">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="7"/>
@@ -26094,7 +26597,7 @@
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
@@ -26106,7 +26609,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:L21)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P21" t="s">
         <v>11</v>
@@ -26174,7 +26677,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="8">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="8"/>
@@ -26194,7 +26697,7 @@
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="8"/>
@@ -26202,7 +26705,7 @@
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="8"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="8"/>
@@ -26214,7 +26717,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:L24)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P24" t="s">
         <v>29</v>
@@ -26282,7 +26785,7 @@
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="9">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="9"/>
@@ -26310,11 +26813,11 @@
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="9"/>
@@ -26322,7 +26825,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:L27)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P27" t="s">
         <v>96</v>
@@ -26406,7 +26909,7 @@
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="10"/>
@@ -26418,11 +26921,11 @@
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="10"/>
@@ -26430,7 +26933,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:L30)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P30" t="s">
         <v>171</v>
@@ -26498,7 +27001,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="11">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="11"/>
@@ -26526,11 +27029,11 @@
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="11"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="11"/>
@@ -26538,7 +27041,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:L33)</f>
-        <v>20.454545454545453</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P33" t="s">
         <v>177</v>
@@ -26606,7 +27109,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="12">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="12"/>
@@ -26626,7 +27129,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="12"/>
@@ -26634,11 +27137,11 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="12"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="12"/>
@@ -26646,7 +27149,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:L36)</f>
-        <v>20.09090909090909</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P36" t="s">
         <v>198</v>
@@ -26734,7 +27237,7 @@
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="13"/>
@@ -26742,11 +27245,11 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="13"/>
@@ -26754,7 +27257,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:L39)</f>
-        <v>20.181818181818183</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P39" t="s">
         <v>20</v>
@@ -26822,7 +27325,7 @@
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="14">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="14"/>
@@ -26842,7 +27345,7 @@
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="14"/>
@@ -26854,7 +27357,7 @@
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="14"/>
@@ -26862,7 +27365,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:L42)</f>
-        <v>20.363636363636363</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P42" t="s">
         <v>251</v>
@@ -26930,7 +27433,7 @@
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="15">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="15"/>
@@ -26938,7 +27441,7 @@
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="15"/>
@@ -26958,11 +27461,11 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="15"/>
@@ -26970,7 +27473,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:L45)</f>
-        <v>20.545454545454547</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P45" t="s">
         <v>267</v>
@@ -27001,7 +27504,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.534759358288767</v>
+        <v>19.646464646464644</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27053,7 +27556,7 @@
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
@@ -27061,7 +27564,7 @@
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
@@ -27089,7 +27592,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -27141,7 +27644,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
@@ -27149,7 +27652,7 @@
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
@@ -27177,7 +27680,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -27229,7 +27732,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
@@ -27237,7 +27740,7 @@
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
@@ -27265,7 +27768,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.09090909090909</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -27325,7 +27828,7 @@
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
@@ -27353,7 +27856,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -27413,7 +27916,7 @@
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
@@ -27441,7 +27944,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -27501,7 +28004,7 @@
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
@@ -27529,7 +28032,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="P18" t="s">
         <v>47</v>
@@ -27612,7 +28115,7 @@
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
@@ -27640,7 +28143,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P21" t="s">
         <v>45</v>
@@ -27720,7 +28223,7 @@
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="7"/>
@@ -27748,7 +28251,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P24" t="s">
         <v>44</v>
@@ -27828,7 +28331,7 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
@@ -27836,7 +28339,7 @@
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
@@ -27856,7 +28359,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.636363636363637</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P27" t="s">
         <v>54</v>
@@ -27936,7 +28439,7 @@
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
@@ -27944,7 +28447,7 @@
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
@@ -27964,7 +28467,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P30" t="s">
         <v>162</v>
@@ -28044,7 +28547,7 @@
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
@@ -28052,7 +28555,7 @@
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
@@ -28072,7 +28575,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P33" t="s">
         <v>181</v>
@@ -28140,7 +28643,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -28152,7 +28655,7 @@
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
@@ -28180,7 +28683,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P36" t="s">
         <v>233</v>
@@ -28248,7 +28751,7 @@
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
@@ -28260,7 +28763,7 @@
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
@@ -28288,13 +28791,21 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="P39" t="s">
         <v>276</v>
       </c>
       <c r="Q39" s="6">
         <v>39232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P40" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>38829</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -28334,6 +28845,12 @@
       <c r="L41" t="s">
         <v>45</v>
       </c>
+      <c r="P41" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>39557</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
@@ -28354,7 +28871,7 @@
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
@@ -28362,11 +28879,11 @@
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="13"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
@@ -28382,7 +28899,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.454545454545453</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -28434,7 +28951,7 @@
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
@@ -28442,7 +28959,7 @@
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
@@ -28470,7 +28987,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -28522,7 +29039,7 @@
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
@@ -28530,7 +29047,7 @@
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
@@ -28558,7 +29075,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -28610,7 +29127,7 @@
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E51">
         <f t="shared" ca="1" si="16"/>
@@ -28618,7 +29135,7 @@
       </c>
       <c r="F51">
         <f t="shared" ca="1" si="16"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="16"/>
@@ -28646,7 +29163,95 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.09090909090909</v>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>204</v>
+      </c>
+      <c r="B53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" t="s">
+        <v>181</v>
+      </c>
+      <c r="D53" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" t="s">
+        <v>276</v>
+      </c>
+      <c r="F53" t="s">
+        <v>289</v>
+      </c>
+      <c r="G53" t="s">
+        <v>290</v>
+      </c>
+      <c r="H53" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53" t="s">
+        <v>203</v>
+      </c>
+      <c r="J53" t="s">
+        <v>54</v>
+      </c>
+      <c r="K53" t="s">
+        <v>44</v>
+      </c>
+      <c r="L53" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>17</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>21</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>18.818181818181817</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -28689,7 +29294,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>18.855614973262028</v>
+        <v>19.373737373737374</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -28734,7 +29339,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <f ca="1">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -28742,27 +29347,27 @@
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
@@ -28774,11 +29379,11 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>18.636363636363637</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -28823,7 +29428,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <f ca="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -28831,27 +29436,27 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
@@ -28863,11 +29468,11 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>18.818181818181817</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -28912,7 +29517,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <f ca="1">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -28920,27 +29525,27 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
@@ -28952,11 +29557,11 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>18.90909090909091</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -29009,27 +29614,27 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
@@ -29041,11 +29646,11 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>18.818181818181817</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -29098,27 +29703,27 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
@@ -29126,15 +29731,15 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>18.727272727272727</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -29187,11 +29792,11 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
@@ -29199,15 +29804,15 @@
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
@@ -29219,11 +29824,11 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P18" t="s">
         <v>99</v>
@@ -29295,11 +29900,11 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
@@ -29311,15 +29916,15 @@
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
@@ -29331,11 +29936,11 @@
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P21" t="s">
         <v>62</v>
@@ -29404,11 +30009,11 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="7"/>
@@ -29420,15 +30025,15 @@
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="7"/>
@@ -29440,11 +30045,11 @@
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>18.818181818181817</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P24" t="s">
         <v>100</v>
@@ -29509,35 +30114,35 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
         <f ca="1">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="8"/>
@@ -29549,11 +30154,11 @@
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>18.636363636363637</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P27" t="s">
         <v>61</v>
@@ -29622,15 +30227,15 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
@@ -29638,11 +30243,11 @@
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
@@ -29658,11 +30263,11 @@
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P30" t="s">
         <v>116</v>
@@ -29731,15 +30336,15 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
@@ -29747,11 +30352,11 @@
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
@@ -29771,7 +30376,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>18.818181818181817</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P33" t="s">
         <v>206</v>
@@ -29836,7 +30441,7 @@
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
         <f ca="1">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -29844,11 +30449,11 @@
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
@@ -29860,7 +30465,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
@@ -29880,7 +30485,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P36" t="s">
         <v>213</v>
@@ -29945,7 +30550,7 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
         <f ca="1">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -29953,11 +30558,11 @@
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
@@ -29989,7 +30594,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.181818181818183</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P39" t="s">
         <v>214</v>
@@ -30054,7 +30659,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
         <f ca="1">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -30062,11 +30667,11 @@
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
@@ -30086,7 +30691,7 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
@@ -30098,7 +30703,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>18.818181818181817</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="P42" t="s">
         <v>259</v>
@@ -30163,7 +30768,7 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
         <f ca="1">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -30171,11 +30776,11 @@
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
@@ -30183,7 +30788,7 @@
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45">
         <f t="shared" ca="1" si="14"/>
@@ -30191,7 +30796,7 @@
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
@@ -30207,13 +30812,21 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P45" t="s">
         <v>275</v>
       </c>
       <c r="Q45" s="6">
         <v>39186</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>39198</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -30270,7 +30883,7 @@
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
@@ -30278,15 +30891,15 @@
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="15"/>
@@ -30302,7 +30915,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>19</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -30347,7 +30960,7 @@
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -30359,7 +30972,7 @@
       </c>
       <c r="E51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51">
         <f t="shared" ca="1" si="16"/>
@@ -30367,15 +30980,15 @@
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="16"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="16"/>
@@ -30391,14 +31004,97 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
-        <v>18.818181818181817</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" t="s">
+        <v>64</v>
+      </c>
+      <c r="G53" t="s">
+        <v>291</v>
+      </c>
+      <c r="H53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I53" t="s">
+        <v>274</v>
+      </c>
+      <c r="J53" t="s">
+        <v>147</v>
+      </c>
+      <c r="K53" t="s">
+        <v>217</v>
+      </c>
+      <c r="L53" t="s">
+        <v>205</v>
+      </c>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N54" s="1"/>
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:L54)</f>
+        <v>18.90909090909091</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N56" s="1"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6002" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC938903-DE49-4841-B95D-86F9E4603AA7}"/>
+  <xr:revisionPtr revIDLastSave="6017" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C9ABBA1-4EB3-48FA-A926-0137761A9F8A}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="292">
   <si>
     <t>Scholl</t>
   </si>
@@ -2434,6 +2434,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5315,6 +5318,9 @@
                 <c:pt idx="14">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
+                <c:pt idx="15">
+                  <c:v>21</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -15895,29 +15901,29 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B7" s="5">
-        <f ca="1">WAC!N1</f>
-        <v>20.672727272727276</v>
+        <f ca="1">'Young Violets'!N1</f>
+        <v>20.684210526315791</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">'Young Violets'!N1</f>
-        <v>20.684210526315791</v>
+        <f ca="1">Sturm!N1</f>
+        <v>20.689839572192511</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5">
-        <f ca="1">Sturm!N1</f>
-        <v>20.689839572192511</v>
+        <f ca="1">WAC!N1</f>
+        <v>20.69318181818182</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -18211,7 +18217,7 @@
       </c>
       <c r="Q6" s="5" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R6" s="5" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -25960,7 +25966,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -25970,7 +25976,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.672727272727276</v>
+        <v>20.69318181818182</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27480,6 +27486,94 @@
       </c>
       <c r="Q45" s="6">
         <v>37955</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" t="s">
+        <v>239</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="s">
+        <v>96</v>
+      </c>
+      <c r="J47" t="s">
+        <v>12</v>
+      </c>
+      <c r="K47" t="s">
+        <v>97</v>
+      </c>
+      <c r="L47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C48">
+        <f t="shared" ref="C48:L48" ca="1" si="16">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D48">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="E48">
+        <f t="shared" ca="1" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <f t="shared" ca="1" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="G48">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="H48">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="I48">
+        <f t="shared" ca="1" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="J48">
+        <f t="shared" ca="1" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="K48">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="L48">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="N48" s="1">
+        <f ca="1">AVERAGE(B48:L48)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6017" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C9ABBA1-4EB3-48FA-A926-0137761A9F8A}"/>
+  <xr:revisionPtr revIDLastSave="6027" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0973985A-E72B-46D1-AE73-8F272F0DA5F9}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="293">
   <si>
     <t>Scholl</t>
   </si>
@@ -946,6 +946,9 @@
   </si>
   <si>
     <t>Zangerl</t>
+  </si>
+  <si>
+    <t>Donat</t>
   </si>
 </sst>
 </file>
@@ -3363,6 +3366,9 @@
                 <c:pt idx="48" formatCode="0.00">
                   <c:v>20.454545454545453</c:v>
                 </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4325,6 +4331,9 @@
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
                   <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15901,20 +15910,20 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="5">
+        <f ca="1">Sturm!N1</f>
+        <v>20.68181818181818</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="5">
         <f ca="1">'Young Violets'!N1</f>
         <v>20.684210526315791</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="5">
-        <f ca="1">Sturm!N1</f>
-        <v>20.689839572192511</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -15960,7 +15969,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.689839572192511</v>
+        <v>20.68181818181818</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -17480,6 +17489,12 @@
         <f ca="1">AVERAGE(B45:M45)</f>
         <v>20.545454545454547</v>
       </c>
+      <c r="P45" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>39164</v>
+      </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -17660,10 +17675,93 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>232</v>
+      </c>
+      <c r="B53" t="s">
+        <v>292</v>
+      </c>
+      <c r="C53" t="s">
+        <v>148</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G53" t="s">
+        <v>202</v>
+      </c>
+      <c r="H53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I53" t="s">
+        <v>118</v>
+      </c>
+      <c r="J53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53" t="s">
+        <v>226</v>
+      </c>
+      <c r="L53" t="s">
+        <v>102</v>
+      </c>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N54" s="1"/>
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>23</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>26</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>26</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>20.545454545454547</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N56" s="1"/>
@@ -18492,7 +18590,7 @@
       </c>
       <c r="S9" s="5" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="T9" s="5" cm="1">
         <f t="array" aca="1" ref="T9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6027" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0973985A-E72B-46D1-AE73-8F272F0DA5F9}"/>
+  <xr:revisionPtr revIDLastSave="6038" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8725283D-2D21-4EFB-984D-F28E692715F4}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="294">
   <si>
     <t>Scholl</t>
   </si>
@@ -949,6 +949,9 @@
   </si>
   <si>
     <t>Donat</t>
+  </si>
+  <si>
+    <t>Yeboah</t>
   </si>
 </sst>
 </file>
@@ -2084,49 +2087,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
@@ -2135,10 +2138,10 @@
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.454545454545453</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2757,6 +2760,9 @@
                 <c:pt idx="51">
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
+                <c:pt idx="54">
+                  <c:v>18.454545454545453</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3011,28 +3017,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -3041,25 +3047,25 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="36" formatCode="0.00">
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>18.90909090909091</c:v>
@@ -3955,28 +3961,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -3985,25 +3991,25 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="36" formatCode="0.00">
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>18.90909090909091</c:v>
@@ -4953,49 +4959,49 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
@@ -5004,10 +5010,10 @@
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.454545454545453</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5666,6 +5672,9 @@
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>18.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>18.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15864,21 +15873,21 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="5">
-        <f ca="1">Liefering!N1</f>
-        <v>19.373737373737374</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B2" s="3">
         <f ca="1">JWR!N1</f>
         <v>19.414772727272727</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5">
+        <f ca="1">Liefering!N1</f>
+        <v>19.444444444444443</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -15896,7 +15905,7 @@
       </c>
       <c r="B5" s="5">
         <f ca="1">Rapid!N1</f>
-        <v>19.646464646464644</v>
+        <v>19.583732057416263</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15919,20 +15928,20 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">'Young Violets'!N1</f>
-        <v>20.684210526315791</v>
+        <f ca="1">WAC!N1</f>
+        <v>20.69318181818182</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B9" s="5">
-        <f ca="1">WAC!N1</f>
-        <v>20.69318181818182</v>
+        <f ca="1">'Young Violets'!N1</f>
+        <v>20.799043062200955</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -18166,43 +18175,43 @@
       </c>
       <c r="B5" s="5" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="C5" s="5" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="D5" s="5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="E5" s="5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="F5" s="5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="G5" s="5" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="H5" s="5" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="I5" s="5" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="K5" s="5" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="L5" s="5" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18210,19 +18219,19 @@
       </c>
       <c r="M5" s="5" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="N5" s="5" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="O5" s="5" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P5" s="5" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="Q5" s="5" cm="1">
         <f t="array" aca="1" ref="Q5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18234,11 +18243,11 @@
       </c>
       <c r="S5" s="5" cm="1">
         <f t="array" aca="1" ref="S5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="T5" s="5" cm="1">
         <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18416,7 +18425,7 @@
       </c>
       <c r="T7" s="5" cm="1">
         <f t="array" aca="1" ref="T7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.454545454545453</v>
       </c>
       <c r="U7" s="5" cm="1">
         <f t="array" aca="1" ref="U7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18433,27 +18442,27 @@
       </c>
       <c r="B8" s="5" cm="1">
         <f t="array" aca="1" ref="B8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="C8" s="5" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="D8" s="5" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="E8" s="5" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="F8" s="5" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="G8" s="5" cm="1">
         <f t="array" aca="1" ref="G8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18461,7 +18470,7 @@
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18473,31 +18482,31 @@
       </c>
       <c r="L8" s="5" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="M8" s="5" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="N8" s="5" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="O8" s="5" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P8" s="5" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="R8" s="5" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -24152,7 +24161,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.684210526315791</v>
+        <v>20.799043062200955</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24205,7 +24214,7 @@
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
@@ -24229,7 +24238,7 @@
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
@@ -24241,7 +24250,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -24321,7 +24330,7 @@
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="1"/>
@@ -24333,7 +24342,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -24401,7 +24410,7 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
@@ -24413,7 +24422,7 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -24425,7 +24434,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -24493,7 +24502,7 @@
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
@@ -24505,7 +24514,7 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
@@ -24517,7 +24526,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -24594,7 +24603,7 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="4"/>
@@ -24606,7 +24615,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -24683,7 +24692,7 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
@@ -24695,7 +24704,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P18" t="s">
         <v>94</v>
@@ -24791,11 +24800,11 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
@@ -24807,7 +24816,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P21" t="s">
         <v>38</v>
@@ -24900,11 +24909,11 @@
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
@@ -24916,7 +24925,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P24" t="s">
         <v>32</v>
@@ -25009,11 +25018,11 @@
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
@@ -25025,7 +25034,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P27" t="s">
         <v>22</v>
@@ -25118,11 +25127,11 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="9"/>
@@ -25134,7 +25143,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.09090909090909</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P30" t="s">
         <v>111</v>
@@ -25328,7 +25337,7 @@
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
@@ -25352,7 +25361,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P36" t="s">
         <v>228</v>
@@ -25437,7 +25446,7 @@
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
@@ -25461,7 +25470,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P39" t="s">
         <v>248</v>
@@ -25546,7 +25555,7 @@
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="13"/>
@@ -25570,7 +25579,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P42" t="s">
         <v>272</v>
@@ -25655,7 +25664,7 @@
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H45">
         <f t="shared" ca="1" si="14"/>
@@ -25679,7 +25688,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P45" t="s">
         <v>190</v>
@@ -25928,11 +25937,11 @@
       </c>
       <c r="E54">
         <f t="shared" ca="1" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F54">
         <f t="shared" ca="1" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="17"/>
@@ -25960,7 +25969,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -26021,7 +26030,7 @@
       </c>
       <c r="F57">
         <f t="shared" ca="1" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G57">
         <f t="shared" ca="1" si="18"/>
@@ -26049,7 +26058,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -27688,6 +27697,7 @@
   <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" style="1"/>
     <col min="16" max="16" width="14.6640625" customWidth="1"/>
@@ -27696,7 +27706,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.646464646464644</v>
+        <v>19.583732057416263</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -29093,6 +29103,12 @@
         <f ca="1">AVERAGE(B42:M42)</f>
         <v>19.727272727272727</v>
       </c>
+      <c r="P42" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>39296</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -29360,7 +29376,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
         <v>162</v>
@@ -29444,6 +29460,94 @@
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
         <v>18.818181818181817</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C56" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" t="s">
+        <v>52</v>
+      </c>
+      <c r="E56" t="s">
+        <v>276</v>
+      </c>
+      <c r="F56" t="s">
+        <v>289</v>
+      </c>
+      <c r="G56" t="s">
+        <v>290</v>
+      </c>
+      <c r="H56" t="s">
+        <v>293</v>
+      </c>
+      <c r="I56" t="s">
+        <v>203</v>
+      </c>
+      <c r="J56" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" t="s">
+        <v>44</v>
+      </c>
+      <c r="L56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>18.454545454545453</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -29486,7 +29590,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.373737373737374</v>
+        <v>19.444444444444443</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -29535,7 +29639,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
@@ -29575,7 +29679,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -29624,7 +29728,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
@@ -29664,7 +29768,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -29713,7 +29817,7 @@
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
@@ -29753,7 +29857,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -29802,7 +29906,7 @@
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
@@ -29842,7 +29946,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -29891,7 +29995,7 @@
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
@@ -29931,7 +30035,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -29980,7 +30084,7 @@
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
@@ -30020,7 +30124,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P18" t="s">
         <v>99</v>
@@ -30209,7 +30313,7 @@
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
@@ -30241,7 +30345,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P24" t="s">
         <v>100</v>
@@ -30564,11 +30668,11 @@
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P33" t="s">
         <v>206</v>
@@ -30673,11 +30777,11 @@
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P36" t="s">
         <v>213</v>
@@ -30782,11 +30886,11 @@
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P39" t="s">
         <v>214</v>
@@ -30891,11 +30995,11 @@
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P42" t="s">
         <v>259</v>
@@ -31000,11 +31104,11 @@
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P45" t="s">
         <v>275</v>
@@ -31103,11 +31207,11 @@
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -31192,11 +31296,11 @@
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6038" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8725283D-2D21-4EFB-984D-F28E692715F4}"/>
+  <xr:revisionPtr revIDLastSave="6073" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EE1F978-AE3C-46CA-B796-E6A4AE1446B1}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="297">
   <si>
     <t>Scholl</t>
   </si>
@@ -953,6 +953,15 @@
   <si>
     <t>Yeboah</t>
   </si>
+  <si>
+    <t>Cechal</t>
+  </si>
+  <si>
+    <t>Maierhofer</t>
+  </si>
+  <si>
+    <t>Palacios</t>
+  </si>
 </sst>
 </file>
 
@@ -1222,6 +1231,9 @@
                 <c:pt idx="15">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1486,52 +1498,52 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.636363636363637</c:v>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="7">
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
                   <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.90909090909091</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2111,16 +2123,16 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>21.09090909090909</c:v>
@@ -2141,7 +2153,7 @@
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.545454545454547</c:v>
+                  <c:v>21.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2400,16 +2412,16 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>20.272727272727273</c:v>
@@ -2433,16 +2445,16 @@
                   <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2707,7 +2719,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>20.181818181818183</c:v>
@@ -2761,6 +2773,9 @@
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>18.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>18.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
@@ -3070,6 +3085,9 @@
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>18.90909090909091</c:v>
                 </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3337,25 +3355,25 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
@@ -3370,10 +3388,13 @@
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4014,6 +4035,9 @@
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>18.90909090909091</c:v>
                 </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4303,25 +4327,25 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
@@ -4336,10 +4360,13 @@
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4615,52 +4642,52 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.636363636363637</c:v>
+                <c:pt idx="6">
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="7">
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="12">
                   <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.90909090909091</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4983,16 +5010,16 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>21.09090909090909</c:v>
@@ -5013,7 +5040,7 @@
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.545454545454547</c:v>
+                  <c:v>21.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5292,16 +5319,16 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>20.272727272727273</c:v>
@@ -5325,16 +5352,16 @@
                   <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5620,7 +5647,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>20.181818181818183</c:v>
@@ -5674,6 +5701,9 @@
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>18.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>18.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
@@ -15878,7 +15908,7 @@
       </c>
       <c r="B2" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.414772727272727</v>
+        <v>19.427807486631014</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -15887,7 +15917,7 @@
       </c>
       <c r="B3" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>19.444444444444443</v>
+        <v>19.435406698564591</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -15905,7 +15935,7 @@
       </c>
       <c r="B5" s="5">
         <f ca="1">Rapid!N1</f>
-        <v>19.583732057416263</v>
+        <v>19.531818181818178</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15914,7 +15944,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.170454545454543</v>
+        <v>20.25568181818182</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15923,7 +15953,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.68181818181818</v>
+        <v>20.717703349282299</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15932,7 +15962,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.69318181818182</v>
+        <v>20.72727272727273</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -15941,7 +15971,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>20.799043062200955</v>
+        <v>20.822966507177028</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -15978,7 +16008,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.68181818181818</v>
+        <v>20.717703349282299</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -16500,7 +16530,7 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
@@ -16512,7 +16542,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P18" t="s">
         <v>67</v>
@@ -16693,7 +16723,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
@@ -16733,7 +16763,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P24" t="s">
         <v>76</v>
@@ -16911,7 +16941,7 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
@@ -16951,7 +16981,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P30" t="s">
         <v>119</v>
@@ -17020,7 +17050,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
@@ -17060,7 +17090,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P33" t="s">
         <v>149</v>
@@ -17129,7 +17159,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -17169,7 +17199,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P36" t="s">
         <v>184</v>
@@ -17505,6 +17535,14 @@
         <v>39164</v>
       </c>
     </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>39069</v>
+      </c>
+    </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>49</v>
@@ -17660,7 +17698,7 @@
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I51">
         <f t="shared" ca="1" si="16"/>
@@ -17680,7 +17718,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -17773,10 +17811,93 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
+        <v>292</v>
+      </c>
+      <c r="C56" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" t="s">
+        <v>202</v>
+      </c>
+      <c r="H56" t="s">
+        <v>57</v>
+      </c>
+      <c r="I56" t="s">
+        <v>118</v>
+      </c>
+      <c r="J56" t="s">
+        <v>66</v>
+      </c>
+      <c r="K56" t="s">
+        <v>226</v>
+      </c>
+      <c r="L56" t="s">
+        <v>102</v>
+      </c>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N57" s="1"/>
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>23</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>22</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>26</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>26</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>20.818181818181817</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N59" s="1"/>
@@ -17972,7 +18093,7 @@
       </c>
       <c r="R2" s="8" cm="1">
         <f t="array" aca="1" ref="R2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="S2" s="8" cm="1">
         <f t="array" aca="1" ref="S2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -17997,55 +18118,55 @@
       </c>
       <c r="B3" s="8" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="C3" s="8" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="D3" s="8" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="E3" s="8" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="F3" s="8" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="H3" s="8" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="J3" s="8" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="K3" s="8" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="L3" s="8" cm="1">
         <f t="array" aca="1" ref="L3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="M3" s="8" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18053,11 +18174,11 @@
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18207,19 +18328,19 @@
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="K5" s="5" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="L5" s="5" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="M5" s="5" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="N5" s="5" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18247,7 +18368,7 @@
       </c>
       <c r="T5" s="5" cm="1">
         <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.545454545454547</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18268,7 +18389,7 @@
       </c>
       <c r="C6" s="5" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18276,11 +18397,11 @@
       </c>
       <c r="E6" s="5" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="F6" s="5" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="G6" s="5" cm="1">
         <f t="array" aca="1" ref="G6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18312,11 +18433,11 @@
       </c>
       <c r="N6" s="5" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="O6" s="5" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P6" s="5" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18324,7 +18445,7 @@
       </c>
       <c r="Q6" s="5" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="R6" s="5" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18353,7 +18474,7 @@
       </c>
       <c r="B7" s="5" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="C7" s="5" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18429,7 +18550,7 @@
       </c>
       <c r="U7" s="5" cm="1">
         <f t="array" aca="1" ref="U7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.454545454545453</v>
       </c>
       <c r="V7" s="5" cm="1">
         <f t="array" aca="1" ref="V7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18514,7 +18635,7 @@
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18551,7 +18672,7 @@
       </c>
       <c r="G9" s="5" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="H9" s="5" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18559,7 +18680,7 @@
       </c>
       <c r="I9" s="5" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="J9" s="5" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18567,15 +18688,15 @@
       </c>
       <c r="K9" s="5" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="L9" s="5" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="M9" s="5" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="N9" s="5" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18595,7 +18716,7 @@
       </c>
       <c r="R9" s="5" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="S9" s="5" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18603,7 +18724,7 @@
       </c>
       <c r="T9" s="5" cm="1">
         <f t="array" aca="1" ref="T9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="U9" s="5" cm="1">
         <f t="array" aca="1" ref="U9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19242,7 +19363,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.414772727272727</v>
+        <v>19.427807486631014</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -20868,7 +20989,7 @@
         <v>39468</v>
       </c>
     </row>
-    <row r="49" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P49" t="s">
         <v>283</v>
       </c>
@@ -20876,7 +20997,43 @@
         <v>38486</v>
       </c>
     </row>
-    <row r="50" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
+        <v>294</v>
+      </c>
+      <c r="C50" t="s">
+        <v>284</v>
+      </c>
+      <c r="D50" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>0</v>
+      </c>
+      <c r="H50" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" t="s">
+        <v>261</v>
+      </c>
+      <c r="J50" t="s">
+        <v>83</v>
+      </c>
+      <c r="K50" t="s">
+        <v>166</v>
+      </c>
+      <c r="L50" t="s">
+        <v>280</v>
+      </c>
       <c r="P50" t="s">
         <v>284</v>
       </c>
@@ -20884,19 +21041,72 @@
         <v>38422</v>
       </c>
     </row>
-    <row r="51" spans="14:17" x14ac:dyDescent="0.3">
-      <c r="N51" s="1"/>
-    </row>
-    <row r="54" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="G51">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="I51">
+        <f t="shared" ca="1" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="N51" s="1">
+        <f ca="1">AVERAGE(B51:M51)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="P51" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>38384</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N54" s="1"/>
     </row>
-    <row r="57" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N57" s="1"/>
     </row>
-    <row r="60" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N60" s="1"/>
     </row>
-    <row r="63" spans="14:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N63" s="1"/>
     </row>
     <row r="66" spans="14:14" x14ac:dyDescent="0.3">
@@ -20936,7 +21146,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.170454545454543</v>
+        <v>20.25568181818182</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -20984,7 +21194,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
@@ -21024,7 +21234,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -21072,7 +21282,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
@@ -21112,7 +21322,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -21160,7 +21370,7 @@
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
@@ -21200,7 +21410,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -21248,7 +21458,7 @@
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
@@ -21288,7 +21498,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -21336,7 +21546,7 @@
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
@@ -21376,7 +21586,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -21424,7 +21634,7 @@
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
@@ -21464,7 +21674,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -21529,7 +21739,7 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
@@ -21569,7 +21779,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -21637,7 +21847,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
@@ -21677,7 +21887,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P24" t="s">
         <v>87</v>
@@ -21745,7 +21955,7 @@
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
@@ -21785,7 +21995,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P27" t="s">
         <v>35</v>
@@ -21853,7 +22063,7 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
@@ -21893,7 +22103,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P30" t="s">
         <v>105</v>
@@ -21961,7 +22171,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
@@ -22001,7 +22211,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P33" t="s">
         <v>152</v>
@@ -22069,7 +22279,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -22109,7 +22319,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P36" t="s">
         <v>169</v>
@@ -22177,7 +22387,7 @@
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
@@ -22217,7 +22427,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P39" t="s">
         <v>252</v>
@@ -22421,7 +22631,7 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
@@ -22433,7 +22643,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P45" t="s">
         <v>287</v>
@@ -22515,7 +22725,7 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="15"/>
@@ -22527,7 +22737,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -24161,7 +24371,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.799043062200955</v>
+        <v>20.822966507177028</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24994,7 +25204,7 @@
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
@@ -25034,7 +25244,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P27" t="s">
         <v>22</v>
@@ -25103,7 +25313,7 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
@@ -25143,7 +25353,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P30" t="s">
         <v>111</v>
@@ -25212,7 +25422,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
@@ -25252,7 +25462,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P33" t="s">
         <v>179</v>
@@ -25321,7 +25531,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -25361,7 +25571,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P36" t="s">
         <v>228</v>
@@ -26022,7 +26232,7 @@
       </c>
       <c r="D57">
         <f t="shared" ca="1" si="18"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E57">
         <f t="shared" ca="1" si="18"/>
@@ -26058,7 +26268,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>21.545454545454547</v>
+        <v>21.636363636363637</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -26083,7 +26293,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.69318181818182</v>
+        <v>20.72727272727273</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -26239,7 +26449,7 @@
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
@@ -26259,7 +26469,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -26411,7 +26621,7 @@
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
@@ -26435,7 +26645,7 @@
       </c>
       <c r="N12" s="1">
         <f t="shared" ref="N12" ca="1" si="4">AVERAGE(B12:M12)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -26499,7 +26709,7 @@
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="5"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="5"/>
@@ -26523,7 +26733,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:L15)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -27330,7 +27540,7 @@
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="13">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="13"/>
@@ -27370,7 +27580,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:L39)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P39" t="s">
         <v>20</v>
@@ -27466,7 +27676,7 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="14"/>
@@ -27478,7 +27688,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:L42)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P42" t="s">
         <v>251</v>
@@ -27640,7 +27850,7 @@
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="16">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="16"/>
@@ -27680,7 +27890,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
     </row>
   </sheetData>
@@ -27706,7 +27916,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.583732057416263</v>
+        <v>19.531818181818178</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27786,7 +27996,7 @@
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
@@ -27794,7 +28004,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -29547,6 +29757,94 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
+        <v>18.454545454545453</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D59" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" t="s">
+        <v>276</v>
+      </c>
+      <c r="F59" t="s">
+        <v>289</v>
+      </c>
+      <c r="G59" t="s">
+        <v>290</v>
+      </c>
+      <c r="H59" t="s">
+        <v>293</v>
+      </c>
+      <c r="I59" t="s">
+        <v>203</v>
+      </c>
+      <c r="J59" t="s">
+        <v>54</v>
+      </c>
+      <c r="K59" t="s">
+        <v>44</v>
+      </c>
+      <c r="L59" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>17</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
         <v>18.454545454545453</v>
       </c>
     </row>
@@ -29590,7 +29888,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.444444444444443</v>
+        <v>19.435406698564591</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -31163,6 +31461,12 @@
         <v>62</v>
       </c>
       <c r="N47" s="1"/>
+      <c r="P47" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>39132</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -31393,10 +31697,93 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C56" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>58</v>
+      </c>
+      <c r="F56" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" t="s">
+        <v>291</v>
+      </c>
+      <c r="H56" t="s">
+        <v>62</v>
+      </c>
+      <c r="I56" t="s">
+        <v>274</v>
+      </c>
+      <c r="J56" t="s">
+        <v>147</v>
+      </c>
+      <c r="K56" t="s">
+        <v>296</v>
+      </c>
+      <c r="L56" t="s">
+        <v>61</v>
+      </c>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N57" s="1"/>
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:L57)</f>
+        <v>19.272727272727273</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N59" s="1"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6073" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EE1F978-AE3C-46CA-B796-E6A4AE1446B1}"/>
+  <xr:revisionPtr revIDLastSave="6113" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{598F61EF-EE9C-4F1F-832E-61028E2891E6}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="300">
   <si>
     <t>Scholl</t>
   </si>
@@ -962,6 +962,15 @@
   <si>
     <t>Palacios</t>
   </si>
+  <si>
+    <t>Antonitsch</t>
+  </si>
+  <si>
+    <t>Wilson</t>
+  </si>
+  <si>
+    <t>Chase</t>
+  </si>
 </sst>
 </file>
 
@@ -1232,7 +1241,7 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2155,6 +2164,9 @@
                 <c:pt idx="18">
                   <c:v>21.636363636363637</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.727272727272727</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2455,6 +2467,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3074,7 +3089,7 @@
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -3083,10 +3098,13 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3349,16 +3367,16 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
@@ -3370,16 +3388,16 @@
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
@@ -3395,6 +3413,9 @@
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4024,7 +4045,7 @@
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -4033,10 +4054,13 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4321,16 +4345,16 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
@@ -4342,16 +4366,16 @@
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
@@ -4367,6 +4391,9 @@
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5042,6 +5069,9 @@
                 <c:pt idx="18">
                   <c:v>21.636363636363637</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.727272727272727</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5362,6 +5392,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15908,7 +15941,7 @@
       </c>
       <c r="B2" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.427807486631014</v>
+        <v>19.433155080213904</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -15917,7 +15950,7 @@
       </c>
       <c r="B3" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>19.435406698564591</v>
+        <v>19.449999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -15949,20 +15982,20 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5">
-        <f ca="1">Sturm!N1</f>
-        <v>20.717703349282299</v>
+        <f ca="1">WAC!N1</f>
+        <v>20.716577540106954</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">WAC!N1</f>
-        <v>20.72727272727273</v>
+        <f ca="1">Sturm!N1</f>
+        <v>20.74545454545455</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -15971,7 +16004,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>20.822966507177028</v>
+        <v>20.868181818181817</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16008,7 +16041,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.717703349282299</v>
+        <v>20.74545454545455</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -16344,7 +16377,7 @@
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
@@ -16364,7 +16397,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -16522,7 +16555,7 @@
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
@@ -16542,7 +16575,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P18" t="s">
         <v>67</v>
@@ -16634,7 +16667,7 @@
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
@@ -16654,7 +16687,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P21" t="s">
         <v>57</v>
@@ -17070,7 +17103,7 @@
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
@@ -17090,7 +17123,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P33" t="s">
         <v>149</v>
@@ -17179,7 +17212,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
@@ -17199,7 +17232,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P36" t="s">
         <v>184</v>
@@ -17393,7 +17426,7 @@
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="13"/>
@@ -17417,7 +17450,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="P42" t="s">
         <v>256</v>
@@ -17581,6 +17614,12 @@
         <v>102</v>
       </c>
       <c r="N47" s="1"/>
+      <c r="P47" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>38722</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -17900,10 +17939,93 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" t="s">
+        <v>292</v>
+      </c>
+      <c r="C59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s">
+        <v>183</v>
+      </c>
+      <c r="G59" t="s">
+        <v>202</v>
+      </c>
+      <c r="H59" t="s">
+        <v>57</v>
+      </c>
+      <c r="I59" t="s">
+        <v>118</v>
+      </c>
+      <c r="J59" t="s">
+        <v>66</v>
+      </c>
+      <c r="K59" t="s">
+        <v>298</v>
+      </c>
+      <c r="L59" t="s">
+        <v>102</v>
+      </c>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N60" s="1"/>
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>23</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>26</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>26</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
+        <v>20.727272727272727</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N62" s="1"/>
@@ -18093,7 +18215,7 @@
       </c>
       <c r="R2" s="8" cm="1">
         <f t="array" aca="1" ref="R2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="S2" s="8" cm="1">
         <f t="array" aca="1" ref="S2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18372,7 +18494,7 @@
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="V5" s="5" cm="1">
         <f t="array" aca="1" ref="V5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18449,7 +18571,7 @@
       </c>
       <c r="R6" s="5" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="S6" s="5" cm="1">
         <f t="array" aca="1" ref="S6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18619,7 +18741,7 @@
       </c>
       <c r="P8" s="5" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18631,15 +18753,15 @@
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -18664,7 +18786,7 @@
       </c>
       <c r="E9" s="5" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="F9" s="5" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18672,11 +18794,11 @@
       </c>
       <c r="G9" s="5" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="H9" s="5" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="I9" s="5" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18692,11 +18814,11 @@
       </c>
       <c r="L9" s="5" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="M9" s="5" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="N9" s="5" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18704,7 +18826,7 @@
       </c>
       <c r="O9" s="5" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="P9" s="5" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -18728,7 +18850,7 @@
       </c>
       <c r="U9" s="5" cm="1">
         <f t="array" aca="1" ref="U9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="V9" s="5" cm="1">
         <f t="array" aca="1" ref="V9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19363,7 +19485,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.427807486631014</v>
+        <v>19.433155080213904</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21048,7 +21170,7 @@
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
@@ -21088,7 +21210,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P51" t="s">
         <v>294</v>
@@ -24371,7 +24493,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.822966507177028</v>
+        <v>20.868181818181817</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -26271,8 +26393,94 @@
         <v>21.636363636363637</v>
       </c>
     </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>178</v>
+      </c>
+      <c r="B59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E59" t="s">
+        <v>242</v>
+      </c>
+      <c r="F59" t="s">
+        <v>38</v>
+      </c>
+      <c r="G59" t="s">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" t="s">
+        <v>111</v>
+      </c>
+      <c r="J59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" t="s">
+        <v>271</v>
+      </c>
+      <c r="L59" t="s">
+        <v>288</v>
+      </c>
+      <c r="N59" s="1"/>
+    </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N60" s="1"/>
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>36</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>28</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
+        <v>21.727272727272727</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -26283,7 +26491,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -26293,7 +26501,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.72727272727273</v>
+        <v>20.716577540106954</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27805,6 +28013,14 @@
         <v>37955</v>
       </c>
     </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>39276</v>
+      </c>
+    </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
@@ -27891,6 +28107,94 @@
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
         <v>21.09090909090909</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>266</v>
+      </c>
+      <c r="F50" t="s">
+        <v>297</v>
+      </c>
+      <c r="G50" t="s">
+        <v>239</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" t="s">
+        <v>96</v>
+      </c>
+      <c r="J50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K50" t="s">
+        <v>97</v>
+      </c>
+      <c r="L50" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:L51" ca="1" si="17">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="17"/>
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="G51">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="I51">
+        <f t="shared" ca="1" si="17"/>
+        <v>21</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ca="1" si="17"/>
+        <v>24</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="N51" s="1">
+        <f ca="1">AVERAGE(B51:L51)</f>
+        <v>20.545454545454547</v>
       </c>
     </row>
   </sheetData>
@@ -29882,13 +30186,14 @@
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.435406698564591</v>
+        <v>19.449999999999996</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -31394,7 +31699,7 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
@@ -31406,7 +31711,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P45" t="s">
         <v>275</v>
@@ -31517,6 +31822,12 @@
         <f ca="1">AVERAGE(B48:L48)</f>
         <v>19.454545454545453</v>
       </c>
+      <c r="P48" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>38070</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -31677,7 +31988,7 @@
       </c>
       <c r="I54">
         <f t="shared" ca="1" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="17"/>
@@ -31693,7 +32004,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:L54)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -31766,7 +32077,7 @@
       </c>
       <c r="I57">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57">
         <f t="shared" ca="1" si="18"/>
@@ -31782,14 +32093,97 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:L57)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" t="s">
+        <v>215</v>
+      </c>
+      <c r="D59" t="s">
+        <v>214</v>
+      </c>
+      <c r="E59" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" t="s">
+        <v>274</v>
+      </c>
+      <c r="J59" t="s">
+        <v>299</v>
+      </c>
+      <c r="K59" t="s">
+        <v>205</v>
+      </c>
+      <c r="L59" t="s">
+        <v>61</v>
+      </c>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N60" s="1"/>
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:L60)</f>
+        <v>19.454545454545453</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N62" s="1"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6113" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{598F61EF-EE9C-4F1F-832E-61028E2891E6}"/>
+  <xr:revisionPtr revIDLastSave="6204" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B190B82-CC16-4032-B34F-DE9FC3CBCEC4}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="307">
   <si>
     <t>Scholl</t>
   </si>
@@ -971,6 +971,27 @@
   <si>
     <t>Chase</t>
   </si>
+  <si>
+    <t>Scharner</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>Aisowieren</t>
+  </si>
+  <si>
+    <t>Wustinger</t>
+  </si>
+  <si>
+    <t>Scherf</t>
+  </si>
+  <si>
+    <t>de Freitas</t>
+  </si>
+  <si>
+    <t>Djuric</t>
+  </si>
 </sst>
 </file>
 
@@ -1242,6 +1263,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1554,6 +1578,9 @@
                 <c:pt idx="15">
                   <c:v>20</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.90909090909091</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1814,13 +1841,13 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
@@ -1854,6 +1881,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,10 +2144,10 @@
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21</c:v>
@@ -2126,25 +2156,25 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>21</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>21.272727272727273</c:v>
@@ -2159,13 +2189,13 @@
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21.727272727272727</c:v>
+                  <c:v>21.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2471,6 +2501,9 @@
                 <c:pt idx="16">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>21</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2743,13 +2776,13 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.90909090909091</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.636363636363637</c:v>
@@ -2767,10 +2800,10 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>19.727272727272727</c:v>
@@ -2782,7 +2815,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>18.818181818181817</c:v>
@@ -2792,6 +2825,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>18.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3106,6 +3142,9 @@
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3417,6 +3456,9 @@
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3688,13 +3730,13 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
@@ -3728,6 +3770,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4062,6 +4107,9 @@
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4395,6 +4443,9 @@
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4716,6 +4767,9 @@
                 <c:pt idx="15">
                   <c:v>20</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.90909090909091</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5019,10 +5073,10 @@
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>21</c:v>
@@ -5031,25 +5085,25 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>21</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>21.272727272727273</c:v>
@@ -5064,13 +5118,13 @@
                   <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21.727272727272727</c:v>
+                  <c:v>21.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5396,6 +5450,9 @@
                 <c:pt idx="16">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
+                <c:pt idx="17">
+                  <c:v>21</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5689,13 +5746,13 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>19.90909090909091</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.636363636363637</c:v>
@@ -5713,10 +5770,10 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>19.727272727272727</c:v>
@@ -5728,7 +5785,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>18.818181818181817</c:v>
@@ -5738,6 +5795,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>18.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15936,21 +15996,21 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="5">
+        <f ca="1">Liefering!N1</f>
+        <v>19.437229437229433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B3" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.433155080213904</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="5">
-        <f ca="1">Liefering!N1</f>
-        <v>19.449999999999996</v>
+        <v>19.474747474747474</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -15959,7 +16019,7 @@
       </c>
       <c r="B4" s="5">
         <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.47159090909091</v>
+        <v>19.497326203208559</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15968,7 +16028,7 @@
       </c>
       <c r="B5" s="5">
         <f ca="1">Rapid!N1</f>
-        <v>19.531818181818178</v>
+        <v>19.519480519480517</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15977,7 +16037,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.25568181818182</v>
+        <v>20.176470588235297</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15986,7 +16046,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.716577540106954</v>
+        <v>20.732323232323235</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15995,7 +16055,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.74545454545455</v>
+        <v>20.748917748917751</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -16004,7 +16064,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>20.868181818181817</v>
+        <v>20.961038961038959</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16041,7 +16101,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.74545454545455</v>
+        <v>20.748917748917751</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -18028,10 +18088,93 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" t="s">
+        <v>292</v>
+      </c>
+      <c r="C62" t="s">
+        <v>295</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" t="s">
+        <v>65</v>
+      </c>
+      <c r="G62" t="s">
+        <v>202</v>
+      </c>
+      <c r="H62" t="s">
+        <v>57</v>
+      </c>
+      <c r="I62" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" t="s">
+        <v>66</v>
+      </c>
+      <c r="K62" t="s">
+        <v>226</v>
+      </c>
+      <c r="L62" t="s">
+        <v>102</v>
+      </c>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N63" s="1"/>
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>23</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>22</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>26</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>26</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
+        <v>20.818181818181817</v>
+      </c>
     </row>
     <row r="65" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N65" s="1"/>
@@ -18219,7 +18362,7 @@
       </c>
       <c r="S2" s="8" cm="1">
         <f t="array" aca="1" ref="S2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="T2" s="8" cm="1">
         <f t="array" aca="1" ref="T2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18304,7 +18447,7 @@
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18337,15 +18480,15 @@
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18393,7 +18536,7 @@
       </c>
       <c r="R4" s="5" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="S4" s="5" cm="1">
         <f t="array" aca="1" ref="S4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18426,11 +18569,11 @@
       </c>
       <c r="D5" s="5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="E5" s="5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="F5" s="5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18442,11 +18585,11 @@
       </c>
       <c r="H5" s="5" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18454,19 +18597,19 @@
       </c>
       <c r="K5" s="5" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="L5" s="5" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="M5" s="5" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="N5" s="5" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="O5" s="5" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18486,19 +18629,19 @@
       </c>
       <c r="S5" s="5" cm="1">
         <f t="array" aca="1" ref="S5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="T5" s="5" cm="1">
         <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.727272727272727</v>
+        <v>21.818181818181817</v>
       </c>
       <c r="V5" s="5" cm="1">
         <f t="array" aca="1" ref="V5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.818181818181817</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -18575,7 +18718,7 @@
       </c>
       <c r="S6" s="5" cm="1">
         <f t="array" aca="1" ref="S6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T6" s="5" cm="1">
         <f t="array" aca="1" ref="T6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18608,7 +18751,7 @@
       </c>
       <c r="E7" s="5" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="F7" s="5" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18616,7 +18759,7 @@
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18640,11 +18783,11 @@
       </c>
       <c r="M7" s="5" cm="1">
         <f t="array" aca="1" ref="M7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="N7" s="5" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="O7" s="5" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18660,7 +18803,7 @@
       </c>
       <c r="R7" s="5" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="S7" s="5" cm="1">
         <f t="array" aca="1" ref="S7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -18676,7 +18819,7 @@
       </c>
       <c r="V7" s="5" cm="1">
         <f t="array" aca="1" ref="V7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.818181818181817</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -18765,7 +18908,7 @@
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -18854,7 +18997,7 @@
       </c>
       <c r="V9" s="5" cm="1">
         <f t="array" aca="1" ref="V9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -19485,7 +19628,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.433155080213904</v>
+        <v>19.474747474747474</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21219,8 +21362,101 @@
         <v>38384</v>
       </c>
     </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P52" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>38569</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" t="s">
+        <v>294</v>
+      </c>
+      <c r="C53" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" t="s">
+        <v>81</v>
+      </c>
+      <c r="E53" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" t="s">
+        <v>278</v>
+      </c>
+      <c r="J53" t="s">
+        <v>83</v>
+      </c>
+      <c r="K53" t="s">
+        <v>75</v>
+      </c>
+      <c r="L53" t="s">
+        <v>280</v>
+      </c>
+    </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N54" s="1"/>
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>23</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>24</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>20.181818181818183</v>
+      </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N57" s="1"/>
@@ -21255,7 +21491,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -21268,7 +21504,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.25568181818182</v>
+        <v>20.176470588235297</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -22774,6 +23010,14 @@
         <v>39689</v>
       </c>
     </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>39524</v>
+      </c>
+    </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>33</v>
@@ -22860,6 +23104,94 @@
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" t="s">
+        <v>200</v>
+      </c>
+      <c r="E50" t="s">
+        <v>253</v>
+      </c>
+      <c r="F50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50" t="s">
+        <v>285</v>
+      </c>
+      <c r="H50" t="s">
+        <v>301</v>
+      </c>
+      <c r="I50" t="s">
+        <v>286</v>
+      </c>
+      <c r="J50" t="s">
+        <v>6</v>
+      </c>
+      <c r="K50" t="s">
+        <v>287</v>
+      </c>
+      <c r="L50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="G51">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ca="1" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="I51">
+        <f t="shared" ca="1" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ca="1" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="N51" s="1">
+        <f ca="1">AVERAGE(B51:M51)</f>
+        <v>18.90909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -22873,7 +23205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -22884,7 +23216,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.47159090909091</v>
+        <v>19.497326203208559</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -23128,7 +23460,7 @@
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="2"/>
@@ -23148,7 +23480,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -23216,7 +23548,7 @@
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
@@ -23236,7 +23568,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -23304,7 +23636,7 @@
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
@@ -23324,7 +23656,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -24389,6 +24721,20 @@
         <f ca="1">AVERAGE(B45:M45)</f>
         <v>20.181818181818183</v>
       </c>
+      <c r="P45" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>38724</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P46" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>37752</v>
+      </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -24476,6 +24822,94 @@
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>20.09090909090909</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" t="s">
+        <v>304</v>
+      </c>
+      <c r="C50" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" t="s">
+        <v>212</v>
+      </c>
+      <c r="H50" t="s">
+        <v>92</v>
+      </c>
+      <c r="I50" t="s">
+        <v>305</v>
+      </c>
+      <c r="J50" t="s">
+        <v>237</v>
+      </c>
+      <c r="K50" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D51">
+        <f t="shared" ca="1" si="16"/>
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ca="1" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="G51">
+        <f t="shared" ca="1" si="16"/>
+        <v>24</v>
+      </c>
+      <c r="H51">
+        <f t="shared" ca="1" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="I51">
+        <f t="shared" ca="1" si="16"/>
+        <v>20</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ca="1" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="K51">
+        <f t="shared" ca="1" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="L51">
+        <f t="shared" ca="1" si="16"/>
+        <v>19</v>
+      </c>
+      <c r="N51" s="1">
+        <f ca="1">AVERAGE(B51:M51)</f>
+        <v>19.636363636363637</v>
       </c>
     </row>
   </sheetData>
@@ -24487,13 +24921,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628DC590-5B70-45B7-BCD6-8ED432E7A1AF}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.868181818181817</v>
+        <v>20.961038961038959</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24758,7 +25192,7 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -24766,7 +25200,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -24850,7 +25284,7 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
@@ -24858,7 +25292,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -25108,7 +25542,7 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
@@ -25148,7 +25582,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P21" t="s">
         <v>38</v>
@@ -25217,7 +25651,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
@@ -25257,7 +25691,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P24" t="s">
         <v>32</v>
@@ -25471,11 +25905,11 @@
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P30" t="s">
         <v>111</v>
@@ -25580,11 +26014,11 @@
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P33" t="s">
         <v>179</v>
@@ -25689,11 +26123,11 @@
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P36" t="s">
         <v>228</v>
@@ -25798,11 +26232,11 @@
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P39" t="s">
         <v>248</v>
@@ -26075,6 +26509,12 @@
         <v>79</v>
       </c>
       <c r="N47" s="1"/>
+      <c r="P47" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>37823</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -26281,7 +26721,7 @@
       </c>
       <c r="H54">
         <f t="shared" ca="1" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I54">
         <f t="shared" ca="1" si="17"/>
@@ -26301,7 +26741,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -26370,7 +26810,7 @@
       </c>
       <c r="H57">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I57">
         <f t="shared" ca="1" si="18"/>
@@ -26390,7 +26830,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -26459,7 +26899,7 @@
       </c>
       <c r="H60">
         <f t="shared" ca="1" si="19"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I60">
         <f t="shared" ca="1" si="19"/>
@@ -26479,7 +26919,96 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>21.727272727272727</v>
+        <v>21.818181818181817</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" t="s">
+        <v>94</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>231</v>
+      </c>
+      <c r="E62" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" t="s">
+        <v>303</v>
+      </c>
+      <c r="G62" t="s">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s">
+        <v>228</v>
+      </c>
+      <c r="I62" t="s">
+        <v>111</v>
+      </c>
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" t="s">
+        <v>272</v>
+      </c>
+      <c r="L62" t="s">
+        <v>288</v>
+      </c>
+      <c r="N62" s="1"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>22</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>36</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>28</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
+        <v>21.818181818181817</v>
       </c>
     </row>
   </sheetData>
@@ -26491,7 +27020,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -26501,7 +27030,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.716577540106954</v>
+        <v>20.732323232323235</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -28058,6 +28587,12 @@
       <c r="L47" t="s">
         <v>171</v>
       </c>
+      <c r="P47" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>36921</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -28108,6 +28643,12 @@
         <f ca="1">AVERAGE(B48:L48)</f>
         <v>21.09090909090909</v>
       </c>
+      <c r="P48" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>38795</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -28195,6 +28736,94 @@
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
         <v>20.545454545454547</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>266</v>
+      </c>
+      <c r="F53" t="s">
+        <v>306</v>
+      </c>
+      <c r="G53" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J53" t="s">
+        <v>12</v>
+      </c>
+      <c r="K53" t="s">
+        <v>194</v>
+      </c>
+      <c r="L53" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="18">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="18"/>
+        <v>25</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="18"/>
+        <v>24</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:L54)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -28220,7 +28849,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.531818181818178</v>
+        <v>19.519480519480517</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -28536,7 +29165,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
@@ -28572,7 +29201,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -28736,7 +29365,7 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
@@ -28748,7 +29377,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="P18" t="s">
         <v>47</v>
@@ -29379,7 +30008,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
@@ -29399,7 +30028,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P36" t="s">
         <v>233</v>
@@ -29487,7 +30116,7 @@
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
@@ -29507,7 +30136,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P39" t="s">
         <v>276</v>
@@ -29845,7 +30474,7 @@
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
@@ -29885,7 +30514,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
@@ -30153,10 +30782,93 @@
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="N62"/>
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>276</v>
+      </c>
+      <c r="F62" t="s">
+        <v>289</v>
+      </c>
+      <c r="G62" t="s">
+        <v>290</v>
+      </c>
+      <c r="H62" t="s">
+        <v>233</v>
+      </c>
+      <c r="I62" t="s">
+        <v>203</v>
+      </c>
+      <c r="J62" t="s">
+        <v>163</v>
+      </c>
+      <c r="K62" t="s">
+        <v>44</v>
+      </c>
+      <c r="L62" t="s">
+        <v>45</v>
+      </c>
       <c r="O62" s="1"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>17</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
+        <v>18.818181818181817</v>
+      </c>
       <c r="O63" s="1"/>
     </row>
     <row r="65" spans="14:14" x14ac:dyDescent="0.3">
@@ -30193,7 +30905,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.449999999999996</v>
+        <v>19.437229437229433</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -31829,7 +32541,15 @@
         <v>38070</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>38454</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -31868,7 +32588,7 @@
       </c>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -31918,7 +32638,7 @@
         <v>19.363636363636363</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>170</v>
       </c>
@@ -31957,7 +32677,7 @@
       </c>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>18</v>
@@ -32007,7 +32727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -32046,7 +32766,7 @@
       </c>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>18</v>
@@ -32096,7 +32816,7 @@
         <v>19.363636363636363</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>50</v>
       </c>
@@ -32135,7 +32855,7 @@
       </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -32185,11 +32905,94 @@
         <v>19.454545454545453</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" t="s">
+        <v>225</v>
+      </c>
+      <c r="C62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" t="s">
+        <v>214</v>
+      </c>
+      <c r="E62" t="s">
+        <v>101</v>
+      </c>
+      <c r="F62" t="s">
+        <v>291</v>
+      </c>
+      <c r="G62" t="s">
+        <v>217</v>
+      </c>
+      <c r="H62" t="s">
+        <v>300</v>
+      </c>
+      <c r="I62" t="s">
+        <v>64</v>
+      </c>
+      <c r="J62" t="s">
+        <v>299</v>
+      </c>
+      <c r="K62" t="s">
+        <v>205</v>
+      </c>
+      <c r="L62" t="s">
+        <v>61</v>
+      </c>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N63" s="1"/>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:L63)</f>
+        <v>19.181818181818183</v>
+      </c>
     </row>
     <row r="65" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N65" s="1"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6204" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B190B82-CC16-4032-B34F-DE9FC3CBCEC4}"/>
+  <xr:revisionPtr revIDLastSave="6287" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2C6164-295C-4DBD-A54B-BCF59616C2EA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="310">
   <si>
     <t>Scholl</t>
   </si>
@@ -992,6 +992,15 @@
   <si>
     <t>Djuric</t>
   </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Wanker</t>
+  </si>
+  <si>
+    <t>Peinhart</t>
+  </si>
 </sst>
 </file>
 
@@ -1214,25 +1223,25 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>18.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>19.636363636363637</c:v>
@@ -1266,6 +1275,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1540,7 +1552,7 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
@@ -1573,13 +1585,19 @@
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1862,13 +1880,13 @@
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>19.363636363636363</c:v>
@@ -1884,6 +1902,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2451,58 +2472,61 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>21</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21.09090909090909</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2829,6 +2853,9 @@
                 <c:pt idx="56">
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
+                <c:pt idx="57">
+                  <c:v>19</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3145,6 +3172,9 @@
                 <c:pt idx="56" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
+                <c:pt idx="57" formatCode="0.00">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3459,6 +3489,9 @@
                 <c:pt idx="56" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
+                <c:pt idx="57" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3751,13 +3784,13 @@
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>19.363636363636363</c:v>
@@ -3773,6 +3806,9 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4108,6 +4144,9 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
@@ -4446,6 +4485,9 @@
                 <c:pt idx="56" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
+                <c:pt idx="57" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4729,7 +4771,7 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
@@ -4762,13 +4804,19 @@
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5400,58 +5448,61 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>21</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21.09090909090909</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21</c:v>
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5799,6 +5850,9 @@
                 <c:pt idx="56">
                   <c:v>18.818181818181817</c:v>
                 </c:pt>
+                <c:pt idx="57">
+                  <c:v>19</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6050,7 +6104,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>19,55</c:v>
+                  <c:v>19,64</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -16001,34 +16055,34 @@
       </c>
       <c r="B2" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>19.437229437229433</v>
+        <v>19.425619834710741</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5">
+        <f ca="1">Rapid!N1</f>
+        <v>19.495867768595041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B4" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.474747474747474</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5">
-        <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.497326203208559</v>
+        <v>19.497607655502396</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5">
-        <f ca="1">Rapid!N1</f>
-        <v>19.519480519480517</v>
+        <f ca="1">'Altach Juniors'!N1</f>
+        <v>19.550505050505052</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16037,25 +16091,25 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.176470588235297</v>
+        <v>20.090909090909093</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5">
-        <f ca="1">WAC!N1</f>
-        <v>20.732323232323235</v>
+        <f ca="1">Sturm!N1</f>
+        <v>20.752066115702483</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">Sturm!N1</f>
-        <v>20.748917748917751</v>
+        <f ca="1">WAC!N1</f>
+        <v>20.909090909090907</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -16064,7 +16118,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>20.961038961038959</v>
+        <v>21.004132231404956</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16101,7 +16155,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.748917748917751</v>
+        <v>20.752066115702483</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -17730,6 +17784,12 @@
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>20.90909090909091</v>
       </c>
+      <c r="P48" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>39860</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -18176,34 +18236,117 @@
         <v>20.818181818181817</v>
       </c>
     </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" t="s">
+        <v>295</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" t="s">
+        <v>202</v>
+      </c>
+      <c r="H65" t="s">
+        <v>57</v>
+      </c>
+      <c r="I65" t="s">
+        <v>118</v>
+      </c>
+      <c r="J65" t="s">
+        <v>66</v>
+      </c>
+      <c r="K65" t="s">
+        <v>309</v>
+      </c>
+      <c r="L65" t="s">
+        <v>102</v>
+      </c>
       <c r="N65" s="1"/>
     </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N66" s="1"/>
-    </row>
-    <row r="68" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>23</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>26</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>20.818181818181817</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N68" s="1"/>
     </row>
-    <row r="69" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N69" s="1"/>
     </row>
-    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N71" s="1"/>
     </row>
-    <row r="72" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N72" s="1"/>
     </row>
-    <row r="74" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N74" s="1"/>
     </row>
-    <row r="75" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N75" s="1"/>
     </row>
-    <row r="77" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N78" s="1"/>
     </row>
   </sheetData>
@@ -18294,23 +18437,23 @@
       </c>
       <c r="B2" s="8" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="C2" s="8" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
       <c r="D2" s="8" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="E2" s="8" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="F2" s="8" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="G2" s="8" cm="1">
         <f t="array" aca="1" ref="G2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18318,7 +18461,7 @@
       </c>
       <c r="H2" s="8" cm="1">
         <f t="array" aca="1" ref="H2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.636363636363637</v>
+        <v>18.727272727272727</v>
       </c>
       <c r="I2" s="8" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18366,7 +18509,7 @@
       </c>
       <c r="T2" s="8" cm="1">
         <f t="array" aca="1" ref="T2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="U2" s="8" cm="1">
         <f t="array" aca="1" ref="U2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18395,7 +18538,7 @@
       </c>
       <c r="E3" s="8" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="F3" s="8" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18439,7 +18582,7 @@
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18447,15 +18590,15 @@
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T3" s="8" cm="1">
         <f t="array" aca="1" ref="T3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U3" s="8" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18508,15 +18651,15 @@
       </c>
       <c r="K4" s="5" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
       <c r="L4" s="5" cm="1">
         <f t="array" aca="1" ref="L4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="M4" s="5" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="N4" s="5" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18540,7 +18683,7 @@
       </c>
       <c r="S4" s="5" cm="1">
         <f t="array" aca="1" ref="S4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="T4" s="5" cm="1">
         <f t="array" aca="1" ref="T4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18650,79 +18793,79 @@
       </c>
       <c r="B6" s="5" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="C6" s="5" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.272727272727273</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="E6" s="5" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="F6" s="5" cm="1">
         <f t="array" aca="1" ref="F6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>21</v>
       </c>
       <c r="G6" s="5" cm="1">
         <f t="array" aca="1" ref="G6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="H6" s="5" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="I6" s="5" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="J6" s="5" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="K6" s="5" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="L6" s="5" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="M6" s="5" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="N6" s="5" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="O6" s="5" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P6" s="5" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="5" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="R6" s="5" cm="1">
         <f t="array" aca="1" ref="R6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="S6" s="5" cm="1">
         <f t="array" aca="1" ref="S6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="T6" s="5" cm="1">
         <f t="array" aca="1" ref="T6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="U6" s="5" cm="1">
         <f t="array" aca="1" ref="U6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -19628,7 +19771,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.474747474747474</v>
+        <v>19.497607655502396</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -19684,7 +19827,7 @@
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
@@ -19716,7 +19859,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -19772,7 +19915,7 @@
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
@@ -19804,7 +19947,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -19860,7 +20003,7 @@
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
@@ -19892,7 +20035,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -19951,7 +20094,7 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
@@ -19983,7 +20126,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -20042,7 +20185,7 @@
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
@@ -20074,7 +20217,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -20241,7 +20384,7 @@
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
@@ -20273,7 +20416,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>18.636363636363637</v>
+        <v>18.727272727272727</v>
       </c>
       <c r="P21" t="s">
         <v>1</v>
@@ -21458,8 +21601,93 @@
         <v>20.181818181818183</v>
       </c>
     </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" t="s">
+        <v>284</v>
+      </c>
+      <c r="D56" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" t="s">
+        <v>166</v>
+      </c>
+      <c r="J56" t="s">
+        <v>83</v>
+      </c>
+      <c r="K56" t="s">
+        <v>75</v>
+      </c>
+      <c r="L56" t="s">
+        <v>280</v>
+      </c>
+    </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N57" s="1"/>
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>24</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>19.363636363636363</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N60" s="1"/>
@@ -21491,7 +21719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -21504,7 +21732,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.176470588235297</v>
+        <v>20.090909090909093</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21824,7 +22052,7 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
@@ -21856,7 +22084,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -22969,7 +23197,7 @@
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
@@ -23001,7 +23229,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P45" t="s">
         <v>287</v>
@@ -23055,6 +23283,12 @@
       <c r="L47" t="s">
         <v>18</v>
       </c>
+      <c r="P47" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>38884</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -23105,16 +23339,22 @@
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>20</v>
       </c>
+      <c r="P48" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>39283</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
         <v>252</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
         <v>200</v>
@@ -23123,13 +23363,13 @@
         <v>253</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>254</v>
       </c>
       <c r="G50" t="s">
         <v>285</v>
       </c>
       <c r="H50" t="s">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="I50" t="s">
         <v>286</v>
@@ -23141,7 +23381,7 @@
         <v>287</v>
       </c>
       <c r="L50" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -23171,7 +23411,7 @@
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I51">
         <f t="shared" ca="1" si="16"/>
@@ -23187,11 +23427,187 @@
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>18.90909090909091</v>
+        <v>19.454545454545453</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" t="s">
+        <v>200</v>
+      </c>
+      <c r="E53" t="s">
+        <v>253</v>
+      </c>
+      <c r="F53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53" t="s">
+        <v>285</v>
+      </c>
+      <c r="H53" t="s">
+        <v>301</v>
+      </c>
+      <c r="I53" t="s">
+        <v>286</v>
+      </c>
+      <c r="J53" t="s">
+        <v>6</v>
+      </c>
+      <c r="K53" t="s">
+        <v>287</v>
+      </c>
+      <c r="L53" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>21</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>18</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>21</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>17</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C56" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" t="s">
+        <v>307</v>
+      </c>
+      <c r="F56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56" t="s">
+        <v>153</v>
+      </c>
+      <c r="H56" t="s">
+        <v>301</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s">
+        <v>6</v>
+      </c>
+      <c r="K56" t="s">
+        <v>287</v>
+      </c>
+      <c r="L56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>21</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -23205,7 +23621,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -23216,7 +23632,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.497326203208559</v>
+        <v>19.550505050505052</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24139,7 +24555,7 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
@@ -24179,7 +24595,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
       <c r="P30" t="s">
         <v>121</v>
@@ -24247,7 +24663,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
@@ -24287,7 +24703,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P33" t="s">
         <v>158</v>
@@ -24355,7 +24771,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -24395,7 +24811,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P36" t="s">
         <v>189</v>
@@ -24910,6 +25326,94 @@
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
         <v>19.636363636363637</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C53" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" t="s">
+        <v>158</v>
+      </c>
+      <c r="H53" t="s">
+        <v>212</v>
+      </c>
+      <c r="I53" t="s">
+        <v>305</v>
+      </c>
+      <c r="J53" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="E54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="F54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ca="1" si="17"/>
+        <v>22</v>
+      </c>
+      <c r="H54">
+        <f t="shared" ca="1" si="17"/>
+        <v>24</v>
+      </c>
+      <c r="I54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="J54">
+        <f t="shared" ca="1" si="17"/>
+        <v>20</v>
+      </c>
+      <c r="K54">
+        <f t="shared" ca="1" si="17"/>
+        <v>22</v>
+      </c>
+      <c r="L54">
+        <f t="shared" ca="1" si="17"/>
+        <v>19</v>
+      </c>
+      <c r="N54" s="1">
+        <f ca="1">AVERAGE(B54:M54)</f>
+        <v>20.181818181818183</v>
       </c>
     </row>
   </sheetData>
@@ -24921,13 +25425,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628DC590-5B70-45B7-BCD6-8ED432E7A1AF}">
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.961038961038959</v>
+        <v>21.004132231404956</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27009,6 +27516,95 @@
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
         <v>21.818181818181817</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>231</v>
+      </c>
+      <c r="E65" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" t="s">
+        <v>303</v>
+      </c>
+      <c r="G65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s">
+        <v>228</v>
+      </c>
+      <c r="I65" t="s">
+        <v>248</v>
+      </c>
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" t="s">
+        <v>272</v>
+      </c>
+      <c r="L65" t="s">
+        <v>288</v>
+      </c>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>36</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>28</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>21.90909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -27020,7 +27616,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -27030,7 +27626,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.732323232323235</v>
+        <v>20.909090909090907</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27086,11 +27682,11 @@
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
@@ -27118,7 +27714,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -27174,11 +27770,11 @@
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
@@ -27206,7 +27802,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>21.272727272727273</v>
+        <v>21.454545454545453</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -27262,11 +27858,11 @@
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
@@ -27294,7 +27890,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -27350,11 +27946,11 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
@@ -27382,7 +27978,7 @@
       </c>
       <c r="N12" s="1">
         <f t="shared" ref="N12" ca="1" si="4">AVERAGE(B12:M12)</f>
-        <v>21</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -27438,11 +28034,11 @@
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="5"/>
@@ -27470,7 +28066,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:L15)</f>
-        <v>20.818181818181817</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -27530,7 +28126,7 @@
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="6"/>
@@ -27558,7 +28154,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:L18)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P18" t="s">
         <v>9</v>
@@ -27641,11 +28237,11 @@
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="7"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="7"/>
@@ -27669,7 +28265,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:L21)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P21" t="s">
         <v>11</v>
@@ -27749,11 +28345,11 @@
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="8"/>
@@ -27777,7 +28373,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:L24)</f>
-        <v>20.454545454545453</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P24" t="s">
         <v>29</v>
@@ -27857,11 +28453,11 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="9"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="9"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="9"/>
@@ -27885,7 +28481,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:L27)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P27" t="s">
         <v>96</v>
@@ -27965,7 +28561,7 @@
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="10"/>
@@ -27993,7 +28589,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:L30)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P30" t="s">
         <v>171</v>
@@ -28073,11 +28669,11 @@
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="11"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="11"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="11"/>
@@ -28101,7 +28697,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:L33)</f>
-        <v>20.727272727272727</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P33" t="s">
         <v>177</v>
@@ -28181,7 +28777,7 @@
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="12"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="12"/>
@@ -28209,7 +28805,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:L36)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P36" t="s">
         <v>198</v>
@@ -28289,7 +28885,7 @@
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="13"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="13"/>
@@ -28317,7 +28913,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:L39)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P39" t="s">
         <v>20</v>
@@ -28397,7 +28993,7 @@
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="14"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="14"/>
@@ -28425,7 +29021,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:L42)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="P42" t="s">
         <v>251</v>
@@ -28505,7 +29101,7 @@
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="15"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="15"/>
@@ -28533,7 +29129,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:L45)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P45" t="s">
         <v>267</v>
@@ -28613,7 +29209,7 @@
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="16"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="16"/>
@@ -28629,7 +29225,7 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="16"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="16"/>
@@ -28641,7 +29237,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>21.09090909090909</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P48" t="s">
         <v>306</v>
@@ -28723,7 +29319,7 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="17"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="17"/>
@@ -28735,7 +29331,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -28795,7 +29391,7 @@
       </c>
       <c r="F54">
         <f t="shared" ca="1" si="18"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="18"/>
@@ -28811,7 +29407,7 @@
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="18"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="18"/>
@@ -28823,7 +29419,95 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:L54)</f>
+        <v>21.181818181818183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>266</v>
+      </c>
+      <c r="F56" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" t="s">
+        <v>176</v>
+      </c>
+      <c r="I56" t="s">
+        <v>96</v>
+      </c>
+      <c r="J56" t="s">
+        <v>12</v>
+      </c>
+      <c r="K56" t="s">
+        <v>251</v>
+      </c>
+      <c r="L56" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="19">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="19"/>
         <v>21</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:L57)</f>
+        <v>21.454545454545453</v>
       </c>
     </row>
   </sheetData>
@@ -28849,7 +29533,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.519480519480517</v>
+        <v>19.495867768595041</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -30871,16 +31555,98 @@
       </c>
       <c r="O63" s="1"/>
     </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N65"/>
-    </row>
-    <row r="68" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N68"/>
-    </row>
-    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E65" t="s">
+        <v>54</v>
+      </c>
+      <c r="F65" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" t="s">
+        <v>290</v>
+      </c>
+      <c r="H65" t="s">
+        <v>233</v>
+      </c>
+      <c r="I65" t="s">
+        <v>203</v>
+      </c>
+      <c r="J65" t="s">
+        <v>163</v>
+      </c>
+      <c r="K65" t="s">
+        <v>44</v>
+      </c>
+      <c r="L65" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N71"/>
     </row>
-    <row r="74" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N74"/>
     </row>
   </sheetData>
@@ -30905,7 +31671,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.437229437229433</v>
+        <v>19.425619834710741</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -32994,22 +33760,105 @@
         <v>19.181818181818183</v>
       </c>
     </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" t="s">
+        <v>225</v>
+      </c>
+      <c r="C65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D65" t="s">
+        <v>214</v>
+      </c>
+      <c r="E65" t="s">
+        <v>101</v>
+      </c>
+      <c r="F65" t="s">
+        <v>291</v>
+      </c>
+      <c r="G65" t="s">
+        <v>217</v>
+      </c>
+      <c r="H65" t="s">
+        <v>62</v>
+      </c>
+      <c r="I65" t="s">
+        <v>64</v>
+      </c>
+      <c r="J65" t="s">
+        <v>147</v>
+      </c>
+      <c r="K65" t="s">
+        <v>274</v>
+      </c>
+      <c r="L65" t="s">
+        <v>61</v>
+      </c>
       <c r="N65" s="1"/>
     </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N66" s="1"/>
-    </row>
-    <row r="68" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:L66)</f>
+        <v>19.181818181818183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N68" s="1"/>
     </row>
-    <row r="69" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N69" s="1"/>
     </row>
-    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N71" s="1"/>
     </row>
-    <row r="72" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N72" s="1"/>
     </row>
   </sheetData>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6287" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2C6164-295C-4DBD-A54B-BCF59616C2EA}"/>
+  <xr:revisionPtr revIDLastSave="6313" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94477392-7B17-4EAB-AF50-D12778FED65B}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="313">
   <si>
     <t>Scholl</t>
   </si>
@@ -316,9 +316,6 @@
   </si>
   <si>
     <t>Balabas</t>
-  </si>
-  <si>
-    <t>Boguo</t>
   </si>
   <si>
     <t>Zotz</t>
@@ -1001,6 +998,18 @@
   <si>
     <t>Peinhart</t>
   </si>
+  <si>
+    <t>Coulibaly</t>
+  </si>
+  <si>
+    <t>Adeshina</t>
+  </si>
+  <si>
+    <t>Bogou</t>
+  </si>
+  <si>
+    <t>Scherzer</t>
+  </si>
 </sst>
 </file>
 
@@ -1278,6 +1287,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1599,6 +1611,9 @@
                 <c:pt idx="18">
                   <c:v>19</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1853,31 +1868,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>19.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -1886,22 +1901,22 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
@@ -3167,10 +3182,10 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
@@ -3430,67 +3445,67 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>20</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
+                  <c:v>21.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
                   <c:v>21.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>21.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="0.00">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0.00">
+                <c:pt idx="56" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="30" formatCode="0.00">
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3757,31 +3772,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>19.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -3790,22 +3805,22 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
@@ -4141,10 +4156,10 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>19.181818181818183</c:v>
@@ -4426,67 +4441,67 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>20</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
+                  <c:v>21.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
                   <c:v>21.181818181818183</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>21.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="0.00">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>20.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="0.00">
+                <c:pt idx="56" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="30" formatCode="0.00">
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>21.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="0.00">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>20.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4817,6 +4832,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16046,7 +16064,7 @@
         <v>71</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -16055,7 +16073,7 @@
       </c>
       <c r="B2" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>19.425619834710741</v>
+        <v>19.43388429752066</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -16068,21 +16086,21 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5">
+        <f ca="1">'Altach Juniors'!N1</f>
+        <v>19.621212121212125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B5" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.497607655502396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5">
-        <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.550505050505052</v>
+        <v>19.622727272727275</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16091,7 +16109,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.090909090909093</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -16100,7 +16118,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.752066115702483</v>
+        <v>20.855371900826448</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -16155,7 +16173,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.752066115702483</v>
+        <v>20.855371900826448</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -16169,7 +16187,7 @@
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -16249,19 +16267,19 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s">
         <v>69</v>
@@ -16276,7 +16294,7 @@
         <v>65</v>
       </c>
       <c r="J5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K5" t="s">
         <v>74</v>
@@ -16289,7 +16307,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <f ca="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16333,7 +16351,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -16341,19 +16359,19 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G8" t="s">
         <v>57</v>
@@ -16365,7 +16383,7 @@
         <v>65</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K8" t="s">
         <v>74</v>
@@ -16378,7 +16396,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <f ca="1">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16422,7 +16440,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -16430,13 +16448,13 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -16448,13 +16466,13 @@
         <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I11" t="s">
         <v>65</v>
       </c>
       <c r="J11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K11" t="s">
         <v>74</v>
@@ -16467,7 +16485,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <f ca="1">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16511,24 +16529,24 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
@@ -16537,16 +16555,16 @@
         <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I14" t="s">
         <v>76</v>
       </c>
       <c r="J14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14" t="s">
         <v>185</v>
-      </c>
-      <c r="K14" t="s">
-        <v>186</v>
       </c>
       <c r="L14" t="s">
         <v>70</v>
@@ -16556,7 +16574,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <f ca="1">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16580,7 +16598,7 @@
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
@@ -16600,7 +16618,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -16608,16 +16626,16 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
         <v>68</v>
@@ -16626,16 +16644,16 @@
         <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I17" t="s">
         <v>76</v>
       </c>
       <c r="J17" t="s">
+        <v>200</v>
+      </c>
+      <c r="K17" t="s">
         <v>201</v>
-      </c>
-      <c r="K17" t="s">
-        <v>202</v>
       </c>
       <c r="L17" t="s">
         <v>70</v>
@@ -16645,7 +16663,7 @@
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
         <f ca="1">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16689,7 +16707,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P18" t="s">
         <v>67</v>
@@ -16714,10 +16732,10 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -16732,23 +16750,23 @@
         <v>74</v>
       </c>
       <c r="H20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J20" t="s">
         <v>66</v>
       </c>
       <c r="K20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s">
         <v>70</v>
       </c>
       <c r="N20" s="1"/>
       <c r="P20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q20" s="6">
         <v>36322</v>
@@ -16757,7 +16775,7 @@
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
         <f ca="1">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16801,7 +16819,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P21" t="s">
         <v>57</v>
@@ -16823,10 +16841,10 @@
         <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -16838,10 +16856,10 @@
         <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I23" t="s">
         <v>76</v>
@@ -16850,10 +16868,10 @@
         <v>66</v>
       </c>
       <c r="K23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N23" s="1"/>
       <c r="P23" t="s">
@@ -16866,7 +16884,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
         <f ca="1">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -16910,7 +16928,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P24" t="s">
         <v>76</v>
@@ -16932,10 +16950,10 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -16947,10 +16965,10 @@
         <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I26" t="s">
         <v>74</v>
@@ -16959,10 +16977,10 @@
         <v>66</v>
       </c>
       <c r="K26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N26" s="1"/>
       <c r="P26" t="s">
@@ -16975,7 +16993,7 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
         <f ca="1">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17019,7 +17037,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>21.545454545454547</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="P27" t="s">
         <v>70</v>
@@ -17038,13 +17056,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -17059,7 +17077,7 @@
         <v>76</v>
       </c>
       <c r="H29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I29" t="s">
         <v>57</v>
@@ -17068,14 +17086,14 @@
         <v>66</v>
       </c>
       <c r="K29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N29" s="1"/>
       <c r="P29" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="6">
         <v>39243</v>
@@ -17084,7 +17102,7 @@
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30">
         <f ca="1">DATEDIF(VLOOKUP(B29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17128,10 +17146,10 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6">
         <v>36567</v>
@@ -17139,7 +17157,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="6">
         <v>38803</v>
@@ -17147,13 +17165,13 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -17162,13 +17180,13 @@
         <v>74</v>
       </c>
       <c r="F32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G32" t="s">
         <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
         <v>57</v>
@@ -17177,14 +17195,14 @@
         <v>66</v>
       </c>
       <c r="K32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N32" s="1"/>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q32" s="6">
         <v>39050</v>
@@ -17193,7 +17211,7 @@
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
         <f ca="1">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17209,7 +17227,7 @@
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
@@ -17237,10 +17255,10 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q33" s="6">
         <v>38469</v>
@@ -17248,7 +17266,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q34" s="6">
         <v>38419</v>
@@ -17259,10 +17277,10 @@
         <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -17271,13 +17289,13 @@
         <v>74</v>
       </c>
       <c r="F35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
         <v>57</v>
@@ -17286,14 +17304,14 @@
         <v>66</v>
       </c>
       <c r="K35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N35" s="1"/>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q35" s="6">
         <v>38919</v>
@@ -17302,7 +17320,7 @@
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
         <f ca="1">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17318,7 +17336,7 @@
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G36">
         <f t="shared" ca="1" si="11"/>
@@ -17346,10 +17364,10 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q36" s="6">
         <v>38799</v>
@@ -17357,7 +17375,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q37" s="6">
         <v>39609</v>
@@ -17365,13 +17383,13 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -17380,10 +17398,10 @@
         <v>74</v>
       </c>
       <c r="F38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H38" t="s">
         <v>70</v>
@@ -17395,14 +17413,14 @@
         <v>66</v>
       </c>
       <c r="K38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N38" s="1"/>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q38" s="6">
         <v>36322</v>
@@ -17427,7 +17445,7 @@
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
@@ -17455,10 +17473,10 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="P39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q39" s="6">
         <v>38783</v>
@@ -17466,7 +17484,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q40" s="6">
         <v>36576</v>
@@ -17474,13 +17492,13 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -17489,29 +17507,29 @@
         <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H41" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J41" t="s">
         <v>66</v>
       </c>
       <c r="K41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N41" s="1"/>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q41" s="6">
         <v>39206</v>
@@ -17536,7 +17554,7 @@
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42">
         <f t="shared" ca="1" si="13"/>
@@ -17564,10 +17582,10 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21.727272727272727</v>
+        <v>21.818181818181817</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q42" s="6">
         <v>37995</v>
@@ -17575,7 +17593,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q43" s="6">
         <v>36554</v>
@@ -17583,13 +17601,13 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -17598,29 +17616,29 @@
         <v>74</v>
       </c>
       <c r="F44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J44" t="s">
         <v>66</v>
       </c>
       <c r="K44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N44" s="1"/>
       <c r="P44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q44" s="6">
         <v>38239</v>
@@ -17645,7 +17663,7 @@
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45">
         <f t="shared" ca="1" si="14"/>
@@ -17673,10 +17691,10 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q45" s="6">
         <v>39164</v>
@@ -17684,7 +17702,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q46" s="6">
         <v>39069</v>
@@ -17695,10 +17713,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -17707,29 +17725,29 @@
         <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H47" t="s">
         <v>57</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J47" t="s">
         <v>66</v>
       </c>
       <c r="K47" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N47" s="1"/>
       <c r="P47" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q47" s="6">
         <v>38722</v>
@@ -17754,7 +17772,7 @@
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48">
         <f t="shared" ca="1" si="15"/>
@@ -17782,10 +17800,10 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q48" s="6">
         <v>39860</v>
@@ -17796,37 +17814,37 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E50" t="s">
         <v>74</v>
       </c>
       <c r="F50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J50" t="s">
         <v>66</v>
       </c>
       <c r="K50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N50" s="1"/>
     </row>
@@ -17849,7 +17867,7 @@
       </c>
       <c r="F51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51">
         <f t="shared" ca="1" si="16"/>
@@ -17877,18 +17895,18 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B53" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -17897,32 +17915,32 @@
         <v>74</v>
       </c>
       <c r="F53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H53" t="s">
         <v>57</v>
       </c>
       <c r="I53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J53" t="s">
         <v>66</v>
       </c>
       <c r="K53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54">
         <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -17938,7 +17956,7 @@
       </c>
       <c r="F54">
         <f t="shared" ca="1" si="17"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="17"/>
@@ -17966,18 +17984,18 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -17989,29 +18007,29 @@
         <v>65</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H56" t="s">
         <v>57</v>
       </c>
       <c r="I56" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J56" t="s">
         <v>66</v>
       </c>
       <c r="K56" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -18055,7 +18073,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -18063,10 +18081,10 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -18075,32 +18093,32 @@
         <v>74</v>
       </c>
       <c r="F59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G59" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
         <v>57</v>
       </c>
       <c r="I59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J59" t="s">
         <v>66</v>
       </c>
       <c r="K59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60">
         <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -18144,7 +18162,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -18152,10 +18170,10 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -18167,29 +18185,29 @@
         <v>65</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H62" t="s">
         <v>57</v>
       </c>
       <c r="I62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J62" t="s">
         <v>66</v>
       </c>
       <c r="K62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B63">
         <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -18233,7 +18251,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -18241,10 +18259,10 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -18256,29 +18274,29 @@
         <v>65</v>
       </c>
       <c r="G65" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H65" t="s">
         <v>57</v>
       </c>
       <c r="I65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J65" t="s">
         <v>66</v>
       </c>
       <c r="K65" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B66">
         <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C66">
         <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -18322,7 +18340,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -18368,67 +18386,67 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="V1" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -18513,7 +18531,7 @@
       </c>
       <c r="U2" s="8" cm="1">
         <f t="array" aca="1" ref="U2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V2" s="8" cm="1">
         <f t="array" aca="1" ref="V2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18602,7 +18620,7 @@
       </c>
       <c r="U3" s="8" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="V3" s="8" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18611,27 +18629,27 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
       <c r="C4" s="5" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18639,15 +18657,15 @@
       </c>
       <c r="H4" s="5" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="I4" s="5" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="J4" s="5" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="K4" s="5" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18659,27 +18677,27 @@
       </c>
       <c r="M4" s="5" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="N4" s="5" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="O4" s="5" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="P4" s="5" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="Q4" s="5" cm="1">
         <f t="array" aca="1" ref="Q4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="R4" s="5" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="S4" s="5" cm="1">
         <f t="array" aca="1" ref="S4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19047,11 +19065,11 @@
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -19064,83 +19082,83 @@
       </c>
       <c r="C9" s="5" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="D9" s="5" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="E9" s="5" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="F9" s="5" cm="1">
         <f t="array" aca="1" ref="F9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="G9" s="5" cm="1">
         <f t="array" aca="1" ref="G9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="H9" s="5" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="I9" s="5" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="J9" s="5" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.545454545454547</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="K9" s="5" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="L9" s="5" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="M9" s="5" cm="1">
         <f t="array" aca="1" ref="M9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="N9" s="5" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="O9" s="5" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.727272727272727</v>
+        <v>21.818181818181817</v>
       </c>
       <c r="P9" s="5" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="Q9" s="5" cm="1">
         <f t="array" aca="1" ref="Q9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="R9" s="5" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="S9" s="5" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="T9" s="5" cm="1">
         <f t="array" aca="1" ref="T9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="U9" s="5" cm="1">
         <f t="array" aca="1" ref="U9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="V9" s="5" cm="1">
         <f t="array" aca="1" ref="V9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -19771,7 +19789,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.497607655502396</v>
+        <v>19.622727272727275</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -19797,16 +19815,16 @@
         <v>81</v>
       </c>
       <c r="H2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2" t="s">
         <v>82</v>
-      </c>
-      <c r="I2" t="s">
-        <v>83</v>
       </c>
       <c r="J2" t="s">
         <v>77</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s">
         <v>2</v>
@@ -19864,10 +19882,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
@@ -19882,19 +19900,19 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" t="s">
         <v>107</v>
       </c>
-      <c r="H5" t="s">
-        <v>108</v>
-      </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s">
         <v>77</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
         <v>2</v>
@@ -19970,19 +19988,19 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H8" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
         <v>77</v>
       </c>
       <c r="K8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L8" t="s">
         <v>2</v>
@@ -20043,10 +20061,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
         <v>75</v>
@@ -20061,10 +20079,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
         <v>81</v>
@@ -20073,7 +20091,7 @@
         <v>77</v>
       </c>
       <c r="K11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L11" t="s">
         <v>2</v>
@@ -20155,16 +20173,16 @@
         <v>81</v>
       </c>
       <c r="H14" t="s">
+        <v>311</v>
+      </c>
+      <c r="I14" t="s">
         <v>82</v>
-      </c>
-      <c r="I14" t="s">
-        <v>83</v>
       </c>
       <c r="J14" t="s">
         <v>77</v>
       </c>
       <c r="K14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s">
         <v>2</v>
@@ -20222,10 +20240,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
         <v>75</v>
@@ -20234,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -20243,16 +20261,16 @@
         <v>81</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="I17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J17" t="s">
         <v>77</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s">
         <v>2</v>
@@ -20327,10 +20345,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
         <v>75</v>
@@ -20342,7 +20360,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G20" t="s">
         <v>0</v>
@@ -20351,16 +20369,16 @@
         <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P20" t="s">
         <v>80</v>
@@ -20435,7 +20453,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -20450,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" t="s">
         <v>0</v>
@@ -20459,16 +20477,16 @@
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23" t="s">
+        <v>82</v>
+      </c>
+      <c r="K23" t="s">
         <v>83</v>
       </c>
-      <c r="K23" t="s">
-        <v>84</v>
-      </c>
       <c r="L23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P23" t="s">
         <v>81</v>
@@ -20535,7 +20553,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="6">
         <v>39266</v>
@@ -20543,10 +20561,10 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
         <v>75</v>
@@ -20558,7 +20576,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G26" t="s">
         <v>0</v>
@@ -20567,19 +20585,19 @@
         <v>2</v>
       </c>
       <c r="I26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J26" t="s">
+        <v>82</v>
+      </c>
+      <c r="K26" t="s">
         <v>83</v>
       </c>
-      <c r="K26" t="s">
-        <v>84</v>
-      </c>
       <c r="L26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P26" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="Q26" s="6">
         <v>39372</v>
@@ -20635,7 +20653,7 @@
         <v>18.727272727272727</v>
       </c>
       <c r="P27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="6">
         <v>38668</v>
@@ -20651,7 +20669,7 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -20666,7 +20684,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G29" t="s">
         <v>0</v>
@@ -20675,19 +20693,19 @@
         <v>2</v>
       </c>
       <c r="I29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K29" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="L29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="6">
         <v>39664</v>
@@ -20743,7 +20761,7 @@
         <v>19.636363636363637</v>
       </c>
       <c r="P30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q30" s="6">
         <v>39653</v>
@@ -20751,7 +20769,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q31" s="6">
         <v>39418</v>
@@ -20759,7 +20777,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -20771,10 +20789,10 @@
         <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
@@ -20783,19 +20801,19 @@
         <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J32" t="s">
         <v>77</v>
       </c>
       <c r="K32" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q32" s="6">
         <v>38272</v>
@@ -20851,7 +20869,7 @@
         <v>19.363636363636363</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q33" s="6">
         <v>38665</v>
@@ -20859,7 +20877,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q34" s="6">
         <v>33804</v>
@@ -20867,7 +20885,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -20879,10 +20897,10 @@
         <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G35" t="s">
         <v>0</v>
@@ -20891,19 +20909,19 @@
         <v>2</v>
       </c>
       <c r="I35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K35" t="s">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q35" s="6">
         <v>39356</v>
@@ -20959,7 +20977,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q36" s="6">
         <v>39361</v>
@@ -20967,7 +20985,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q37" s="6">
         <v>38982</v>
@@ -20975,7 +20993,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
@@ -20987,10 +21005,10 @@
         <v>81</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G38" t="s">
         <v>0</v>
@@ -20999,19 +21017,19 @@
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J38" t="s">
+        <v>82</v>
+      </c>
+      <c r="K38" t="s">
         <v>83</v>
       </c>
-      <c r="K38" t="s">
-        <v>84</v>
-      </c>
       <c r="L38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q38" s="6">
         <v>38539</v>
@@ -21067,7 +21085,7 @@
         <v>18.818181818181817</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q39" s="6">
         <v>38932</v>
@@ -21083,7 +21101,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -21095,10 +21113,10 @@
         <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G41" t="s">
         <v>0</v>
@@ -21107,19 +21125,19 @@
         <v>2</v>
       </c>
       <c r="I41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q41" s="6">
         <v>39424</v>
@@ -21175,7 +21193,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q42" s="6">
         <v>39739</v>
@@ -21183,7 +21201,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q43" s="6">
         <v>39667</v>
@@ -21191,10 +21209,10 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
         <v>75</v>
@@ -21203,10 +21221,10 @@
         <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G44" t="s">
         <v>0</v>
@@ -21218,16 +21236,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q44" s="6">
         <v>37496</v>
@@ -21283,7 +21301,7 @@
         <v>18.545454545454547</v>
       </c>
       <c r="P45" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q45" s="6">
         <v>37129</v>
@@ -21291,7 +21309,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q46" s="6">
         <v>37139</v>
@@ -21302,7 +21320,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C47" t="s">
         <v>75</v>
@@ -21311,7 +21329,7 @@
         <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F47" t="s">
         <v>1</v>
@@ -21320,22 +21338,22 @@
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I47" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s">
+        <v>279</v>
+      </c>
+      <c r="P47" t="s">
         <v>280</v>
-      </c>
-      <c r="P47" t="s">
-        <v>281</v>
       </c>
       <c r="Q47" s="6">
         <v>39613</v>
@@ -21391,7 +21409,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q48" s="6">
         <v>39468</v>
@@ -21399,7 +21417,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P49" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q49" s="6">
         <v>38486</v>
@@ -21407,19 +21425,19 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B50" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" t="s">
         <v>1</v>
@@ -21431,19 +21449,19 @@
         <v>2</v>
       </c>
       <c r="I50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q50" s="6">
         <v>38422</v>
@@ -21499,7 +21517,7 @@
         <v>19.727272727272727</v>
       </c>
       <c r="P51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q51" s="6">
         <v>38384</v>
@@ -21507,7 +21525,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q52" s="6">
         <v>38569</v>
@@ -21518,16 +21536,16 @@
         <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
         <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F53" t="s">
         <v>1</v>
@@ -21539,16 +21557,22 @@
         <v>2</v>
       </c>
       <c r="I53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s">
         <v>75</v>
       </c>
       <c r="L53" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+      <c r="P53" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>34902</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
@@ -21603,19 +21627,19 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C56" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D56" t="s">
         <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F56" t="s">
         <v>1</v>
@@ -21627,16 +21651,16 @@
         <v>2</v>
       </c>
       <c r="I56" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s">
         <v>75</v>
       </c>
       <c r="L56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
@@ -21689,8 +21713,93 @@
         <v>19.363636363636363</v>
       </c>
     </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" t="s">
+        <v>283</v>
+      </c>
+      <c r="D59" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" t="s">
+        <v>312</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" t="s">
+        <v>311</v>
+      </c>
+      <c r="J59" t="s">
+        <v>82</v>
+      </c>
+      <c r="K59" t="s">
+        <v>160</v>
+      </c>
+      <c r="L59" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N60" s="1"/>
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>30</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>33</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>24</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N63" s="1"/>
@@ -21719,7 +21828,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -21732,7 +21841,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.090909090909093</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21740,7 +21849,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -21755,7 +21864,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -21767,7 +21876,7 @@
         <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L2" t="s">
         <v>18</v>
@@ -21825,10 +21934,10 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -21840,10 +21949,10 @@
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -21855,10 +21964,10 @@
         <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -21913,10 +22022,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -21928,22 +22037,22 @@
         <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
       </c>
       <c r="I8" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" t="s">
         <v>152</v>
       </c>
-      <c r="J8" t="s">
-        <v>153</v>
-      </c>
       <c r="K8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s">
         <v>18</v>
@@ -22001,10 +22110,10 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
@@ -22013,25 +22122,25 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L11" t="s">
         <v>18</v>
@@ -22089,10 +22198,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -22107,19 +22216,19 @@
         <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L14" t="s">
         <v>18</v>
@@ -22177,10 +22286,10 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -22192,10 +22301,10 @@
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -22204,10 +22313,10 @@
         <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L17" t="s">
         <v>18</v>
@@ -22265,7 +22374,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="6">
         <v>38475</v>
@@ -22276,10 +22385,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -22291,10 +22400,10 @@
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -22303,13 +22412,13 @@
         <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P20" t="s">
         <v>6</v>
@@ -22384,10 +22493,10 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
@@ -22399,10 +22508,10 @@
         <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -22411,10 +22520,10 @@
         <v>35</v>
       </c>
       <c r="J23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L23" t="s">
         <v>18</v>
@@ -22476,7 +22585,7 @@
         <v>20.363636363636363</v>
       </c>
       <c r="P24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q24" s="6">
         <v>37276</v>
@@ -22492,10 +22601,10 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
@@ -22507,10 +22616,10 @@
         <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -22519,10 +22628,10 @@
         <v>35</v>
       </c>
       <c r="J26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L26" t="s">
         <v>18</v>
@@ -22592,7 +22701,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q28" s="6">
         <v>38916</v>
@@ -22600,10 +22709,10 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
         <v>6</v>
@@ -22615,10 +22724,10 @@
         <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -22627,10 +22736,10 @@
         <v>35</v>
       </c>
       <c r="J29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L29" t="s">
         <v>18</v>
@@ -22692,7 +22801,7 @@
         <v>20.545454545454547</v>
       </c>
       <c r="P30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q30" s="6">
         <v>38335</v>
@@ -22700,7 +22809,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q31" s="6">
         <v>37927</v>
@@ -22708,10 +22817,10 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s">
         <v>85</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
@@ -22723,10 +22832,10 @@
         <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -22735,16 +22844,16 @@
         <v>35</v>
       </c>
       <c r="J32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L32" t="s">
         <v>18</v>
       </c>
       <c r="P32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q32" s="6">
         <v>38512</v>
@@ -22800,7 +22909,7 @@
         <v>20.363636363636363</v>
       </c>
       <c r="P33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q33" s="6">
         <v>38513</v>
@@ -22808,7 +22917,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q34" s="6">
         <v>38448</v>
@@ -22819,22 +22928,22 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -22843,16 +22952,16 @@
         <v>35</v>
       </c>
       <c r="J35" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L35" t="s">
         <v>37</v>
       </c>
       <c r="P35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q35" s="6">
         <v>39162</v>
@@ -22908,7 +23017,7 @@
         <v>20.181818181818183</v>
       </c>
       <c r="P36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q36" s="6">
         <v>39597</v>
@@ -22916,7 +23025,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q37" s="6">
         <v>39178</v>
@@ -22924,10 +23033,10 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
@@ -22939,28 +23048,28 @@
         <v>36</v>
       </c>
       <c r="F38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J38" t="s">
         <v>18</v>
       </c>
       <c r="K38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L38" t="s">
         <v>37</v>
       </c>
       <c r="P38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q38" s="6">
         <v>38410</v>
@@ -23016,7 +23125,7 @@
         <v>20.181818181818183</v>
       </c>
       <c r="P39" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q39" s="6">
         <v>39226</v>
@@ -23024,7 +23133,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q40" s="6">
         <v>38395</v>
@@ -23035,40 +23144,40 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E41" t="s">
         <v>36</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L41" t="s">
         <v>37</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q41" s="6">
         <v>38718</v>
@@ -23124,7 +23233,7 @@
         <v>20.09090909090909</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q42" s="6">
         <v>38062</v>
@@ -23132,7 +23241,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q43" s="6">
         <v>39118</v>
@@ -23140,25 +23249,25 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" t="s">
+        <v>264</v>
+      </c>
+      <c r="F44" t="s">
         <v>86</v>
       </c>
-      <c r="C44" t="s">
-        <v>254</v>
-      </c>
-      <c r="D44" t="s">
-        <v>200</v>
-      </c>
-      <c r="E44" t="s">
-        <v>265</v>
-      </c>
-      <c r="F44" t="s">
-        <v>87</v>
-      </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -23170,13 +23279,13 @@
         <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L44" t="s">
         <v>37</v>
       </c>
       <c r="P44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q44" s="6">
         <v>39260</v>
@@ -23232,7 +23341,7 @@
         <v>20.272727272727273</v>
       </c>
       <c r="P45" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q45" s="6">
         <v>39689</v>
@@ -23240,7 +23349,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q46" s="6">
         <v>39524</v>
@@ -23251,40 +23360,40 @@
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
         <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s">
+        <v>284</v>
+      </c>
+      <c r="H47" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" t="s">
         <v>285</v>
-      </c>
-      <c r="H47" t="s">
-        <v>104</v>
-      </c>
-      <c r="I47" t="s">
-        <v>286</v>
       </c>
       <c r="J47" t="s">
         <v>6</v>
       </c>
       <c r="K47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L47" t="s">
         <v>18</v>
       </c>
       <c r="P47" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q47" s="6">
         <v>38884</v>
@@ -23340,51 +23449,65 @@
         <v>20</v>
       </c>
       <c r="P48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q48" s="6">
         <v>39283</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>36885</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C50" t="s">
         <v>35</v>
       </c>
       <c r="D50" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E50" t="s">
+        <v>252</v>
+      </c>
+      <c r="F50" t="s">
         <v>253</v>
       </c>
-      <c r="F50" t="s">
-        <v>254</v>
-      </c>
       <c r="G50" t="s">
+        <v>284</v>
+      </c>
+      <c r="H50" t="s">
+        <v>103</v>
+      </c>
+      <c r="I50" t="s">
         <v>285</v>
-      </c>
-      <c r="H50" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" t="s">
-        <v>286</v>
       </c>
       <c r="J50" t="s">
         <v>6</v>
       </c>
       <c r="K50" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L50" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>38323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>18</v>
@@ -23434,45 +23557,45 @@
         <v>19.454545454545453</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C53" t="s">
         <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E53" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F53" t="s">
         <v>36</v>
       </c>
       <c r="G53" t="s">
+        <v>284</v>
+      </c>
+      <c r="H53" t="s">
+        <v>300</v>
+      </c>
+      <c r="I53" t="s">
         <v>285</v>
-      </c>
-      <c r="H53" t="s">
-        <v>301</v>
-      </c>
-      <c r="I53" t="s">
-        <v>286</v>
       </c>
       <c r="J53" t="s">
         <v>6</v>
       </c>
       <c r="K53" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L53" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>18</v>
@@ -23522,30 +23645,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C56" t="s">
         <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E56" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F56" t="s">
         <v>36</v>
       </c>
       <c r="G56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
@@ -23554,13 +23677,13 @@
         <v>6</v>
       </c>
       <c r="K56" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L56" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>18</v>
@@ -23608,6 +23731,94 @@
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
         <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>251</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" t="s">
+        <v>306</v>
+      </c>
+      <c r="F59" t="s">
+        <v>284</v>
+      </c>
+      <c r="G59" t="s">
+        <v>152</v>
+      </c>
+      <c r="H59" t="s">
+        <v>309</v>
+      </c>
+      <c r="I59" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s">
+        <v>6</v>
+      </c>
+      <c r="K59" t="s">
+        <v>310</v>
+      </c>
+      <c r="L59" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>25</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>21</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
+        <v>20.09090909090909</v>
       </c>
     </row>
   </sheetData>
@@ -23632,7 +23843,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.550505050505052</v>
+        <v>19.621212121212125</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -23646,28 +23857,28 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
         <v>89</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
         <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>91</v>
       </c>
       <c r="H2" t="s">
         <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L2" t="s">
         <v>30</v>
@@ -23680,7 +23891,7 @@
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <f t="shared" ca="1" si="0"/>
@@ -23720,12 +23931,12 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -23734,28 +23945,28 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" t="s">
         <v>121</v>
       </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>91</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
-        <v>92</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L5" t="s">
         <v>30</v>
@@ -23768,7 +23979,7 @@
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="1"/>
@@ -23808,12 +24019,12 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -23822,31 +24033,31 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
         <v>89</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
         <v>90</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" t="s">
         <v>91</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>157</v>
-      </c>
-      <c r="I8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J8" t="s">
-        <v>158</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -23856,7 +24067,7 @@
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
@@ -23896,12 +24107,12 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -23913,22 +24124,22 @@
         <v>30</v>
       </c>
       <c r="E11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>90</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" t="s">
         <v>91</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>157</v>
-      </c>
-      <c r="I11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" t="s">
-        <v>158</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
@@ -23944,7 +24155,7 @@
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="3"/>
@@ -23984,15 +24195,15 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" t="s">
         <v>187</v>
-      </c>
-      <c r="B14" t="s">
-        <v>188</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -24001,28 +24212,28 @@
         <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" t="s">
+        <v>188</v>
+      </c>
+      <c r="J14" t="s">
         <v>157</v>
-      </c>
-      <c r="I14" t="s">
-        <v>189</v>
-      </c>
-      <c r="J14" t="s">
-        <v>158</v>
       </c>
       <c r="K14" t="s">
         <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -24032,7 +24243,7 @@
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
@@ -24072,45 +24283,45 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" t="s">
         <v>208</v>
-      </c>
-      <c r="B17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C17" t="s">
-        <v>209</v>
       </c>
       <c r="D17" t="s">
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
       </c>
       <c r="L17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -24174,7 +24385,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="6">
         <v>39135</v>
@@ -24182,19 +24393,19 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -24203,19 +24414,19 @@
         <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P20" t="s">
         <v>13</v>
@@ -24231,7 +24442,7 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
@@ -24271,10 +24482,10 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="6">
         <v>38965</v>
@@ -24290,19 +24501,19 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
@@ -24311,22 +24522,22 @@
         <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
       </c>
       <c r="L23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="6">
         <v>39689</v>
@@ -24339,7 +24550,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
@@ -24379,10 +24590,10 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q24" s="6">
         <v>39460</v>
@@ -24398,43 +24609,43 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="6">
         <v>39654</v>
@@ -24447,7 +24658,7 @@
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
@@ -24487,7 +24698,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P27" t="s">
         <v>30</v>
@@ -24506,43 +24717,43 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" t="s">
         <v>234</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>235</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" t="s">
         <v>236</v>
       </c>
-      <c r="D29" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" t="s">
-        <v>89</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
+        <v>157</v>
+      </c>
+      <c r="J29" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" t="s">
         <v>237</v>
       </c>
-      <c r="I29" t="s">
-        <v>158</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
         <v>92</v>
       </c>
-      <c r="K29" t="s">
-        <v>238</v>
-      </c>
-      <c r="L29" t="s">
-        <v>93</v>
-      </c>
       <c r="P29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="6">
         <v>38152</v>
@@ -24598,7 +24809,7 @@
         <v>18.636363636363637</v>
       </c>
       <c r="P30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6">
         <v>38392</v>
@@ -24606,7 +24817,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="6">
         <v>37447</v>
@@ -24614,43 +24825,43 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
         <v>89</v>
       </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>90</v>
-      </c>
       <c r="H32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s">
         <v>30</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q32" s="6">
         <v>38790</v>
@@ -24706,7 +24917,7 @@
         <v>20.272727272727273</v>
       </c>
       <c r="P33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q33" s="6">
         <v>38012</v>
@@ -24714,7 +24925,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q34" s="6">
         <v>39085</v>
@@ -24722,16 +24933,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
         <v>21</v>
@@ -24740,25 +24951,25 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I35" t="s">
         <v>13</v>
       </c>
       <c r="J35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s">
         <v>30</v>
       </c>
       <c r="L35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q35" s="6">
         <v>38728</v>
@@ -24795,7 +25006,7 @@
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="11"/>
@@ -24811,10 +25022,10 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q36" s="6">
         <v>39538</v>
@@ -24822,7 +25033,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q37" s="6">
         <v>39427</v>
@@ -24830,16 +25041,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
         <v>21</v>
@@ -24848,25 +25059,25 @@
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I38" t="s">
         <v>13</v>
       </c>
       <c r="J38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K38" t="s">
         <v>30</v>
       </c>
       <c r="L38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q38" s="6">
         <v>39500</v>
@@ -24903,7 +25114,7 @@
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
@@ -24919,10 +25130,10 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q39" s="6">
         <v>37302</v>
@@ -24930,7 +25141,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q40" s="6">
         <v>38913</v>
@@ -24938,43 +25149,43 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>256</v>
+      </c>
+      <c r="B41" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" t="s">
         <v>257</v>
       </c>
-      <c r="B41" t="s">
-        <v>188</v>
-      </c>
-      <c r="C41" t="s">
-        <v>209</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s">
         <v>91</v>
-      </c>
-      <c r="E41" t="s">
-        <v>258</v>
-      </c>
-      <c r="F41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" t="s">
-        <v>90</v>
-      </c>
-      <c r="H41" t="s">
-        <v>92</v>
       </c>
       <c r="I41" t="s">
         <v>13</v>
       </c>
       <c r="J41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K41" t="s">
         <v>30</v>
       </c>
       <c r="L41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q41" s="6">
         <v>38795</v>
@@ -25011,7 +25222,7 @@
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="13"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
@@ -25027,10 +25238,10 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q42" s="6">
         <v>39771</v>
@@ -25038,7 +25249,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q43" s="6">
         <v>39339</v>
@@ -25046,28 +25257,28 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
       </c>
       <c r="E44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F44" t="s">
         <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I44" t="s">
         <v>13</v>
@@ -25079,10 +25290,10 @@
         <v>30</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q44" s="6">
         <v>37852</v>
@@ -25119,7 +25330,7 @@
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="14"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
@@ -25135,10 +25346,10 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q45" s="6">
         <v>38724</v>
@@ -25146,7 +25357,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q46" s="6">
         <v>37752</v>
@@ -25154,28 +25365,28 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
         <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F47" t="s">
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I47" t="s">
         <v>13</v>
@@ -25187,7 +25398,7 @@
         <v>30</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -25221,7 +25432,7 @@
       </c>
       <c r="I48">
         <f t="shared" ca="1" si="15"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="15"/>
@@ -25237,7 +25448,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -25245,10 +25456,10 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -25257,25 +25468,25 @@
         <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G50" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K50" t="s">
         <v>30</v>
       </c>
       <c r="L50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -25289,7 +25500,7 @@
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E51">
         <f t="shared" ca="1" si="16"/>
@@ -25325,36 +25536,36 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
         <v>89</v>
       </c>
-      <c r="E53" t="s">
-        <v>20</v>
-      </c>
-      <c r="F53" t="s">
-        <v>90</v>
-      </c>
       <c r="G53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I53" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J53" t="s">
         <v>21</v>
@@ -25363,7 +25574,7 @@
         <v>30</v>
       </c>
       <c r="L53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -25442,7 +25653,7 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -25451,7 +25662,7 @@
         <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -25531,19 +25742,19 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
@@ -25623,16 +25834,16 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>59</v>
@@ -25653,7 +25864,7 @@
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L8" t="s">
         <v>25</v>
@@ -25718,13 +25929,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>59</v>
@@ -25745,7 +25956,7 @@
         <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
@@ -25804,16 +26015,16 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
@@ -25822,7 +26033,7 @@
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" t="s">
         <v>31</v>
@@ -25834,7 +26045,7 @@
         <v>24</v>
       </c>
       <c r="K14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
@@ -25893,16 +26104,16 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>59</v>
@@ -25911,7 +26122,7 @@
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H17" t="s">
         <v>79</v>
@@ -25923,7 +26134,7 @@
         <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
@@ -25980,7 +26191,7 @@
         <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q18" s="6">
         <v>38482</v>
@@ -26002,13 +26213,13 @@
         <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E20" t="s">
         <v>59</v>
@@ -26017,7 +26228,7 @@
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H20" t="s">
         <v>79</v>
@@ -26036,7 +26247,7 @@
       </c>
       <c r="N20" s="1"/>
       <c r="P20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q20" s="6">
         <v>38620</v>
@@ -26111,13 +26322,13 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>59</v>
@@ -26138,7 +26349,7 @@
         <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
@@ -26220,19 +26431,19 @@
         <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
         <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G26" t="s">
         <v>26</v>
@@ -26247,7 +26458,7 @@
         <v>24</v>
       </c>
       <c r="K26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s">
         <v>22</v>
@@ -26326,16 +26537,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -26356,10 +26567,10 @@
         <v>24</v>
       </c>
       <c r="K29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N29" s="1"/>
       <c r="P29" t="s">
@@ -26419,7 +26630,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="6">
         <v>39031</v>
@@ -26435,44 +26646,44 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G32" t="s">
         <v>32</v>
       </c>
       <c r="H32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J32" t="s">
         <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N32" s="1"/>
       <c r="P32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q32" s="6">
         <v>38425</v>
@@ -26528,7 +26739,7 @@
         <v>21.181818181818183</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q33" s="6">
         <v>38324</v>
@@ -26536,7 +26747,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q34" s="6">
         <v>38653</v>
@@ -26547,19 +26758,19 @@
         <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
         <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G35" t="s">
         <v>24</v>
@@ -26568,20 +26779,20 @@
         <v>26</v>
       </c>
       <c r="I35" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J35" t="s">
         <v>25</v>
       </c>
       <c r="K35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N35" s="1"/>
       <c r="P35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q35" s="6">
         <v>37284</v>
@@ -26637,7 +26848,7 @@
         <v>21.09090909090909</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q36" s="6">
         <v>39501</v>
@@ -26645,7 +26856,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q37" s="6">
         <v>38783</v>
@@ -26653,22 +26864,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D38" t="s">
         <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G38" t="s">
         <v>24</v>
@@ -26677,7 +26888,7 @@
         <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J38" t="s">
         <v>25</v>
@@ -26686,11 +26897,11 @@
         <v>23</v>
       </c>
       <c r="L38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N38" s="1"/>
       <c r="P38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q38" s="6">
         <v>38520</v>
@@ -26746,7 +26957,7 @@
         <v>21.181818181818183</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q39" s="6">
         <v>38493</v>
@@ -26754,7 +26965,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q40" s="6">
         <v>39427</v>
@@ -26765,25 +26976,25 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
         <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
       </c>
       <c r="H41" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -26792,14 +27003,14 @@
         <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L41" t="s">
         <v>22</v>
       </c>
       <c r="N41" s="1"/>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q41" s="6">
         <v>38387</v>
@@ -26855,7 +27066,7 @@
         <v>21.272727272727273</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q42" s="6">
         <v>38599</v>
@@ -26863,7 +27074,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q43" s="6">
         <v>38364</v>
@@ -26871,28 +27082,28 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
         <v>24</v>
       </c>
       <c r="H44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -26901,14 +27112,14 @@
         <v>25</v>
       </c>
       <c r="K44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L44" t="s">
         <v>22</v>
       </c>
       <c r="N44" s="1"/>
       <c r="P44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q44" s="6">
         <v>39580</v>
@@ -26964,7 +27175,7 @@
         <v>21.272727272727273</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q45" s="6">
         <v>38999</v>
@@ -26972,7 +27183,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q46" s="6">
         <v>35610</v>
@@ -26983,25 +27194,25 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
       </c>
       <c r="E47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I47" t="s">
         <v>26</v>
@@ -27010,14 +27221,14 @@
         <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L47" t="s">
         <v>79</v>
       </c>
       <c r="N47" s="1"/>
       <c r="P47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q47" s="6">
         <v>37823</v>
@@ -27075,28 +27286,28 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I50" t="s">
         <v>26</v>
@@ -27105,10 +27316,10 @@
         <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L50" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N50" s="1"/>
     </row>
@@ -27164,10 +27375,10 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
@@ -27185,19 +27396,19 @@
         <v>79</v>
       </c>
       <c r="H53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J53" t="s">
         <v>25</v>
       </c>
       <c r="K53" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L53" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N53" s="1"/>
     </row>
@@ -27256,16 +27467,16 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F56" t="s">
         <v>38</v>
@@ -27274,19 +27485,19 @@
         <v>79</v>
       </c>
       <c r="H56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J56" t="s">
         <v>25</v>
       </c>
       <c r="K56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N56" s="1"/>
     </row>
@@ -27342,19 +27553,19 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
         <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F59" t="s">
         <v>38</v>
@@ -27363,19 +27574,19 @@
         <v>79</v>
       </c>
       <c r="H59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J59" t="s">
         <v>25</v>
       </c>
       <c r="K59" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N59" s="1"/>
     </row>
@@ -27431,40 +27642,40 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E62" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F62" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G62" t="s">
         <v>79</v>
       </c>
       <c r="H62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J62" t="s">
         <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L62" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N62" s="1"/>
     </row>
@@ -27523,37 +27734,37 @@
         <v>50</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
         <v>23</v>
       </c>
       <c r="D65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E65" t="s">
         <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G65" t="s">
         <v>79</v>
       </c>
       <c r="H65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J65" t="s">
         <v>25</v>
       </c>
       <c r="K65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N65" s="1"/>
     </row>
@@ -27661,10 +27872,10 @@
         <v>78</v>
       </c>
       <c r="K2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" t="s">
         <v>96</v>
-      </c>
-      <c r="L2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -27719,7 +27930,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -27740,7 +27951,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I5" t="s">
         <v>28</v>
@@ -27749,10 +27960,10 @@
         <v>78</v>
       </c>
       <c r="K5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" t="s">
         <v>96</v>
-      </c>
-      <c r="L5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -27837,10 +28048,10 @@
         <v>78</v>
       </c>
       <c r="K8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" t="s">
         <v>96</v>
-      </c>
-      <c r="L8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -27895,7 +28106,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -27913,7 +28124,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -27925,10 +28136,10 @@
         <v>78</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -27983,7 +28194,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -28001,22 +28212,22 @@
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I14" t="s">
         <v>176</v>
-      </c>
-      <c r="I14" t="s">
-        <v>177</v>
       </c>
       <c r="J14" t="s">
         <v>78</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -28071,13 +28282,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -28089,10 +28300,10 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I17" t="s">
         <v>28</v>
@@ -28101,10 +28312,10 @@
         <v>78</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -28176,10 +28387,10 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -28197,7 +28408,7 @@
         <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I20" t="s">
         <v>29</v>
@@ -28206,7 +28417,7 @@
         <v>78</v>
       </c>
       <c r="K20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s">
         <v>17</v>
@@ -28284,7 +28495,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -28305,7 +28516,7 @@
         <v>11</v>
       </c>
       <c r="H23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
@@ -28314,7 +28525,7 @@
         <v>78</v>
       </c>
       <c r="K23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s">
         <v>17</v>
@@ -28392,7 +28603,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -28413,7 +28624,7 @@
         <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I26" t="s">
         <v>29</v>
@@ -28484,7 +28695,7 @@
         <v>20.90909090909091</v>
       </c>
       <c r="P27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q27" s="6">
         <v>38149</v>
@@ -28492,7 +28703,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q28" s="6">
         <v>39101</v>
@@ -28500,13 +28711,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -28518,10 +28729,10 @@
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I29" t="s">
         <v>29</v>
@@ -28536,7 +28747,7 @@
         <v>17</v>
       </c>
       <c r="P29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="6">
         <v>38051</v>
@@ -28592,7 +28803,7 @@
         <v>20.545454545454547</v>
       </c>
       <c r="P30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q30" s="6">
         <v>39287</v>
@@ -28608,7 +28819,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -28620,7 +28831,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -28629,7 +28840,7 @@
         <v>11</v>
       </c>
       <c r="H32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I32" t="s">
         <v>29</v>
@@ -28644,7 +28855,7 @@
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q32" s="6">
         <v>38141</v>
@@ -28700,7 +28911,7 @@
         <v>20.90909090909091</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q33" s="6">
         <v>38563</v>
@@ -28708,7 +28919,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q34" s="6">
         <v>39028</v>
@@ -28728,16 +28939,16 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
@@ -28746,13 +28957,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L35" t="s">
         <v>17</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q35" s="6">
         <v>38357</v>
@@ -28808,7 +29019,7 @@
         <v>20.545454545454547</v>
       </c>
       <c r="P36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q36" s="6">
         <v>38587</v>
@@ -28816,7 +29027,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q37" s="6">
         <v>39590</v>
@@ -28824,28 +29035,28 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I38" t="s">
         <v>29</v>
@@ -28854,13 +29065,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s">
         <v>17</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q38" s="6">
         <v>38719</v>
@@ -28924,7 +29135,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q40" s="6">
         <v>38650</v>
@@ -28932,7 +29143,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -28944,31 +29155,31 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I41" t="s">
         <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L41" t="s">
         <v>17</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q41" s="6">
         <v>38829</v>
@@ -29024,7 +29235,7 @@
         <v>20.818181818181817</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q42" s="6">
         <v>39108</v>
@@ -29032,7 +29243,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q43" s="6">
         <v>38417</v>
@@ -29040,7 +29251,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -29052,31 +29263,31 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I44" t="s">
         <v>29</v>
       </c>
       <c r="J44" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L44" t="s">
         <v>17</v>
       </c>
       <c r="P44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q44" s="6">
         <v>38342</v>
@@ -29132,7 +29343,7 @@
         <v>21</v>
       </c>
       <c r="P45" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q45" s="6">
         <v>37955</v>
@@ -29140,7 +29351,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q46" s="6">
         <v>39276</v>
@@ -29154,37 +29365,37 @@
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H47" t="s">
         <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s">
         <v>12</v>
       </c>
       <c r="K47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q47" s="6">
         <v>36921</v>
@@ -29240,7 +29451,7 @@
         <v>21.272727272727273</v>
       </c>
       <c r="P48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q48" s="6">
         <v>38795</v>
@@ -29248,40 +29459,40 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H50" t="s">
         <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J50" t="s">
         <v>12</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -29342,34 +29553,34 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F53" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G53" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
         <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J53" t="s">
         <v>12</v>
       </c>
       <c r="K53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -29424,19 +29635,19 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -29445,19 +29656,19 @@
         <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s">
         <v>12</v>
       </c>
       <c r="K56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -29553,7 +29764,7 @@
         <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
         <v>45</v>
@@ -29641,7 +29852,7 @@
         <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
         <v>45</v>
@@ -29656,7 +29867,7 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
@@ -29714,10 +29925,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -29729,7 +29940,7 @@
         <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
@@ -29738,13 +29949,13 @@
         <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J8" t="s">
         <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L8" t="s">
         <v>27</v>
@@ -29805,19 +30016,19 @@
         <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -29826,13 +30037,13 @@
         <v>44</v>
       </c>
       <c r="I11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J11" t="s">
         <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s">
         <v>27</v>
@@ -29899,13 +30110,13 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E14" t="s">
         <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" t="s">
         <v>45</v>
@@ -29914,13 +30125,13 @@
         <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J14" t="s">
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s">
         <v>27</v>
@@ -29987,28 +30198,28 @@
         <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
         <v>52</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
         <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s">
         <v>27</v>
@@ -30083,7 +30294,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -30098,16 +30309,16 @@
         <v>52</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
         <v>45</v>
       </c>
       <c r="H20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J20" t="s">
         <v>54</v>
@@ -30191,10 +30402,10 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
         <v>56</v>
@@ -30206,16 +30417,16 @@
         <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G23" t="s">
         <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J23" t="s">
         <v>54</v>
@@ -30227,7 +30438,7 @@
         <v>27</v>
       </c>
       <c r="P23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="6">
         <v>36935</v>
@@ -30299,10 +30510,10 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
         <v>56</v>
@@ -30314,16 +30525,16 @@
         <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G26" t="s">
         <v>45</v>
       </c>
       <c r="H26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J26" t="s">
         <v>54</v>
@@ -30407,13 +30618,13 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D29" t="s">
         <v>42</v>
@@ -30422,16 +30633,16 @@
         <v>52</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G29" t="s">
         <v>45</v>
       </c>
       <c r="H29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J29" t="s">
         <v>54</v>
@@ -30440,10 +30651,10 @@
         <v>44</v>
       </c>
       <c r="L29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="6">
         <v>36691</v>
@@ -30499,7 +30710,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q30" s="6">
         <v>38273</v>
@@ -30507,7 +30718,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q31" s="6">
         <v>38930</v>
@@ -30518,10 +30729,10 @@
         <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D32" t="s">
         <v>42</v>
@@ -30530,16 +30741,16 @@
         <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
         <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J32" t="s">
         <v>54</v>
@@ -30548,10 +30759,10 @@
         <v>44</v>
       </c>
       <c r="L32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q32" s="6">
         <v>39521</v>
@@ -30607,7 +30818,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q33" s="6">
         <v>39202</v>
@@ -30615,7 +30826,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q34" s="6">
         <v>39235</v>
@@ -30623,10 +30834,10 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
@@ -30635,19 +30846,19 @@
         <v>42</v>
       </c>
       <c r="E35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G35" t="s">
         <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J35" t="s">
         <v>54</v>
@@ -30656,10 +30867,10 @@
         <v>44</v>
       </c>
       <c r="L35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q35" s="6">
         <v>38695</v>
@@ -30715,7 +30926,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q36" s="6">
         <v>38377</v>
@@ -30723,7 +30934,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q37" s="6">
         <v>38949</v>
@@ -30731,7 +30942,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
@@ -30743,19 +30954,19 @@
         <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J38" t="s">
         <v>54</v>
@@ -30767,7 +30978,7 @@
         <v>45</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q38" s="6">
         <v>37972</v>
@@ -30823,7 +31034,7 @@
         <v>19.272727272727273</v>
       </c>
       <c r="P39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q39" s="6">
         <v>39232</v>
@@ -30831,7 +31042,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q40" s="6">
         <v>38829</v>
@@ -30839,7 +31050,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -30851,19 +31062,19 @@
         <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J41" t="s">
         <v>54</v>
@@ -30875,7 +31086,7 @@
         <v>45</v>
       </c>
       <c r="P41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q41" s="6">
         <v>39557</v>
@@ -30931,7 +31142,7 @@
         <v>19.727272727272727</v>
       </c>
       <c r="P42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q42" s="6">
         <v>39296</v>
@@ -30942,7 +31153,7 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
         <v>52</v>
@@ -30951,19 +31162,19 @@
         <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J44" t="s">
         <v>54</v>
@@ -31030,7 +31241,7 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
         <v>52</v>
@@ -31039,19 +31250,19 @@
         <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J47" t="s">
         <v>54</v>
@@ -31118,28 +31329,28 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J50" t="s">
         <v>54</v>
@@ -31206,28 +31417,28 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D53" t="s">
         <v>48</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F53" t="s">
+        <v>288</v>
+      </c>
+      <c r="G53" t="s">
         <v>289</v>
       </c>
-      <c r="G53" t="s">
-        <v>290</v>
-      </c>
       <c r="H53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J53" t="s">
         <v>54</v>
@@ -31291,31 +31502,31 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s">
         <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F56" t="s">
+        <v>288</v>
+      </c>
+      <c r="G56" t="s">
         <v>289</v>
       </c>
-      <c r="G56" t="s">
-        <v>290</v>
-      </c>
       <c r="H56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I56" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J56" t="s">
         <v>54</v>
@@ -31382,28 +31593,28 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D59" t="s">
         <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F59" t="s">
+        <v>288</v>
+      </c>
+      <c r="G59" t="s">
         <v>289</v>
       </c>
-      <c r="G59" t="s">
-        <v>290</v>
-      </c>
       <c r="H59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J59" t="s">
         <v>54</v>
@@ -31470,31 +31681,31 @@
         <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D62" t="s">
         <v>52</v>
       </c>
       <c r="E62" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F62" t="s">
+        <v>288</v>
+      </c>
+      <c r="G62" t="s">
         <v>289</v>
       </c>
-      <c r="G62" t="s">
-        <v>290</v>
-      </c>
       <c r="H62" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I62" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J62" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K62" t="s">
         <v>44</v>
@@ -31557,13 +31768,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D65" t="s">
         <v>52</v>
@@ -31575,16 +31786,16 @@
         <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K65" t="s">
         <v>44</v>
@@ -31671,7 +31882,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.425619834710741</v>
+        <v>19.43388429752066</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -31679,7 +31890,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>62</v>
@@ -31691,10 +31902,10 @@
         <v>63</v>
       </c>
       <c r="F2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" t="s">
         <v>100</v>
-      </c>
-      <c r="G2" t="s">
-        <v>101</v>
       </c>
       <c r="H2" t="s">
         <v>58</v>
@@ -31768,22 +31979,22 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H5" t="s">
         <v>58</v>
@@ -31857,28 +32068,28 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
         <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H8" t="s">
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J8" t="s">
         <v>59</v>
@@ -31943,25 +32154,25 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
         <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H11" t="s">
         <v>58</v>
@@ -32035,22 +32246,22 @@
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
         <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H14" t="s">
         <v>58</v>
@@ -32062,7 +32273,7 @@
         <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L14" t="s">
         <v>61</v>
@@ -32121,25 +32332,25 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C17" t="s">
         <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" t="s">
         <v>205</v>
       </c>
-      <c r="F17" t="s">
-        <v>206</v>
-      </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
         <v>58</v>
@@ -32151,7 +32362,7 @@
         <v>59</v>
       </c>
       <c r="K17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L17" t="s">
         <v>61</v>
@@ -32208,7 +32419,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q18" s="6">
         <v>39078</v>
@@ -32227,28 +32438,28 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" t="s">
         <v>213</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
         <v>214</v>
       </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>215</v>
       </c>
-      <c r="F20" t="s">
-        <v>216</v>
-      </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I20" t="s">
         <v>72</v>
@@ -32257,7 +32468,7 @@
         <v>59</v>
       </c>
       <c r="K20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s">
         <v>61</v>
@@ -32336,28 +32547,28 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" t="s">
         <v>224</v>
       </c>
-      <c r="B23" t="s">
-        <v>225</v>
-      </c>
       <c r="C23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>62</v>
       </c>
       <c r="F23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
         <v>72</v>
@@ -32366,14 +32577,14 @@
         <v>59</v>
       </c>
       <c r="K23" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s">
         <v>61</v>
       </c>
       <c r="N23" s="1"/>
       <c r="P23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="6">
         <v>38724</v>
@@ -32429,7 +32640,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6">
         <v>38762</v>
@@ -32448,25 +32659,25 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I26" t="s">
         <v>72</v>
@@ -32475,7 +32686,7 @@
         <v>59</v>
       </c>
       <c r="K26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L26" t="s">
         <v>61</v>
@@ -32554,16 +32765,16 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -32572,26 +32783,26 @@
         <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J29" t="s">
         <v>59</v>
       </c>
       <c r="K29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L29" t="s">
         <v>61</v>
       </c>
       <c r="N29" s="1"/>
       <c r="P29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="6">
         <v>38373</v>
@@ -32647,7 +32858,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6">
         <v>39117</v>
@@ -32655,7 +32866,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q31" s="6">
         <v>39109</v>
@@ -32666,13 +32877,13 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>58</v>
@@ -32681,26 +32892,26 @@
         <v>64</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J32" t="s">
         <v>59</v>
       </c>
       <c r="K32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s">
         <v>62</v>
       </c>
       <c r="N32" s="1"/>
       <c r="P32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q32" s="6">
         <v>39204</v>
@@ -32756,7 +32967,7 @@
         <v>19.363636363636363</v>
       </c>
       <c r="P33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q33" s="6">
         <v>38853</v>
@@ -32764,7 +32975,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q34" s="6">
         <v>38666</v>
@@ -32775,13 +32986,13 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
         <v>58</v>
@@ -32790,26 +33001,26 @@
         <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I35" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J35" t="s">
         <v>59</v>
       </c>
       <c r="K35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L35" t="s">
         <v>62</v>
       </c>
       <c r="N35" s="1"/>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q35" s="6">
         <v>39117</v>
@@ -32865,7 +33076,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q36" s="6">
         <v>38977</v>
@@ -32873,7 +33084,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q37" s="6">
         <v>38815</v>
@@ -32881,16 +33092,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -32899,26 +33110,26 @@
         <v>64</v>
       </c>
       <c r="G38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J38" t="s">
         <v>59</v>
       </c>
       <c r="K38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L38" t="s">
         <v>62</v>
       </c>
       <c r="N38" s="1"/>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q38" s="6">
         <v>38151</v>
@@ -32974,7 +33185,7 @@
         <v>19.545454545454547</v>
       </c>
       <c r="P39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q39" s="6">
         <v>39115</v>
@@ -32982,7 +33193,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q40" s="6">
         <v>39179</v>
@@ -32990,16 +33201,16 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E41" t="s">
         <v>58</v>
@@ -33008,26 +33219,26 @@
         <v>64</v>
       </c>
       <c r="G41" t="s">
+        <v>215</v>
+      </c>
+      <c r="H41" t="s">
+        <v>269</v>
+      </c>
+      <c r="I41" t="s">
+        <v>246</v>
+      </c>
+      <c r="J41" t="s">
+        <v>146</v>
+      </c>
+      <c r="K41" t="s">
         <v>216</v>
-      </c>
-      <c r="H41" t="s">
-        <v>270</v>
-      </c>
-      <c r="I41" t="s">
-        <v>247</v>
-      </c>
-      <c r="J41" t="s">
-        <v>147</v>
-      </c>
-      <c r="K41" t="s">
-        <v>217</v>
       </c>
       <c r="L41" t="s">
         <v>62</v>
       </c>
       <c r="N41" s="1"/>
       <c r="P41" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q41" s="6">
         <v>38994</v>
@@ -33083,7 +33294,7 @@
         <v>19.272727272727273</v>
       </c>
       <c r="P42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q42" s="6">
         <v>38581</v>
@@ -33091,7 +33302,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P43" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q43" s="6">
         <v>38932</v>
@@ -33099,16 +33310,16 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E44" t="s">
         <v>58</v>
@@ -33117,26 +33328,26 @@
         <v>64</v>
       </c>
       <c r="G44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I44" t="s">
         <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L44" t="s">
         <v>62</v>
       </c>
       <c r="N44" s="1"/>
       <c r="P44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q44" s="6">
         <v>38422</v>
@@ -33192,7 +33403,7 @@
         <v>19.636363636363637</v>
       </c>
       <c r="P45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q45" s="6">
         <v>39186</v>
@@ -33200,7 +33411,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q46" s="6">
         <v>39198</v>
@@ -33211,13 +33422,13 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" t="s">
         <v>215</v>
-      </c>
-      <c r="D47" t="s">
-        <v>216</v>
       </c>
       <c r="E47" t="s">
         <v>58</v>
@@ -33226,10 +33437,10 @@
         <v>64</v>
       </c>
       <c r="G47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I47" t="s">
         <v>61</v>
@@ -33238,14 +33449,14 @@
         <v>59</v>
       </c>
       <c r="K47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L47" t="s">
         <v>62</v>
       </c>
       <c r="N47" s="1"/>
       <c r="P47" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q47" s="6">
         <v>39132</v>
@@ -33301,7 +33512,7 @@
         <v>19.454545454545453</v>
       </c>
       <c r="P48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q48" s="6">
         <v>38070</v>
@@ -33309,7 +33520,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="P49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q49" s="6">
         <v>38454</v>
@@ -33320,13 +33531,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E50" t="s">
         <v>58</v>
@@ -33335,19 +33546,19 @@
         <v>64</v>
       </c>
       <c r="G50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I50" t="s">
         <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K50" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L50" t="s">
         <v>62</v>
@@ -33406,13 +33617,13 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D53" t="s">
         <v>73</v>
@@ -33424,22 +33635,22 @@
         <v>64</v>
       </c>
       <c r="G53" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L53" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N53" s="1"/>
     </row>
@@ -33498,10 +33709,10 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D56" t="s">
         <v>63</v>
@@ -33513,19 +33724,19 @@
         <v>64</v>
       </c>
       <c r="G56" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H56" t="s">
         <v>62</v>
       </c>
       <c r="I56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L56" t="s">
         <v>61</v>
@@ -33587,34 +33798,34 @@
         <v>50</v>
       </c>
       <c r="B59" t="s">
+        <v>212</v>
+      </c>
+      <c r="C59" t="s">
+        <v>214</v>
+      </c>
+      <c r="D59" t="s">
         <v>213</v>
       </c>
-      <c r="C59" t="s">
-        <v>215</v>
-      </c>
-      <c r="D59" t="s">
-        <v>214</v>
-      </c>
       <c r="E59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F59" t="s">
         <v>72</v>
       </c>
       <c r="G59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H59" t="s">
         <v>62</v>
       </c>
       <c r="I59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L59" t="s">
         <v>61</v>
@@ -33656,7 +33867,7 @@
       </c>
       <c r="J60">
         <f t="shared" ca="1" si="19"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K60">
         <f t="shared" ca="1" si="19"/>
@@ -33668,42 +33879,42 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:L60)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D62" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H62" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I62" t="s">
         <v>64</v>
       </c>
       <c r="J62" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K62" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L62" t="s">
         <v>61</v>
@@ -33745,7 +33956,7 @@
       </c>
       <c r="J63">
         <f t="shared" ca="1" si="20"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="20"/>
@@ -33757,30 +33968,30 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:L63)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H65" t="s">
         <v>62</v>
@@ -33789,10 +34000,10 @@
         <v>64</v>
       </c>
       <c r="J65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L65" t="s">
         <v>61</v>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6313" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94477392-7B17-4EAB-AF50-D12778FED65B}"/>
+  <xr:revisionPtr revIDLastSave="6329" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61B7BE4F-B336-4473-A8AC-F7043A924BF8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" activeTab="3" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="315">
   <si>
     <t>Scholl</t>
   </si>
@@ -1009,6 +1009,12 @@
   </si>
   <si>
     <t>Scherzer</t>
+  </si>
+  <si>
+    <t>Drabo</t>
+  </si>
+  <si>
+    <t>Dermane</t>
   </si>
 </sst>
 </file>
@@ -2542,6 +2548,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5522,6 +5531,9 @@
                 <c:pt idx="18">
                   <c:v>21.454545454545453</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.181818181818183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -16127,7 +16139,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.909090909090907</v>
+        <v>20.922727272727268</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -18887,7 +18899,7 @@
       </c>
       <c r="U6" s="5" cm="1">
         <f t="array" aca="1" ref="U6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="V6" s="5" cm="1">
         <f t="array" aca="1" ref="V6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -27827,7 +27839,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -27837,7 +27849,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.909090909090907</v>
+        <v>20.922727272727268</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -29457,7 +29469,15 @@
         <v>38795</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>38708</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -29494,8 +29514,14 @@
       <c r="L50" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>39042</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>24</v>
@@ -29545,7 +29571,7 @@
         <v>20.636363636363637</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -29583,7 +29609,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>24</v>
@@ -29633,7 +29659,7 @@
         <v>21.181818181818183</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -29671,7 +29697,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>24</v>
@@ -29719,6 +29745,94 @@
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:L57)</f>
         <v>21.454545454545453</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>266</v>
+      </c>
+      <c r="F59" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" t="s">
+        <v>175</v>
+      </c>
+      <c r="I59" t="s">
+        <v>96</v>
+      </c>
+      <c r="J59" t="s">
+        <v>12</v>
+      </c>
+      <c r="K59" t="s">
+        <v>313</v>
+      </c>
+      <c r="L59" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="20">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="20"/>
+        <v>22</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="20"/>
+        <v>25</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="20"/>
+        <v>25</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:L60)</f>
+        <v>21.181818181818183</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6329" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61B7BE4F-B336-4473-A8AC-F7043A924BF8}"/>
+  <xr:revisionPtr revIDLastSave="6462" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F949BB2-C36C-42E8-B609-E03F1D344D88}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" activeTab="3" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="321">
   <si>
     <t>Scholl</t>
   </si>
@@ -1016,6 +1016,24 @@
   <si>
     <t>Dermane</t>
   </si>
+  <si>
+    <t>Rahmani</t>
+  </si>
+  <si>
+    <t>Kolp</t>
+  </si>
+  <si>
+    <t>Blazevic</t>
+  </si>
+  <si>
+    <t>Stöckl</t>
+  </si>
+  <si>
+    <t>Brandt</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
 </sst>
 </file>
 
@@ -1297,6 +1315,9 @@
                 <c:pt idx="19">
                   <c:v>22</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>21.363636363636363</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1567,10 +1588,10 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
@@ -1579,7 +1600,7 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
@@ -1594,30 +1615,33 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
@@ -1886,7 +1910,7 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
@@ -1898,7 +1922,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -1910,10 +1934,10 @@
                   <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.272727272727273</c:v>
@@ -1926,6 +1950,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2493,13 +2520,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.454545454545453</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>21.181818181818183</c:v>
@@ -2511,31 +2538,31 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
@@ -2551,6 +2578,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2880,6 +2910,12 @@
                 <c:pt idx="57">
                   <c:v>19</c:v>
                 </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19.181818181818183</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3152,7 +3188,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -3167,37 +3203,40 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="42" formatCode="0.00">
+                <c:pt idx="58" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="0.00">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3516,6 +3555,12 @@
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
+                <c:pt idx="58" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="0.00">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3793,7 +3838,7 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>19.454545454545453</c:v>
@@ -3805,7 +3850,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -3817,10 +3862,10 @@
                   <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>20.272727272727273</c:v>
@@ -3833,6 +3878,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4126,7 +4174,7 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
@@ -4141,37 +4189,40 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="36" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                <c:pt idx="51" formatCode="0.00">
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
+                <c:pt idx="54" formatCode="0.00">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>19.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="42" formatCode="0.00">
+                <c:pt idx="58" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="0.00">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4512,6 +4563,12 @@
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
+                <c:pt idx="58" formatCode="0.00">
+                  <c:v>21.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="0.00">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4792,10 +4849,10 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>20.181818181818183</c:v>
@@ -4804,7 +4861,7 @@
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
@@ -4819,30 +4876,33 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>20.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>20.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
@@ -5475,13 +5535,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.454545454545453</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>21.181818181818183</c:v>
@@ -5493,31 +5553,31 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>20.818181818181817</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>21.272727272727273</c:v>
@@ -5533,6 +5593,9 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>21.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5882,6 +5945,12 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16081,20 +16150,20 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="5">
-        <f ca="1">Liefering!N1</f>
-        <v>19.43388429752066</v>
+        <f ca="1">Rapid!N1</f>
+        <v>19.450757575757574</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="5">
-        <f ca="1">Rapid!N1</f>
-        <v>19.495867768595041</v>
+        <f ca="1">Liefering!N1</f>
+        <v>19.490118577075094</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -16103,7 +16172,7 @@
       </c>
       <c r="B4" s="5">
         <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.621212121212125</v>
+        <v>19.650000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -16112,7 +16181,7 @@
       </c>
       <c r="B5" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.622727272727275</v>
+        <v>19.705627705627709</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16121,7 +16190,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.09090909090909</v>
+        <v>20.142857142857142</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -16130,7 +16199,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.855371900826448</v>
+        <v>20.844696969696972</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -16139,7 +16208,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.922727272727268</v>
+        <v>20.98268398268398</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -16148,7 +16217,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>21.004132231404956</v>
+        <v>20.984848484848484</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16185,7 +16254,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.855371900826448</v>
+        <v>20.844696969696972</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -18356,16 +18425,182 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>60</v>
+      </c>
+      <c r="B68" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" t="s">
+        <v>201</v>
+      </c>
+      <c r="H68" t="s">
+        <v>57</v>
+      </c>
+      <c r="I68" t="s">
+        <v>68</v>
+      </c>
+      <c r="J68" t="s">
+        <v>66</v>
+      </c>
+      <c r="K68" t="s">
+        <v>225</v>
+      </c>
+      <c r="L68" t="s">
+        <v>101</v>
+      </c>
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N69" s="1"/>
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>23</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>26</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>26</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>21.09090909090909</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" t="s">
+        <v>294</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" t="s">
+        <v>117</v>
+      </c>
+      <c r="F71" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" t="s">
+        <v>201</v>
+      </c>
+      <c r="H71" t="s">
+        <v>308</v>
+      </c>
+      <c r="I71" t="s">
+        <v>68</v>
+      </c>
+      <c r="J71" t="s">
+        <v>66</v>
+      </c>
+      <c r="K71" t="s">
+        <v>182</v>
+      </c>
+      <c r="L71" t="s">
+        <v>101</v>
+      </c>
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N72" s="1"/>
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>23</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>26</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>26</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>20.363636363636363</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N74" s="1"/>
@@ -18547,7 +18782,7 @@
       </c>
       <c r="V2" s="8" cm="1">
         <f t="array" aca="1" ref="V2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.363636363636363</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -18564,11 +18799,11 @@
       </c>
       <c r="D3" s="8" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="E3" s="8" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="F3" s="8" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18580,7 +18815,7 @@
       </c>
       <c r="H3" s="8" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18600,7 +18835,7 @@
       </c>
       <c r="M3" s="8" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18608,35 +18843,35 @@
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="T3" s="8" cm="1">
         <f t="array" aca="1" ref="T3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="U3" s="8" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="V3" s="8" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -18661,7 +18896,7 @@
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18677,7 +18912,7 @@
       </c>
       <c r="J4" s="5" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="K4" s="5" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18693,11 +18928,11 @@
       </c>
       <c r="N4" s="5" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="O4" s="5" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
       <c r="P4" s="5" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18717,11 +18952,11 @@
       </c>
       <c r="T4" s="5" cm="1">
         <f t="array" aca="1" ref="T4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="U4" s="5" cm="1">
         <f t="array" aca="1" ref="U4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="V4" s="5" cm="1">
         <f t="array" aca="1" ref="V4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18823,15 +19058,15 @@
       </c>
       <c r="B6" s="5" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="C6" s="5" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="D6" s="5" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="E6" s="5" cm="1">
         <f t="array" aca="1" ref="E6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18847,39 +19082,39 @@
       </c>
       <c r="H6" s="5" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="I6" s="5" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="J6" s="5" cm="1">
         <f t="array" aca="1" ref="J6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="K6" s="5" cm="1">
         <f t="array" aca="1" ref="K6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="L6" s="5" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="M6" s="5" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="N6" s="5" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="O6" s="5" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P6" s="5" cm="1">
         <f t="array" aca="1" ref="P6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="Q6" s="5" cm="1">
         <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -18903,7 +19138,7 @@
       </c>
       <c r="V6" s="5" cm="1">
         <f t="array" aca="1" ref="V6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>21.09090909090909</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -19025,7 +19260,7 @@
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19045,43 +19280,43 @@
       </c>
       <c r="M8" s="5" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="N8" s="5" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="O8" s="5" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P8" s="5" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="R8" s="5" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -19801,7 +20036,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.622727272727275</v>
+        <v>19.705627705627709</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21813,8 +22048,93 @@
         <v>22</v>
       </c>
     </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" t="s">
+        <v>278</v>
+      </c>
+      <c r="C62" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" t="s">
+        <v>312</v>
+      </c>
+      <c r="F62" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" t="s">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" t="s">
+        <v>311</v>
+      </c>
+      <c r="J62" t="s">
+        <v>82</v>
+      </c>
+      <c r="K62" t="s">
+        <v>282</v>
+      </c>
+      <c r="L62" t="s">
+        <v>279</v>
+      </c>
+    </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N63" s="1"/>
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>30</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>23</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
+        <v>21.363636363636363</v>
+      </c>
     </row>
     <row r="66" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N66" s="1"/>
@@ -21840,7 +22160,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -21853,7 +22173,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.09090909090909</v>
+        <v>20.142857142857142</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -22105,7 +22425,7 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -22117,7 +22437,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -22193,7 +22513,7 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
@@ -22205,7 +22525,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -22482,11 +22802,11 @@
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -22990,7 +23310,7 @@
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="11"/>
@@ -23026,7 +23346,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P36" t="s">
         <v>168</v>
@@ -23206,7 +23526,7 @@
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <f t="shared" ca="1" si="13"/>
@@ -23242,7 +23562,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P42" t="s">
         <v>264</v>
@@ -23314,7 +23634,7 @@
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
@@ -23350,7 +23670,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P45" t="s">
         <v>286</v>
@@ -23422,7 +23742,7 @@
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
@@ -23458,7 +23778,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P48" t="s">
         <v>307</v>
@@ -23530,7 +23850,7 @@
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E51">
         <f t="shared" ca="1" si="16"/>
@@ -23566,7 +23886,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -23618,7 +23938,7 @@
       </c>
       <c r="D54">
         <f t="shared" ca="1" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E54">
         <f t="shared" ca="1" si="17"/>
@@ -23654,7 +23974,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -23706,7 +24026,7 @@
       </c>
       <c r="D57">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57">
         <f t="shared" ca="1" si="18"/>
@@ -23718,7 +24038,7 @@
       </c>
       <c r="G57">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H57">
         <f t="shared" ca="1" si="18"/>
@@ -23742,7 +24062,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>19</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -23806,7 +24126,7 @@
       </c>
       <c r="G60">
         <f t="shared" ca="1" si="19"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60">
         <f t="shared" ca="1" si="19"/>
@@ -23830,6 +24150,94 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
+        <v>20.181818181818183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" t="s">
+        <v>35</v>
+      </c>
+      <c r="F62" t="s">
+        <v>86</v>
+      </c>
+      <c r="G62" t="s">
+        <v>199</v>
+      </c>
+      <c r="H62" t="s">
+        <v>103</v>
+      </c>
+      <c r="I62" t="s">
+        <v>300</v>
+      </c>
+      <c r="J62" t="s">
+        <v>152</v>
+      </c>
+      <c r="K62" t="s">
+        <v>37</v>
+      </c>
+      <c r="L62" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>24</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>22</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
         <v>20.09090909090909</v>
       </c>
     </row>
@@ -23844,7 +24252,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -23855,7 +24263,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.621212121212125</v>
+        <v>19.650000000000002</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24279,7 +24687,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="4"/>
@@ -24295,7 +24703,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -24686,7 +25094,7 @@
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
@@ -24710,7 +25118,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P27" t="s">
         <v>30</v>
@@ -25130,7 +25538,7 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="12"/>
@@ -25142,7 +25550,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P39" t="s">
         <v>211</v>
@@ -25238,7 +25646,7 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
@@ -25250,7 +25658,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>18.90909090909091</v>
+        <v>19</v>
       </c>
       <c r="P42" t="s">
         <v>236</v>
@@ -25411,6 +25819,12 @@
       </c>
       <c r="L47" t="s">
         <v>158</v>
+      </c>
+      <c r="P47" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>38991</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -25637,6 +26051,182 @@
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
         <v>20.181818181818183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>186</v>
+      </c>
+      <c r="B56" t="s">
+        <v>303</v>
+      </c>
+      <c r="C56" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" t="s">
+        <v>89</v>
+      </c>
+      <c r="G56" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" t="s">
+        <v>304</v>
+      </c>
+      <c r="J56" t="s">
+        <v>21</v>
+      </c>
+      <c r="K56" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="C57">
+        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="E57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="F57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="G57">
+        <f t="shared" ca="1" si="18"/>
+        <v>22</v>
+      </c>
+      <c r="H57">
+        <f t="shared" ca="1" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="I57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="J57">
+        <f t="shared" ca="1" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="K57">
+        <f t="shared" ca="1" si="18"/>
+        <v>22</v>
+      </c>
+      <c r="L57">
+        <f t="shared" ca="1" si="18"/>
+        <v>19</v>
+      </c>
+      <c r="N57" s="1">
+        <f ca="1">AVERAGE(B57:M57)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" t="s">
+        <v>303</v>
+      </c>
+      <c r="C59" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" t="s">
+        <v>208</v>
+      </c>
+      <c r="F59" t="s">
+        <v>89</v>
+      </c>
+      <c r="G59" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" t="s">
+        <v>91</v>
+      </c>
+      <c r="I59" t="s">
+        <v>304</v>
+      </c>
+      <c r="J59" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s">
+        <v>30</v>
+      </c>
+      <c r="L59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="C60">
+        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <f t="shared" ca="1" si="19"/>
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="G60">
+        <f t="shared" ca="1" si="19"/>
+        <v>22</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ca="1" si="19"/>
+        <v>17</v>
+      </c>
+      <c r="I60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ca="1" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ca="1" si="19"/>
+        <v>22</v>
+      </c>
+      <c r="L60">
+        <f t="shared" ca="1" si="19"/>
+        <v>19</v>
+      </c>
+      <c r="N60" s="1">
+        <f ca="1">AVERAGE(B60:M60)</f>
+        <v>19.727272727272727</v>
       </c>
     </row>
   </sheetData>
@@ -25648,7 +26238,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628DC590-5B70-45B7-BCD6-8ED432E7A1AF}">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -25657,7 +26247,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>21.004132231404956</v>
+        <v>20.984848484848484</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27295,8 +27885,22 @@
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>21.272727272727273</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P48" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>39100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>38841</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -27334,8 +27938,14 @@
         <v>248</v>
       </c>
       <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>39034</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -27385,7 +27995,7 @@
         <v>20.727272727272727</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -27424,7 +28034,7 @@
       </c>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -27474,7 +28084,7 @@
         <v>21.181818181818183</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -27513,7 +28123,7 @@
       </c>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -27563,7 +28173,7 @@
         <v>21.727272727272727</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>177</v>
       </c>
@@ -27602,7 +28212,7 @@
       </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -27652,7 +28262,7 @@
         <v>21.818181818181817</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -27691,7 +28301,7 @@
       </c>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
         <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -27828,6 +28438,184 @@
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
         <v>21.90909090909091</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" t="s">
+        <v>317</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>230</v>
+      </c>
+      <c r="E68" t="s">
+        <v>318</v>
+      </c>
+      <c r="F68" t="s">
+        <v>302</v>
+      </c>
+      <c r="G68" t="s">
+        <v>79</v>
+      </c>
+      <c r="H68" t="s">
+        <v>241</v>
+      </c>
+      <c r="I68" t="s">
+        <v>247</v>
+      </c>
+      <c r="J68" t="s">
+        <v>319</v>
+      </c>
+      <c r="K68" t="s">
+        <v>271</v>
+      </c>
+      <c r="L68" t="s">
+        <v>287</v>
+      </c>
+      <c r="N68" s="1"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>28</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>20.363636363636363</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" t="s">
+        <v>317</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" t="s">
+        <v>59</v>
+      </c>
+      <c r="F71" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" t="s">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s">
+        <v>227</v>
+      </c>
+      <c r="I71" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" t="s">
+        <v>189</v>
+      </c>
+      <c r="K71" t="s">
+        <v>271</v>
+      </c>
+      <c r="L71" t="s">
+        <v>287</v>
+      </c>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>36</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>28</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>21.181818181818183</v>
       </c>
     </row>
   </sheetData>
@@ -27839,7 +28627,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -27849,7 +28637,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.922727272727268</v>
+        <v>20.98268398268398</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27913,7 +28701,7 @@
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
@@ -27937,7 +28725,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -28001,7 +28789,7 @@
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -28025,7 +28813,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -28089,7 +28877,7 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
@@ -28113,7 +28901,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -28472,7 +29260,7 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="7"/>
@@ -28488,7 +29276,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:L21)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P21" t="s">
         <v>11</v>
@@ -28580,7 +29368,7 @@
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="8"/>
@@ -28596,7 +29384,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:L24)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P24" t="s">
         <v>29</v>
@@ -28688,7 +29476,7 @@
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="9"/>
@@ -28704,7 +29492,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:L27)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P27" t="s">
         <v>95</v>
@@ -28796,7 +29584,7 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="10"/>
@@ -28812,7 +29600,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:L30)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P30" t="s">
         <v>170</v>
@@ -28904,7 +29692,7 @@
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="11"/>
@@ -28920,7 +29708,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:L33)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P33" t="s">
         <v>176</v>
@@ -29012,7 +29800,7 @@
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="12"/>
@@ -29028,7 +29816,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:L36)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P36" t="s">
         <v>197</v>
@@ -29120,7 +29908,7 @@
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="13"/>
@@ -29136,7 +29924,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:L39)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P39" t="s">
         <v>20</v>
@@ -29228,7 +30016,7 @@
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="14"/>
@@ -29244,7 +30032,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:L42)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P42" t="s">
         <v>250</v>
@@ -29336,7 +30124,7 @@
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="15"/>
@@ -29352,7 +30140,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:L45)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P45" t="s">
         <v>266</v>
@@ -29833,6 +30621,94 @@
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:L60)</f>
         <v>21.181818181818183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>305</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
+        <v>266</v>
+      </c>
+      <c r="F62" t="s">
+        <v>96</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" t="s">
+        <v>175</v>
+      </c>
+      <c r="I62" t="s">
+        <v>96</v>
+      </c>
+      <c r="J62" t="s">
+        <v>95</v>
+      </c>
+      <c r="K62" t="s">
+        <v>313</v>
+      </c>
+      <c r="L62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="21">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="21"/>
+        <v>25</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:L63)</f>
+        <v>21.09090909090909</v>
       </c>
     </row>
   </sheetData>
@@ -29858,7 +30734,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.495867768595041</v>
+        <v>19.450757575757574</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -31262,6 +32138,14 @@
         <v>39296</v>
       </c>
     </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P43" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>39596</v>
+      </c>
+    </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>50</v>
@@ -31298,6 +32182,12 @@
       </c>
       <c r="L44" t="s">
         <v>45</v>
+      </c>
+      <c r="P44" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>39645</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -31968,8 +32858,181 @@
         <v>19</v>
       </c>
     </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" t="s">
+        <v>315</v>
+      </c>
+      <c r="H68" t="s">
+        <v>48</v>
+      </c>
+      <c r="I68" t="s">
+        <v>202</v>
+      </c>
+      <c r="J68" t="s">
+        <v>288</v>
+      </c>
+      <c r="K68" t="s">
+        <v>316</v>
+      </c>
+      <c r="L68" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>18.727272727272727</v>
+      </c>
+    </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N71"/>
+      <c r="A71" t="s">
+        <v>231</v>
+      </c>
+      <c r="B71" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" t="s">
+        <v>180</v>
+      </c>
+      <c r="D71" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" t="s">
+        <v>54</v>
+      </c>
+      <c r="F71" t="s">
+        <v>268</v>
+      </c>
+      <c r="G71" t="s">
+        <v>289</v>
+      </c>
+      <c r="H71" t="s">
+        <v>162</v>
+      </c>
+      <c r="I71" t="s">
+        <v>44</v>
+      </c>
+      <c r="J71" t="s">
+        <v>288</v>
+      </c>
+      <c r="K71" t="s">
+        <v>232</v>
+      </c>
+      <c r="L71" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>22</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>19.181818181818183</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N74"/>
@@ -31996,7 +33059,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.43388429752066</v>
+        <v>19.490118577075094</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -32610,7 +33673,7 @@
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
@@ -32642,7 +33705,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P21" t="s">
         <v>62</v>
@@ -33147,7 +34210,7 @@
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
@@ -33187,7 +34250,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P36" t="s">
         <v>212</v>
@@ -33256,7 +34319,7 @@
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
@@ -33296,7 +34359,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P39" t="s">
         <v>213</v>
@@ -33365,7 +34428,7 @@
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
@@ -33405,7 +34468,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="P42" t="s">
         <v>258</v>
@@ -33474,7 +34537,7 @@
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
@@ -33514,7 +34577,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P45" t="s">
         <v>274</v>
@@ -33583,7 +34646,7 @@
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
@@ -33623,7 +34686,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P48" t="s">
         <v>298</v>
@@ -33686,7 +34749,7 @@
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
@@ -33726,7 +34789,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -33775,7 +34838,7 @@
       </c>
       <c r="C54">
         <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <f t="shared" ca="1" si="17"/>
@@ -33815,7 +34878,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:L54)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -33864,7 +34927,7 @@
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <f t="shared" ca="1" si="18"/>
@@ -33904,7 +34967,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:L57)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -33953,7 +35016,7 @@
       </c>
       <c r="C60">
         <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60">
         <f t="shared" ca="1" si="19"/>
@@ -33993,7 +35056,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:L60)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -34042,7 +35105,7 @@
       </c>
       <c r="C63">
         <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <f t="shared" ca="1" si="20"/>
@@ -34082,7 +35145,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:L63)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -34131,7 +35194,7 @@
       </c>
       <c r="C66">
         <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66">
         <f t="shared" ca="1" si="21"/>
@@ -34171,14 +35234,97 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:L66)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68" t="s">
+        <v>214</v>
+      </c>
+      <c r="D68" t="s">
+        <v>246</v>
+      </c>
+      <c r="E68" t="s">
+        <v>100</v>
+      </c>
+      <c r="F68" t="s">
+        <v>290</v>
+      </c>
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68" t="s">
+        <v>62</v>
+      </c>
+      <c r="I68" t="s">
+        <v>59</v>
+      </c>
+      <c r="J68" t="s">
+        <v>206</v>
+      </c>
+      <c r="K68" t="s">
+        <v>273</v>
+      </c>
+      <c r="L68" t="s">
+        <v>61</v>
+      </c>
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N69" s="1"/>
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:L69)</f>
+        <v>19.636363636363637</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N71" s="1"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6462" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F949BB2-C36C-42E8-B609-E03F1D344D88}"/>
+  <xr:revisionPtr revIDLastSave="6637" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BE24C3-7F27-4ACA-8649-E6D1BC3D3F7F}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="333">
   <si>
     <t>Scholl</t>
   </si>
@@ -1034,6 +1034,42 @@
   <si>
     <t>Benjamin</t>
   </si>
+  <si>
+    <t>Wernitznig</t>
+  </si>
+  <si>
+    <t>Zeqiri</t>
+  </si>
+  <si>
+    <t>Antosch</t>
+  </si>
+  <si>
+    <t>Halastar</t>
+  </si>
+  <si>
+    <t>22. Spieltag</t>
+  </si>
+  <si>
+    <t>23. Spieltag</t>
+  </si>
+  <si>
+    <t>24. Spieltag</t>
+  </si>
+  <si>
+    <t>25. Spieltag</t>
+  </si>
+  <si>
+    <t>26. Spieltag</t>
+  </si>
+  <si>
+    <t>Schwaiger</t>
+  </si>
+  <si>
+    <t>Wansch</t>
+  </si>
+  <si>
+    <t>Mahop</t>
+  </si>
 </sst>
 </file>
 
@@ -1256,67 +1292,73 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.636363636363637</c:v>
+                  <c:v>18.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.90909090909091</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>18.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>18.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>19.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>19.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>22</c:v>
+                  <c:v>22.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21.363636363636363</c:v>
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1582,10 +1624,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>20.454545454545453</c:v>
@@ -1597,10 +1639,10 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
@@ -1615,16 +1657,16 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
@@ -1633,7 +1675,7 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.181818181818183</c:v>
@@ -1642,7 +1684,13 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1898,16 +1946,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>19.727272727272727</c:v>
@@ -2582,6 +2630,12 @@
                 <c:pt idx="20">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>21</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2845,10 +2899,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>20.272727272727273</c:v>
@@ -2860,16 +2914,16 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>20</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>19.545454545454547</c:v>
@@ -2896,25 +2950,28 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>18.454545454545453</c:v>
+                  <c:v>18.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>18.454545454545453</c:v>
+                  <c:v>18.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>18.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3188,55 +3245,58 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="27" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="0.00">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3561,6 +3621,12 @@
                 <c:pt idx="59" formatCode="0.00">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
+                <c:pt idx="60" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3826,16 +3892,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>19.727272727272727</c:v>
@@ -4174,55 +4240,58 @@
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="0.00">
+                  <c:v>19.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="21" formatCode="0.00">
+                <c:pt idx="33" formatCode="0.00">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="24" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                <c:pt idx="42" formatCode="0.00">
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="27" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="0.00">
+                <c:pt idx="45" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="39" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="0.00">
-                  <c:v>19.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
                   <c:v>19.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="0.00">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4569,6 +4638,15 @@
                 <c:pt idx="59" formatCode="0.00">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
+                <c:pt idx="60" formatCode="0.00">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="62" formatCode="0.00">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4843,10 +4921,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>20.454545454545453</c:v>
@@ -4858,10 +4936,10 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.363636363636363</c:v>
@@ -4876,16 +4954,16 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>20.09090909090909</c:v>
@@ -4894,7 +4972,7 @@
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.181818181818183</c:v>
@@ -4903,7 +4981,13 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5597,6 +5681,12 @@
                 <c:pt idx="20">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
+                <c:pt idx="21">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>21</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5881,10 +5971,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>20.272727272727273</c:v>
@@ -5896,16 +5986,16 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>20</c:v>
+                  <c:v>20.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>19.818181818181817</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>19.545454545454547</c:v>
@@ -5932,25 +6022,28 @@
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>18.454545454545453</c:v>
+                  <c:v>18.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>18.454545454545453</c:v>
+                  <c:v>18.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>18.818181818181817</c:v>
+                  <c:v>18.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>19</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>18.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6203,7 +6296,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>19,64</c:v>
+                  <c:v>19,73</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -16154,7 +16247,7 @@
       </c>
       <c r="B2" s="5">
         <f ca="1">Rapid!N1</f>
-        <v>19.450757575757574</v>
+        <v>19.47902097902098</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -16163,7 +16256,7 @@
       </c>
       <c r="B3" s="5">
         <f ca="1">Liefering!N1</f>
-        <v>19.490118577075094</v>
+        <v>19.541818181818183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -16172,7 +16265,7 @@
       </c>
       <c r="B4" s="5">
         <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.650000000000002</v>
+        <v>19.632231404958677</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -16181,7 +16274,7 @@
       </c>
       <c r="B5" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.705627705627709</v>
+        <v>19.889328063241102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16190,7 +16283,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.142857142857142</v>
+        <v>20.138339920948617</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -16199,7 +16292,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.844696969696972</v>
+        <v>20.832167832167833</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -16208,7 +16301,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.98268398268398</v>
+        <v>21.003952569169957</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -16217,7 +16310,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>20.984848484848484</v>
+        <v>21.014545454545456</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16254,7 +16347,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.844696969696972</v>
+        <v>20.832167832167833</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -16797,7 +16890,7 @@
         <v>38998</v>
       </c>
       <c r="T18">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -18603,16 +18696,182 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>169</v>
+      </c>
+      <c r="B74" t="s">
+        <v>116</v>
+      </c>
+      <c r="C74" t="s">
+        <v>294</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>117</v>
+      </c>
+      <c r="F74" t="s">
+        <v>65</v>
+      </c>
+      <c r="G74" t="s">
+        <v>201</v>
+      </c>
+      <c r="H74" t="s">
+        <v>308</v>
+      </c>
+      <c r="I74" t="s">
+        <v>68</v>
+      </c>
+      <c r="J74" t="s">
+        <v>66</v>
+      </c>
+      <c r="K74" t="s">
+        <v>182</v>
+      </c>
+      <c r="L74" t="s">
+        <v>101</v>
+      </c>
       <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N75" s="1"/>
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>23</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>22</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>26</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>26</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>20.818181818181817</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" t="s">
+        <v>294</v>
+      </c>
+      <c r="D77" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" t="s">
+        <v>74</v>
+      </c>
+      <c r="F77" t="s">
+        <v>184</v>
+      </c>
+      <c r="G77" t="s">
+        <v>201</v>
+      </c>
+      <c r="H77" t="s">
+        <v>308</v>
+      </c>
+      <c r="I77" t="s">
+        <v>68</v>
+      </c>
+      <c r="J77" t="s">
+        <v>66</v>
+      </c>
+      <c r="K77" t="s">
+        <v>57</v>
+      </c>
+      <c r="L77" t="s">
+        <v>101</v>
+      </c>
       <c r="N77" s="1"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N78" s="1"/>
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>23</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>26</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>26</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>20.545454545454547</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -18622,7 +18881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A980021B-B36B-4907-BAF3-C28A440CD06D}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -18631,7 +18890,7 @@
     <col min="23" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>125</v>
       </c>
@@ -18695,34 +18954,49 @@
       <c r="V1" s="7" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="8" cm="1">
         <f t="array" aca="1" ref="B2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="C2" s="8" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.636363636363637</v>
+        <v>18.727272727272727</v>
       </c>
       <c r="D2" s="8" cm="1">
         <f t="array" aca="1" ref="D2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="E2" s="8" cm="1">
         <f t="array" aca="1" ref="E2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
       <c r="F2" s="8" cm="1">
         <f t="array" aca="1" ref="F2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="G2" s="8" cm="1">
         <f t="array" aca="1" ref="G2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="H2" s="8" cm="1">
         <f t="array" aca="1" ref="H2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18730,35 +19004,35 @@
       </c>
       <c r="I2" s="8" cm="1">
         <f t="array" aca="1" ref="I2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="J2" s="8" cm="1">
         <f t="array" aca="1" ref="J2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.727272727272727</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="K2" s="8" cm="1">
         <f t="array" aca="1" ref="K2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="L2" s="8" cm="1">
         <f t="array" aca="1" ref="L2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="M2" s="8" cm="1">
         <f t="array" aca="1" ref="M2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="N2" s="8" cm="1">
         <f t="array" aca="1" ref="N2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="O2" s="8" cm="1">
         <f t="array" aca="1" ref="O2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P2" s="8" cm="1">
         <f t="array" aca="1" ref="P2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
       <c r="Q2" s="8" cm="1">
         <f t="array" aca="1" ref="Q2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -18766,36 +19040,56 @@
       </c>
       <c r="R2" s="8" cm="1">
         <f t="array" aca="1" ref="R2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="S2" s="8" cm="1">
         <f t="array" aca="1" ref="S2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="T2" s="8" cm="1">
         <f t="array" aca="1" ref="T2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="U2" s="8" cm="1">
         <f t="array" aca="1" ref="U2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>22</v>
+        <v>22.09090909090909</v>
       </c>
       <c r="V2" s="8" cm="1">
         <f t="array" aca="1" ref="V2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.363636363636363</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+        <v>21.454545454545453</v>
+      </c>
+      <c r="W2" s="8" cm="1">
+        <f t="array" aca="1" ref="W2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>23.09090909090909</v>
+      </c>
+      <c r="X2" s="8" cm="1">
+        <f t="array" aca="1" ref="X2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>18.818181818181817</v>
+      </c>
+      <c r="Y2" s="8" cm="1">
+        <f t="array" aca="1" ref="Y2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="8" cm="1">
+        <f t="array" aca="1" ref="Z2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2" s="8" cm="1">
+        <f t="array" aca="1" ref="AA2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="8" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="C3" s="8" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="D3" s="8" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18811,11 +19105,11 @@
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="H3" s="8" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18835,19 +19129,19 @@
       </c>
       <c r="M3" s="8" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18859,7 +19153,7 @@
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="T3" s="8" cm="1">
         <f t="array" aca="1" ref="T3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -18871,28 +19165,48 @@
       </c>
       <c r="V3" s="8" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+        <v>20.181818181818183</v>
+      </c>
+      <c r="W3" s="8" cm="1">
+        <f t="array" aca="1" ref="W3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="X3" s="8" cm="1">
+        <f t="array" aca="1" ref="X3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="Y3" s="8" cm="1">
+        <f t="array" aca="1" ref="Y3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="8" cm="1">
+        <f t="array" aca="1" ref="Z3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="8" cm="1">
+        <f t="array" aca="1" ref="AA3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>124</v>
       </c>
       <c r="B4" s="5" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="C4" s="5" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -18960,10 +19274,30 @@
       </c>
       <c r="V4" s="5" cm="1">
         <f t="array" aca="1" ref="V4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="W4" s="5" cm="1">
+        <f t="array" aca="1" ref="W4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>18.90909090909091</v>
+      </c>
+      <c r="X4" s="5" cm="1">
+        <f t="array" aca="1" ref="X4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Y4" s="5" cm="1">
+        <f t="array" aca="1" ref="Y4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5" cm="1">
+        <f t="array" aca="1" ref="Z4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5" cm="1">
+        <f t="array" aca="1" ref="AA4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
@@ -19051,8 +19385,28 @@
         <f t="array" aca="1" ref="V5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
         <v>21.818181818181817</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W5" s="5" cm="1">
+        <f t="array" aca="1" ref="W5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.90909090909091</v>
+      </c>
+      <c r="X5" s="5" cm="1">
+        <f t="array" aca="1" ref="X5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.363636363636363</v>
+      </c>
+      <c r="Y5" s="5" cm="1">
+        <f t="array" aca="1" ref="Y5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.181818181818183</v>
+      </c>
+      <c r="Z5" s="5" cm="1">
+        <f t="array" aca="1" ref="Z5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.727272727272727</v>
+      </c>
+      <c r="AA5" s="5" cm="1">
+        <f t="array" aca="1" ref="AA5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -19140,18 +19494,38 @@
         <f t="array" aca="1" ref="V6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
         <v>21.09090909090909</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W6" s="5" cm="1">
+        <f t="array" aca="1" ref="W6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.454545454545453</v>
+      </c>
+      <c r="X6" s="5" cm="1">
+        <f t="array" aca="1" ref="X6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21</v>
+      </c>
+      <c r="Y6" s="5" cm="1">
+        <f t="array" aca="1" ref="Y6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5" cm="1">
+        <f t="array" aca="1" ref="Z6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="5" cm="1">
+        <f t="array" aca="1" ref="AA6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="5" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="C7" s="5" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="D7" s="5" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -19167,19 +19541,19 @@
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="I7" s="5" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="K7" s="5" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -19215,22 +19589,42 @@
       </c>
       <c r="S7" s="5" cm="1">
         <f t="array" aca="1" ref="S7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="T7" s="5" cm="1">
         <f t="array" aca="1" ref="T7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.454545454545453</v>
+        <v>18.545454545454547</v>
       </c>
       <c r="U7" s="5" cm="1">
         <f t="array" aca="1" ref="U7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.454545454545453</v>
+        <v>18.545454545454547</v>
       </c>
       <c r="V7" s="5" cm="1">
         <f t="array" aca="1" ref="V7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.818181818181817</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+        <v>18.90909090909091</v>
+      </c>
+      <c r="W7" s="5" cm="1">
+        <f t="array" aca="1" ref="W7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.09090909090909</v>
+      </c>
+      <c r="X7" s="5" cm="1">
+        <f t="array" aca="1" ref="X7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>18.727272727272727</v>
+      </c>
+      <c r="Y7" s="5" cm="1">
+        <f t="array" aca="1" ref="Y7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.272727272727273</v>
+      </c>
+      <c r="Z7" s="5" cm="1">
+        <f t="array" aca="1" ref="Z7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.272727272727273</v>
+      </c>
+      <c r="AA7" s="5" cm="1">
+        <f t="array" aca="1" ref="AA7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -19260,51 +19654,51 @@
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="K8" s="5" cm="1">
         <f t="array" aca="1" ref="K8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="L8" s="5" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="M8" s="5" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="N8" s="5" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="O8" s="5" cm="1">
         <f t="array" aca="1" ref="O8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P8" s="5" cm="1">
         <f t="array" aca="1" ref="P8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="R8" s="5" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19312,14 +19706,34 @@
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.545454545454547</v>
+      </c>
+      <c r="W8" s="5" cm="1">
+        <f t="array" aca="1" ref="W8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
         <v>19.363636363636363</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X8" s="5" cm="1">
+        <f t="array" aca="1" ref="X8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="Y8" s="5" cm="1">
+        <f t="array" aca="1" ref="Y8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.272727272727273</v>
+      </c>
+      <c r="Z8" s="5" cm="1">
+        <f t="array" aca="1" ref="Z8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.454545454545453</v>
+      </c>
+      <c r="AA8" s="5" cm="1">
+        <f t="array" aca="1" ref="AA8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>50</v>
       </c>
@@ -19407,8 +19821,28 @@
         <f t="array" aca="1" ref="V9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
         <v>20.90909090909091</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W9" s="5" cm="1">
+        <f t="array" aca="1" ref="W9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.90909090909091</v>
+      </c>
+      <c r="X9" s="5" cm="1">
+        <f t="array" aca="1" ref="X9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.09090909090909</v>
+      </c>
+      <c r="Y9" s="5" cm="1">
+        <f t="array" aca="1" ref="Y9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.363636363636363</v>
+      </c>
+      <c r="Z9" s="5" cm="1">
+        <f t="array" aca="1" ref="Z9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.818181818181817</v>
+      </c>
+      <c r="AA9" s="5" cm="1">
+        <f t="array" aca="1" ref="AA9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.545454545454547</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -19431,7 +19865,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -19454,7 +19888,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -19477,7 +19911,7 @@
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -19500,7 +19934,7 @@
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -19523,7 +19957,7 @@
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -19546,7 +19980,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -20008,7 +20442,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B2:V9">
+  <conditionalFormatting sqref="B2:AA9">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(B2&lt;&gt;0,B2=MAX(IF(B$2:B$9&lt;&gt;0,B$2:B$9)))</formula>
     </cfRule>
@@ -20036,7 +20470,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.705627705627709</v>
+        <v>19.889328063241102</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -20120,11 +20554,11 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -20208,11 +20642,11 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>18.636363636363637</v>
+        <v>18.727272727272727</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -20296,11 +20730,11 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -20387,11 +20821,11 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.90909090909091</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -20478,11 +20912,11 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.818181818181817</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -20566,11 +21000,11 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="P18" t="s">
         <v>3</v>
@@ -20579,7 +21013,7 @@
         <v>36024</v>
       </c>
       <c r="T18">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -20769,7 +21203,7 @@
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
@@ -20789,7 +21223,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P24" t="s">
         <v>0</v>
@@ -20877,7 +21311,7 @@
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
@@ -20897,7 +21331,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>18.727272727272727</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="P27" t="s">
         <v>83</v>
@@ -20985,7 +21419,7 @@
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
@@ -21005,7 +21439,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P30" t="s">
         <v>106</v>
@@ -21093,7 +21527,7 @@
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
@@ -21113,7 +21547,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P33" t="s">
         <v>159</v>
@@ -21201,7 +21635,7 @@
       </c>
       <c r="H36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
@@ -21221,7 +21655,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P36" t="s">
         <v>190</v>
@@ -21309,7 +21743,7 @@
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I39">
         <f t="shared" ca="1" si="12"/>
@@ -21329,7 +21763,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="P39" t="s">
         <v>218</v>
@@ -21417,7 +21851,7 @@
       </c>
       <c r="H42">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I42">
         <f t="shared" ca="1" si="13"/>
@@ -21437,7 +21871,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P42" t="s">
         <v>260</v>
@@ -21525,7 +21959,7 @@
       </c>
       <c r="H45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="14"/>
@@ -21545,7 +21979,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>18.545454545454547</v>
+        <v>18.636363636363637</v>
       </c>
       <c r="P45" t="s">
         <v>278</v>
@@ -21741,7 +22175,7 @@
       </c>
       <c r="H51">
         <f t="shared" ca="1" si="16"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I51">
         <f t="shared" ca="1" si="16"/>
@@ -21761,7 +22195,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P51" t="s">
         <v>293</v>
@@ -21849,7 +22283,7 @@
       </c>
       <c r="H54">
         <f t="shared" ca="1" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I54">
         <f t="shared" ca="1" si="17"/>
@@ -21869,7 +22303,21 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
+      </c>
+      <c r="P54" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>32928</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P55" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>39743</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -21909,6 +22357,12 @@
       <c r="L56" t="s">
         <v>279</v>
       </c>
+      <c r="P56" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>39773</v>
+      </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
@@ -21937,7 +22391,7 @@
       </c>
       <c r="H57">
         <f t="shared" ca="1" si="18"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I57">
         <f t="shared" ca="1" si="18"/>
@@ -21957,7 +22411,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -22025,7 +22479,7 @@
       </c>
       <c r="H60">
         <f t="shared" ca="1" si="19"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I60">
         <f t="shared" ca="1" si="19"/>
@@ -22045,7 +22499,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>22</v>
+        <v>22.09090909090909</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -22113,7 +22567,7 @@
       </c>
       <c r="H63">
         <f t="shared" ca="1" si="20"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I63">
         <f t="shared" ca="1" si="20"/>
@@ -22133,19 +22587,189 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>21.363636363636363</v>
-      </c>
-    </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N66" s="1"/>
-    </row>
-    <row r="69" spans="14:14" x14ac:dyDescent="0.3">
-      <c r="N69" s="1"/>
-    </row>
-    <row r="71" spans="14:14" x14ac:dyDescent="0.3">
+        <v>21.454545454545453</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" t="s">
+        <v>321</v>
+      </c>
+      <c r="E65" t="s">
+        <v>312</v>
+      </c>
+      <c r="F65" t="s">
+        <v>277</v>
+      </c>
+      <c r="G65" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>2</v>
+      </c>
+      <c r="I65" t="s">
+        <v>301</v>
+      </c>
+      <c r="J65" t="s">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s">
+        <v>218</v>
+      </c>
+      <c r="L65" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>36</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>30</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>23</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>23.09090909090909</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C68" t="s">
+        <v>283</v>
+      </c>
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" t="s">
+        <v>330</v>
+      </c>
+      <c r="F68" t="s">
+        <v>322</v>
+      </c>
+      <c r="G68" t="s">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" t="s">
+        <v>280</v>
+      </c>
+      <c r="J68" t="s">
+        <v>82</v>
+      </c>
+      <c r="K68" t="s">
+        <v>260</v>
+      </c>
+      <c r="L68" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>24</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>18.818181818181817</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N71" s="1"/>
     </row>
-    <row r="72" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N72" s="1"/>
     </row>
   </sheetData>
@@ -22160,7 +22784,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -22173,7 +22797,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.142857142857142</v>
+        <v>20.138339920948617</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -22245,7 +22869,7 @@
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
@@ -22261,7 +22885,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -22333,7 +22957,7 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
@@ -22349,7 +22973,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.545454545454547</v>
+        <v>20.636363636363637</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -22685,7 +23309,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="5"/>
@@ -22701,7 +23325,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -22712,7 +23336,7 @@
         <v>38475</v>
       </c>
       <c r="T19">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -22790,7 +23414,7 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
@@ -22806,7 +23430,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -23342,11 +23966,11 @@
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P36" t="s">
         <v>168</v>
@@ -23450,11 +24074,11 @@
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P39" t="s">
         <v>251</v>
@@ -23558,11 +24182,11 @@
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P42" t="s">
         <v>264</v>
@@ -23666,11 +24290,11 @@
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P45" t="s">
         <v>286</v>
@@ -23888,6 +24512,12 @@
         <f ca="1">AVERAGE(B51:M51)</f>
         <v>19.545454545454547</v>
       </c>
+      <c r="P51" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>39845</v>
+      </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -23970,11 +24600,11 @@
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="17"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -24230,7 +24860,7 @@
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="20"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="20"/>
@@ -24238,7 +24868,183 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>198</v>
+      </c>
+      <c r="B65" t="s">
+        <v>251</v>
+      </c>
+      <c r="C65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" t="s">
+        <v>35</v>
+      </c>
+      <c r="F65" t="s">
+        <v>86</v>
+      </c>
+      <c r="G65" t="s">
+        <v>199</v>
+      </c>
+      <c r="H65" t="s">
+        <v>36</v>
+      </c>
+      <c r="I65" t="s">
+        <v>300</v>
+      </c>
+      <c r="J65" t="s">
+        <v>152</v>
+      </c>
+      <c r="K65" t="s">
+        <v>286</v>
+      </c>
+      <c r="L65" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>21</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>19.636363636363637</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>228</v>
+      </c>
+      <c r="B68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" t="s">
+        <v>306</v>
+      </c>
+      <c r="D68" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" t="s">
+        <v>199</v>
+      </c>
+      <c r="H68" t="s">
+        <v>36</v>
+      </c>
+      <c r="I68" t="s">
+        <v>300</v>
+      </c>
+      <c r="J68" t="s">
+        <v>331</v>
+      </c>
+      <c r="K68" t="s">
+        <v>37</v>
+      </c>
+      <c r="L68" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>24</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>19.636363636363637</v>
       </c>
     </row>
   </sheetData>
@@ -24252,7 +25058,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -24263,7 +25069,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.650000000000002</v>
+        <v>19.632231404958677</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24307,7 +25113,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <f ca="1">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24351,7 +25157,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -24395,7 +25201,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <f ca="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24439,7 +25245,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -24483,7 +25289,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <f ca="1">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24527,7 +25333,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -24571,7 +25377,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <f ca="1">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24615,7 +25421,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -24800,7 +25606,7 @@
         <v>38815</v>
       </c>
       <c r="T18">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -25876,8 +26682,22 @@
         <f ca="1">AVERAGE(B48:M48)</f>
         <v>20.181818181818183</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P48" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>36592</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>39692</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -25914,8 +26734,14 @@
       <c r="L50" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>39829</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>22</v>
@@ -25965,7 +26791,7 @@
         <v>19.727272727272727</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>119</v>
       </c>
@@ -26003,7 +26829,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
@@ -26053,7 +26879,7 @@
         <v>20.181818181818183</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>186</v>
       </c>
@@ -26091,7 +26917,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>22</v>
@@ -26141,7 +26967,7 @@
         <v>19.727272727272727</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>207</v>
       </c>
@@ -26179,7 +27005,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>22</v>
@@ -26227,6 +27053,182 @@
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
         <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" t="s">
+        <v>323</v>
+      </c>
+      <c r="C62" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" t="s">
+        <v>157</v>
+      </c>
+      <c r="F62" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" t="s">
+        <v>90</v>
+      </c>
+      <c r="I62" t="s">
+        <v>304</v>
+      </c>
+      <c r="J62" t="s">
+        <v>158</v>
+      </c>
+      <c r="K62" t="s">
+        <v>324</v>
+      </c>
+      <c r="L62" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>26</v>
+      </c>
+      <c r="C63">
+        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ca="1" si="20"/>
+        <v>22</v>
+      </c>
+      <c r="F63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ca="1" si="20"/>
+        <v>17</v>
+      </c>
+      <c r="H63">
+        <f t="shared" ca="1" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="I63">
+        <f t="shared" ca="1" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="J63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="K63">
+        <f t="shared" ca="1" si="20"/>
+        <v>17</v>
+      </c>
+      <c r="L63">
+        <f t="shared" ca="1" si="20"/>
+        <v>19</v>
+      </c>
+      <c r="N63" s="1">
+        <f ca="1">AVERAGE(B63:M63)</f>
+        <v>19.636363636363637</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F65" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65" t="s">
+        <v>90</v>
+      </c>
+      <c r="I65" t="s">
+        <v>257</v>
+      </c>
+      <c r="J65" t="s">
+        <v>236</v>
+      </c>
+      <c r="K65" t="s">
+        <v>324</v>
+      </c>
+      <c r="L65" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="21"/>
+        <v>20</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:M66)</f>
+        <v>18.90909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -26238,7 +27240,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628DC590-5B70-45B7-BCD6-8ED432E7A1AF}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -26247,7 +27249,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>20.984848484848484</v>
+        <v>21.014545454545456</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -26291,11 +27293,11 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3">
-        <f ca="1">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B3:L3" ca="1" si="0">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
       <c r="D3">
@@ -26383,11 +27385,11 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
-        <f ca="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B6:L6" ca="1" si="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="1"/>
         <v>20</v>
       </c>
       <c r="D6">
@@ -26475,11 +27477,11 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
-        <f ca="1">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B9:L9" ca="1" si="2">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="2"/>
         <v>20</v>
       </c>
       <c r="D9">
@@ -26567,11 +27569,11 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
-        <f ca="1">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B12:L12" ca="1" si="3">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="3"/>
         <v>20</v>
       </c>
       <c r="D12">
@@ -26656,11 +27658,11 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
-        <f ca="1">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B15:L15" ca="1" si="4">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="4"/>
         <v>20</v>
       </c>
       <c r="D15">
@@ -26745,11 +27747,11 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
-        <f ca="1">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B18:L18" ca="1" si="5">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="5"/>
         <v>20</v>
       </c>
       <c r="D18">
@@ -26799,7 +27801,7 @@
         <v>38482</v>
       </c>
       <c r="T18">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -26857,11 +27859,11 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
-        <f ca="1">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B21:L21" ca="1" si="6">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="6"/>
         <v>21</v>
       </c>
       <c r="D21">
@@ -26966,11 +27968,11 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
-        <f ca="1">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B24:L24" ca="1" si="7">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C24">
-        <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="7"/>
         <v>21</v>
       </c>
       <c r="D24">
@@ -27075,11 +28077,11 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
-        <f ca="1">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B27:L27" ca="1" si="8">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C27">
-        <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="8"/>
         <v>20</v>
       </c>
       <c r="D27">
@@ -27293,11 +28295,11 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
-        <f ca="1">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B33:L33" ca="1" si="10">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C33">
-        <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="10"/>
         <v>20</v>
       </c>
       <c r="D33">
@@ -27402,11 +28404,11 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
-        <f ca="1">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B36:L36" ca="1" si="11">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C36">
-        <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="11"/>
         <v>20</v>
       </c>
       <c r="D36">
@@ -27511,11 +28513,11 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
-        <f ca="1">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B39:L39" ca="1" si="12">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C39">
-        <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="12"/>
         <v>21</v>
       </c>
       <c r="D39">
@@ -27620,11 +28622,11 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
-        <f ca="1">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B42:L42" ca="1" si="13">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C42">
-        <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="13"/>
         <v>21</v>
       </c>
       <c r="D42">
@@ -27729,11 +28731,11 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
-        <f ca="1">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B45:L45" ca="1" si="14">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C45">
-        <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="14"/>
         <v>21</v>
       </c>
       <c r="D45">
@@ -27838,11 +28840,11 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
-        <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B48:L48" ca="1" si="15">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C48">
-        <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="15"/>
         <v>21</v>
       </c>
       <c r="D48">
@@ -27947,11 +28949,11 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
-        <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B51:L51" ca="1" si="16">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C51">
-        <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="16"/>
         <v>18</v>
       </c>
       <c r="D51">
@@ -28036,11 +29038,11 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
-        <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B54:L54" ca="1" si="17">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C54">
-        <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="17"/>
         <v>18</v>
       </c>
       <c r="D54">
@@ -28125,11 +29127,11 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
-        <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B57:L57" ca="1" si="18">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C57">
-        <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="18"/>
         <v>18</v>
       </c>
       <c r="D57">
@@ -28214,11 +29216,11 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
-        <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B60:L60" ca="1" si="19">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C60">
-        <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="19"/>
         <v>19</v>
       </c>
       <c r="D60">
@@ -28303,11 +29305,11 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
-        <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B63:L63" ca="1" si="20">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C63">
-        <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="20"/>
         <v>19</v>
       </c>
       <c r="D63">
@@ -28392,11 +29394,11 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B66">
-        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B66:L66" ca="1" si="21">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>20</v>
       </c>
       <c r="C66">
-        <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="21"/>
         <v>19</v>
       </c>
       <c r="D66">
@@ -28481,11 +29483,11 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B69">
-        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B69:L69" ca="1" si="22">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
       </c>
       <c r="C69">
-        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="22"/>
         <v>19</v>
       </c>
       <c r="D69">
@@ -28570,11 +29572,11 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B72">
-        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ref="B72:L72" ca="1" si="23">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
       </c>
       <c r="C72">
-        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <f t="shared" ca="1" si="23"/>
         <v>19</v>
       </c>
       <c r="D72">
@@ -28616,6 +29618,95 @@
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:M72)</f>
         <v>21.181818181818183</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>203</v>
+      </c>
+      <c r="B74" t="s">
+        <v>317</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" t="s">
+        <v>38</v>
+      </c>
+      <c r="E74" t="s">
+        <v>319</v>
+      </c>
+      <c r="F74" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" t="s">
+        <v>318</v>
+      </c>
+      <c r="H74" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" t="s">
+        <v>241</v>
+      </c>
+      <c r="K74" t="s">
+        <v>271</v>
+      </c>
+      <c r="L74" t="s">
+        <v>287</v>
+      </c>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f t="shared" ref="B75:L75" ca="1" si="24">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>36</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>28</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>21.727272727272727</v>
       </c>
     </row>
   </sheetData>
@@ -28627,7 +29718,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -28637,7 +29728,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.98268398268398</v>
+        <v>21.003952569169957</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -29174,7 +30265,7 @@
         <v>37152</v>
       </c>
       <c r="T18">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -30649,7 +31740,7 @@
         <v>175</v>
       </c>
       <c r="I62" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="J62" t="s">
         <v>95</v>
@@ -30709,6 +31800,182 @@
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:L63)</f>
         <v>21.09090909090909</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>238</v>
+      </c>
+      <c r="D65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>265</v>
+      </c>
+      <c r="F65" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" t="s">
+        <v>184</v>
+      </c>
+      <c r="I65" t="s">
+        <v>250</v>
+      </c>
+      <c r="J65" t="s">
+        <v>95</v>
+      </c>
+      <c r="K65" t="s">
+        <v>313</v>
+      </c>
+      <c r="L65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <f t="shared" ref="C66:L66" ca="1" si="22">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D66">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="G66">
+        <f t="shared" ca="1" si="22"/>
+        <v>25</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ca="1" si="22"/>
+        <v>25</v>
+      </c>
+      <c r="I66">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="J66">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="K66">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="L66">
+        <f t="shared" ca="1" si="22"/>
+        <v>21</v>
+      </c>
+      <c r="N66" s="1">
+        <f ca="1">AVERAGE(B66:L66)</f>
+        <v>21.454545454545453</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>191</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" t="s">
+        <v>265</v>
+      </c>
+      <c r="F68" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" t="s">
+        <v>250</v>
+      </c>
+      <c r="J68" t="s">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s">
+        <v>111</v>
+      </c>
+      <c r="L68" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="23">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="23"/>
+        <v>25</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="23"/>
+        <v>25</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="23"/>
+        <v>22</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:L69)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -30722,7 +31989,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D88D7D6-4932-46BC-9430-8F20DDAB89DF}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -30734,7 +32001,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.450757575757574</v>
+        <v>19.47902097902098</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -30806,7 +32073,7 @@
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
@@ -30822,7 +32089,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -30894,7 +32161,7 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
@@ -30910,7 +32177,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -31222,7 +32489,7 @@
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
@@ -31262,7 +32529,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P18" t="s">
         <v>47</v>
@@ -31271,7 +32538,7 @@
         <v>38672</v>
       </c>
       <c r="T18">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -31333,7 +32600,7 @@
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="6"/>
@@ -31373,7 +32640,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P21" t="s">
         <v>45</v>
@@ -31441,7 +32708,7 @@
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="7"/>
@@ -31481,7 +32748,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P24" t="s">
         <v>44</v>
@@ -31549,7 +32816,7 @@
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="8"/>
@@ -31589,7 +32856,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.818181818181817</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="P27" t="s">
         <v>54</v>
@@ -32477,7 +33744,7 @@
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H54">
         <f t="shared" ca="1" si="17"/>
@@ -32501,7 +33768,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
@@ -32565,7 +33832,7 @@
       </c>
       <c r="G57">
         <f t="shared" ca="1" si="18"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H57">
         <f t="shared" ca="1" si="18"/>
@@ -32589,7 +33856,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>18.454545454545453</v>
+        <v>18.545454545454547</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -32653,7 +33920,7 @@
       </c>
       <c r="G60">
         <f t="shared" ca="1" si="19"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60">
         <f t="shared" ca="1" si="19"/>
@@ -32677,7 +33944,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>18.454545454545453</v>
+        <v>18.545454545454547</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -32742,7 +34009,7 @@
       </c>
       <c r="G63">
         <f t="shared" ca="1" si="20"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63">
         <f t="shared" ca="1" si="20"/>
@@ -32766,7 +34033,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>18.818181818181817</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="O63" s="1"/>
     </row>
@@ -32831,7 +34098,7 @@
       </c>
       <c r="G66">
         <f t="shared" ca="1" si="21"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H66">
         <f t="shared" ca="1" si="21"/>
@@ -32855,7 +34122,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>19</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -33007,7 +34274,7 @@
       </c>
       <c r="G72">
         <f t="shared" ca="1" si="23"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H72">
         <f t="shared" ca="1" si="23"/>
@@ -33031,11 +34298,184 @@
       </c>
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:M72)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N74"/>
+      <c r="A74" t="s">
+        <v>177</v>
+      </c>
+      <c r="B74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" t="s">
+        <v>180</v>
+      </c>
+      <c r="D74" t="s">
+        <v>52</v>
+      </c>
+      <c r="E74" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" t="s">
+        <v>268</v>
+      </c>
+      <c r="G74" t="s">
+        <v>289</v>
+      </c>
+      <c r="H74" t="s">
+        <v>162</v>
+      </c>
+      <c r="I74" t="s">
+        <v>44</v>
+      </c>
+      <c r="J74" t="s">
+        <v>288</v>
+      </c>
+      <c r="K74" t="s">
+        <v>232</v>
+      </c>
+      <c r="L74" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>22</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>55</v>
+      </c>
+      <c r="B77" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77" t="s">
+        <v>52</v>
+      </c>
+      <c r="E77" t="s">
+        <v>54</v>
+      </c>
+      <c r="F77" t="s">
+        <v>268</v>
+      </c>
+      <c r="G77" t="s">
+        <v>48</v>
+      </c>
+      <c r="H77" t="s">
+        <v>162</v>
+      </c>
+      <c r="I77" t="s">
+        <v>316</v>
+      </c>
+      <c r="J77" t="s">
+        <v>288</v>
+      </c>
+      <c r="K77" t="s">
+        <v>232</v>
+      </c>
+      <c r="L77" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>22</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>19.272727272727273</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -33046,7 +34486,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03A6E26-4348-4BD7-A4C3-5653B1514462}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -33059,7 +34499,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.490118577075094</v>
+        <v>19.541818181818183</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -33602,7 +35042,7 @@
         <v>39078</v>
       </c>
       <c r="T18">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -33697,7 +35137,7 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
@@ -33705,7 +35145,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P21" t="s">
         <v>62</v>
@@ -33806,7 +35246,7 @@
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
@@ -33814,7 +35254,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P24" t="s">
         <v>99</v>
@@ -33915,7 +35355,7 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
@@ -33923,7 +35363,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P27" t="s">
         <v>61</v>
@@ -34024,7 +35464,7 @@
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="9"/>
@@ -34032,7 +35472,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P30" t="s">
         <v>115</v>
@@ -34133,7 +35573,7 @@
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="10"/>
@@ -34141,7 +35581,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P33" t="s">
         <v>205</v>
@@ -34242,7 +35682,7 @@
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="11"/>
@@ -34250,7 +35690,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P36" t="s">
         <v>212</v>
@@ -34351,7 +35791,7 @@
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
@@ -34359,7 +35799,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P39" t="s">
         <v>213</v>
@@ -34460,7 +35900,7 @@
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
@@ -34468,7 +35908,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.363636363636363</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P42" t="s">
         <v>258</v>
@@ -34569,7 +36009,7 @@
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
@@ -34577,7 +36017,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P45" t="s">
         <v>274</v>
@@ -34678,7 +36118,7 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="15"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="15"/>
@@ -34686,7 +36126,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P48" t="s">
         <v>298</v>
@@ -34777,11 +36217,11 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="16"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="16"/>
@@ -34789,7 +36229,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:L51)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -34870,7 +36310,7 @@
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="17"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="17"/>
@@ -34878,7 +36318,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:L54)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -35032,7 +36472,7 @@
       </c>
       <c r="G60">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H60">
         <f t="shared" ca="1" si="19"/>
@@ -35056,7 +36496,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:L60)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -35121,11 +36561,11 @@
       </c>
       <c r="G63">
         <f t="shared" ca="1" si="20"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H63">
         <f t="shared" ca="1" si="20"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I63">
         <f t="shared" ca="1" si="20"/>
@@ -35145,7 +36585,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:L63)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -35210,7 +36650,7 @@
       </c>
       <c r="G66">
         <f t="shared" ca="1" si="21"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H66">
         <f t="shared" ca="1" si="21"/>
@@ -35234,7 +36674,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:L66)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -35327,10 +36767,182 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>213</v>
+      </c>
+      <c r="D71" t="s">
+        <v>246</v>
+      </c>
+      <c r="E71" t="s">
+        <v>100</v>
+      </c>
+      <c r="F71" t="s">
+        <v>290</v>
+      </c>
+      <c r="G71" t="s">
+        <v>72</v>
+      </c>
+      <c r="H71" t="s">
+        <v>62</v>
+      </c>
+      <c r="I71" t="s">
+        <v>146</v>
+      </c>
+      <c r="J71" t="s">
+        <v>206</v>
+      </c>
+      <c r="K71" t="s">
+        <v>273</v>
+      </c>
+      <c r="L71" t="s">
+        <v>61</v>
+      </c>
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N72" s="1"/>
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:L72)</f>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74" t="s">
+        <v>213</v>
+      </c>
+      <c r="D74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" t="s">
+        <v>100</v>
+      </c>
+      <c r="F74" t="s">
+        <v>290</v>
+      </c>
+      <c r="G74" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" t="s">
+        <v>62</v>
+      </c>
+      <c r="I74" t="s">
+        <v>299</v>
+      </c>
+      <c r="J74" t="s">
+        <v>206</v>
+      </c>
+      <c r="K74" t="s">
+        <v>273</v>
+      </c>
+      <c r="L74" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="1"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:L75)</f>
+        <v>19.454545454545453</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6637" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53BE24C3-7F27-4ACA-8649-E6D1BC3D3F7F}"/>
+  <xr:revisionPtr revIDLastSave="6952" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8A3306-9951-43F9-8623-F88F47F5CE86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Gesamtübersicht" sheetId="6" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="349">
   <si>
     <t>Scholl</t>
   </si>
@@ -1070,6 +1070,54 @@
   <si>
     <t>Mahop</t>
   </si>
+  <si>
+    <t>Ivkovic</t>
+  </si>
+  <si>
+    <t>de Man</t>
+  </si>
+  <si>
+    <t>Grgic</t>
+  </si>
+  <si>
+    <t>Goiginger</t>
+  </si>
+  <si>
+    <t>Wimmer</t>
+  </si>
+  <si>
+    <t>Jindra</t>
+  </si>
+  <si>
+    <t>28. Spieltag</t>
+  </si>
+  <si>
+    <t>29. Spieltag</t>
+  </si>
+  <si>
+    <t>30. Spieltag</t>
+  </si>
+  <si>
+    <t>27. Spieltag</t>
+  </si>
+  <si>
+    <t>Mellberg</t>
+  </si>
+  <si>
+    <t>Nsumbu</t>
+  </si>
+  <si>
+    <t>Petritsch</t>
+  </si>
+  <si>
+    <t>Haas</t>
+  </si>
+  <si>
+    <t>Matjasec</t>
+  </si>
+  <si>
+    <t>Masching</t>
+  </si>
 </sst>
 </file>
 
@@ -1343,7 +1391,7 @@
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>19.454545454545453</c:v>
@@ -1352,13 +1400,16 @@
                   <c:v>22.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>21.454545454545453</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>23.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>18.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1624,55 +1675,55 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>20.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>19.181818181818183</c:v>
@@ -1681,16 +1732,19 @@
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1946,31 +2000,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -1988,19 +2042,19 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2255,64 +2309,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>21.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.727272727272727</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21.818181818181817</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2598,7 +2652,7 @@
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>20.636363636363637</c:v>
@@ -2899,79 +2953,79 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.272727272727273</c:v>
+                <c:pt idx="30">
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                <c:pt idx="33">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="36">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="39">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="42">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>19.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="45">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>19.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="58">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="59">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3236,28 +3290,28 @@
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
@@ -3272,31 +3326,31 @@
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3556,7 +3610,7 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
@@ -3568,16 +3622,16 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>21.272727272727273</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
@@ -3586,37 +3640,37 @@
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
                   <c:v>21.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
                   <c:v>20.363636363636363</c:v>
@@ -3892,31 +3946,31 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>19.09090909090909</c:v>
+                  <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>18.636363636363637</c:v>
@@ -3934,19 +3988,19 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4231,28 +4285,28 @@
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
@@ -4267,31 +4321,31 @@
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
                   <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
+                  <c:v>19.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="0.00">
                   <c:v>19.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="57" formatCode="0.00">
-                  <c:v>19.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4573,7 +4627,7 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00">
                   <c:v>20.545454545454547</c:v>
@@ -4585,16 +4639,16 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00">
-                  <c:v>21.272727272727273</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00">
-                  <c:v>21.636363636363637</c:v>
+                  <c:v>21.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00">
                   <c:v>21.09090909090909</c:v>
@@ -4603,37 +4657,37 @@
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00">
                   <c:v>21.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00">
-                  <c:v>20.727272727272727</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00">
                   <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00">
-                  <c:v>20.90909090909091</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00">
                   <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00">
-                  <c:v>21.09090909090909</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00">
                   <c:v>20.363636363636363</c:v>
@@ -4921,55 +4975,55 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.636363636363637</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>20.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.363636363636363</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.727272727272727</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>20.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>20.363636363636363</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
+                  <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.545454545454547</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>19.181818181818183</c:v>
@@ -4978,16 +5032,19 @@
                   <c:v>19.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>20.181818181818183</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.818181818181817</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5286,64 +5343,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>20.545454545454547</c:v>
+                  <c:v>20.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.818181818181817</c:v>
+                  <c:v>21.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>21</c:v>
+                  <c:v>21.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21</c:v>
+                  <c:v>21.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.636363636363637</c:v>
+                  <c:v>20.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.90909090909091</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.454545454545453</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>21.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.636363636363637</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21.545454545454547</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>21.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>21.181818181818183</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>20.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>21.181818181818183</c:v>
+                  <c:v>21.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21.727272727272727</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21.818181818181817</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5649,7 +5706,7 @@
                   <c:v>20.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21</c:v>
+                  <c:v>21.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>20.636363636363637</c:v>
@@ -5971,79 +6028,79 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20.454545454545453</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20.272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.90909090909091</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>20.09090909090909</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>20.272727272727273</c:v>
+                <c:pt idx="30">
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>20.272727272727273</c:v>
+                <c:pt idx="33">
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.09090909090909</c:v>
+                <c:pt idx="36">
+                  <c:v>19.454545454545453</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="39">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>20.09090909090909</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="42">
                   <c:v>19.727272727272727</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>19.818181818181817</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>19.90909090909091</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>19.545454545454547</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>19.272727272727273</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>19.727272727272727</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>19.454545454545453</c:v>
-                </c:pt>
                 <c:pt idx="45">
-                  <c:v>19.454545454545453</c:v>
+                  <c:v>19.636363636363637</c:v>
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>19.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.09090909090909</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>18.545454545454547</c:v>
+                  <c:v>18.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>18.90909090909091</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>19.363636363636363</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>19.09090909090909</c:v>
                 </c:pt>
-                <c:pt idx="58">
-                  <c:v>18.727272727272727</c:v>
-                </c:pt>
                 <c:pt idx="59">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.545454545454547</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16243,29 +16300,29 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="5">
-        <f ca="1">Rapid!N1</f>
-        <v>19.47902097902098</v>
+        <f ca="1">Liefering!N1</f>
+        <v>19.561128526645771</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B3" s="5">
-        <f ca="1">Liefering!N1</f>
-        <v>19.541818181818183</v>
+        <f ca="1">'Altach Juniors'!N1</f>
+        <v>19.690909090909095</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B4" s="5">
-        <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.632231404958677</v>
+        <f ca="1">Rapid!N1</f>
+        <v>19.70846394984326</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -16274,7 +16331,7 @@
       </c>
       <c r="B5" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.889328063241102</v>
+        <v>19.83164983164983</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16283,7 +16340,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.138339920948617</v>
+        <v>20.144781144781145</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -16292,7 +16349,7 @@
       </c>
       <c r="B7" s="5">
         <f ca="1">Sturm!N1</f>
-        <v>20.832167832167833</v>
+        <v>20.806060606060608</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -16301,7 +16358,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>21.003952569169957</v>
+        <v>20.98951048951049</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -16310,7 +16367,7 @@
       </c>
       <c r="B9" s="5">
         <f ca="1">'Young Violets'!N1</f>
-        <v>21.014545454545456</v>
+        <v>21.169278996865202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -16337,7 +16394,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{706DFA24-3406-41A0-A4BC-C12C2626EFAE}">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -16347,7 +16404,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.832167832167833</v>
+        <v>20.806060606060608</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -16602,7 +16659,7 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -16614,7 +16671,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -16890,7 +16947,7 @@
         <v>38998</v>
       </c>
       <c r="T18">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -16977,7 +17034,7 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
@@ -16993,7 +17050,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>21.272727272727273</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="P21" t="s">
         <v>57</v>
@@ -17082,7 +17139,7 @@
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
@@ -17102,7 +17159,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="P24" t="s">
         <v>76</v>
@@ -17191,7 +17248,7 @@
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
@@ -17211,7 +17268,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="P27" t="s">
         <v>70</v>
@@ -17300,7 +17357,7 @@
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
@@ -17320,7 +17377,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P30" t="s">
         <v>118</v>
@@ -17623,7 +17680,7 @@
       </c>
       <c r="G39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H39">
         <f t="shared" ca="1" si="12"/>
@@ -17647,7 +17704,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P39" t="s">
         <v>200</v>
@@ -17857,7 +17914,7 @@
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
@@ -17865,7 +17922,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P45" t="s">
         <v>291</v>
@@ -17966,7 +18023,7 @@
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="15"/>
@@ -17974,7 +18031,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P48" t="s">
         <v>308</v>
@@ -17983,7 +18040,15 @@
         <v>39860</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P49" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>38739</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -18021,8 +18086,14 @@
         <v>101</v>
       </c>
       <c r="N50" s="1"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="P50" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>39206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>22</v>
@@ -18061,7 +18132,7 @@
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="16"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="16"/>
@@ -18069,10 +18140,16 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.636363636363637</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20.727272727272727</v>
+      </c>
+      <c r="P51" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>39363</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>231</v>
       </c>
@@ -18111,7 +18188,7 @@
       </c>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -18150,7 +18227,7 @@
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="17"/>
@@ -18158,10 +18235,10 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>20.727272727272727</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+        <v>20.818181818181817</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>181</v>
       </c>
@@ -18200,7 +18277,7 @@
       </c>
       <c r="N56" s="1"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -18239,7 +18316,7 @@
       </c>
       <c r="K57">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L57">
         <f t="shared" ca="1" si="18"/>
@@ -18247,10 +18324,10 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>20.90909090909091</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>51</v>
       </c>
@@ -18289,7 +18366,7 @@
       </c>
       <c r="N59" s="1"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -18339,7 +18416,7 @@
         <v>20.818181818181817</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -18378,7 +18455,7 @@
       </c>
       <c r="N62" s="1"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
         <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -18417,7 +18494,7 @@
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="20"/>
@@ -18425,7 +18502,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -18595,7 +18672,7 @@
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="22"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L69">
         <f t="shared" ca="1" si="22"/>
@@ -18603,7 +18680,7 @@
       </c>
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:M69)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -18871,6 +18948,362 @@
       <c r="N78" s="1">
         <f ca="1">AVERAGE(B78:M78)</f>
         <v>20.545454545454547</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" t="s">
+        <v>200</v>
+      </c>
+      <c r="D80" t="s">
+        <v>117</v>
+      </c>
+      <c r="E80" t="s">
+        <v>74</v>
+      </c>
+      <c r="F80" t="s">
+        <v>335</v>
+      </c>
+      <c r="G80" t="s">
+        <v>201</v>
+      </c>
+      <c r="H80" t="s">
+        <v>308</v>
+      </c>
+      <c r="I80" t="s">
+        <v>65</v>
+      </c>
+      <c r="J80" t="s">
+        <v>173</v>
+      </c>
+      <c r="K80" t="s">
+        <v>57</v>
+      </c>
+      <c r="L80" t="s">
+        <v>101</v>
+      </c>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>26</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>17</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>22</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>26</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:M81)</f>
+        <v>20.818181818181817</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>203</v>
+      </c>
+      <c r="B83" t="s">
+        <v>116</v>
+      </c>
+      <c r="C83" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" t="s">
+        <v>117</v>
+      </c>
+      <c r="E83" t="s">
+        <v>74</v>
+      </c>
+      <c r="F83" t="s">
+        <v>294</v>
+      </c>
+      <c r="G83" t="s">
+        <v>201</v>
+      </c>
+      <c r="H83" t="s">
+        <v>308</v>
+      </c>
+      <c r="I83" t="s">
+        <v>65</v>
+      </c>
+      <c r="J83" t="s">
+        <v>66</v>
+      </c>
+      <c r="K83" t="s">
+        <v>57</v>
+      </c>
+      <c r="L83" t="s">
+        <v>101</v>
+      </c>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f ca="1">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ref="C84:L84" ca="1" si="27">DATEDIF(VLOOKUP(C83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>22</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:M84)</f>
+        <v>20.636363636363637</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" t="s">
+        <v>291</v>
+      </c>
+      <c r="C86" t="s">
+        <v>117</v>
+      </c>
+      <c r="D86" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" t="s">
+        <v>308</v>
+      </c>
+      <c r="F86" t="s">
+        <v>344</v>
+      </c>
+      <c r="G86" t="s">
+        <v>294</v>
+      </c>
+      <c r="H86" t="s">
+        <v>345</v>
+      </c>
+      <c r="I86" t="s">
+        <v>101</v>
+      </c>
+      <c r="J86" t="s">
+        <v>65</v>
+      </c>
+      <c r="K86" t="s">
+        <v>66</v>
+      </c>
+      <c r="L86" t="s">
+        <v>57</v>
+      </c>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <f ca="1">DATEDIF(VLOOKUP(B86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C87">
+        <f t="shared" ref="C87:L87" ca="1" si="28">DATEDIF(VLOOKUP(C86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="E87">
+        <f t="shared" ca="1" si="28"/>
+        <v>17</v>
+      </c>
+      <c r="F87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="G87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="H87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="I87">
+        <f t="shared" ca="1" si="28"/>
+        <v>26</v>
+      </c>
+      <c r="J87">
+        <f t="shared" ca="1" si="28"/>
+        <v>22</v>
+      </c>
+      <c r="K87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="L87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="1">
+        <f ca="1">AVERAGE(B87:M87)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" t="s">
+        <v>74</v>
+      </c>
+      <c r="E89" t="s">
+        <v>308</v>
+      </c>
+      <c r="F89" t="s">
+        <v>344</v>
+      </c>
+      <c r="G89" t="s">
+        <v>294</v>
+      </c>
+      <c r="H89" t="s">
+        <v>335</v>
+      </c>
+      <c r="I89" t="s">
+        <v>101</v>
+      </c>
+      <c r="J89" t="s">
+        <v>65</v>
+      </c>
+      <c r="K89" t="s">
+        <v>66</v>
+      </c>
+      <c r="L89" t="s">
+        <v>18</v>
+      </c>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B90">
+        <f ca="1">DATEDIF(VLOOKUP(B89,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C90">
+        <f t="shared" ref="C90:L90" ca="1" si="29">DATEDIF(VLOOKUP(C89,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D90">
+        <f t="shared" ca="1" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="E90">
+        <f t="shared" ca="1" si="29"/>
+        <v>17</v>
+      </c>
+      <c r="F90">
+        <f t="shared" ca="1" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="G90">
+        <f t="shared" ca="1" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="H90">
+        <f t="shared" ca="1" si="29"/>
+        <v>20</v>
+      </c>
+      <c r="I90">
+        <f t="shared" ca="1" si="29"/>
+        <v>26</v>
+      </c>
+      <c r="J90">
+        <f t="shared" ca="1" si="29"/>
+        <v>22</v>
+      </c>
+      <c r="K90">
+        <f t="shared" ca="1" si="29"/>
+        <v>20</v>
+      </c>
+      <c r="L90">
+        <f t="shared" ca="1" si="29"/>
+        <v>23</v>
+      </c>
+      <c r="N90" s="1">
+        <f ca="1">AVERAGE(B90:M90)</f>
+        <v>20.181818181818183</v>
       </c>
     </row>
   </sheetData>
@@ -18881,7 +19314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A980021B-B36B-4907-BAF3-C28A440CD06D}">
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -18890,7 +19323,7 @@
     <col min="23" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>125</v>
       </c>
@@ -18969,8 +19402,20 @@
       <c r="AA1" s="7" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB1" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>33</v>
       </c>
@@ -19044,7 +19489,7 @@
       </c>
       <c r="S2" s="8" cm="1">
         <f t="array" aca="1" ref="S2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="T2" s="8" cm="1">
         <f t="array" aca="1" ref="T2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -19056,7 +19501,7 @@
       </c>
       <c r="V2" s="8" cm="1">
         <f t="array" aca="1" ref="V2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="W2" s="8" cm="1">
         <f t="array" aca="1" ref="W2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -19068,68 +19513,84 @@
       </c>
       <c r="Y2" s="8" cm="1">
         <f t="array" aca="1" ref="Y2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="Z2" s="8" cm="1">
         <f t="array" aca="1" ref="Z2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="AA2" s="8" cm="1">
         <f t="array" aca="1" ref="AA2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.727272727272727</v>
+      </c>
+      <c r="AB2" s="8" cm="1">
+        <f t="array" aca="1" ref="AB2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19</v>
+      </c>
+      <c r="AC2" s="8" cm="1">
+        <f t="array" aca="1" ref="AC2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD2" s="8" cm="1">
+        <f t="array" aca="1" ref="AD2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AE2" s="8" cm="1">
+        <f t="array" aca="1" ref="AE2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="8" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="C3" s="8" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="D3" s="8" cm="1">
         <f t="array" aca="1" ref="D3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="E3" s="8" cm="1">
         <f t="array" aca="1" ref="E3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="F3" s="8" cm="1">
         <f t="array" aca="1" ref="F3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="G3" s="8" cm="1">
         <f t="array" aca="1" ref="G3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="H3" s="8" cm="1">
         <f t="array" aca="1" ref="H3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" aca="1" ref="I3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="J3" s="8" cm="1">
         <f t="array" aca="1" ref="J3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="K3" s="8" cm="1">
         <f t="array" aca="1" ref="K3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="L3" s="8" cm="1">
         <f t="array" aca="1" ref="L3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="M3" s="8" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19137,19 +19598,19 @@
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P3" s="8" cm="1">
         <f t="array" aca="1" ref="P3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="Q3" s="8" cm="1">
         <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19161,40 +19622,56 @@
       </c>
       <c r="U3" s="8" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="V3" s="8" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="W3" s="8" cm="1">
         <f t="array" aca="1" ref="W3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="X3" s="8" cm="1">
         <f t="array" aca="1" ref="X3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="Y3" s="8" cm="1">
         <f t="array" aca="1" ref="Y3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="Z3" s="8" cm="1">
         <f t="array" aca="1" ref="Z3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="AA3" s="8" cm="1">
         <f t="array" aca="1" ref="AA3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.181818181818183</v>
+      </c>
+      <c r="AB3" s="8" cm="1">
+        <f t="array" aca="1" ref="AB3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.636363636363637</v>
+      </c>
+      <c r="AC3" s="8" cm="1">
+        <f t="array" aca="1" ref="AC3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD3" s="8" cm="1">
+        <f t="array" aca="1" ref="AD3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="8" cm="1">
+        <f t="array" aca="1" ref="AE3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>124</v>
       </c>
       <c r="B4" s="5" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
       <c r="C4" s="5" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19202,31 +19679,31 @@
       </c>
       <c r="D4" s="5" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="E4" s="5" cm="1">
         <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="F4" s="5" cm="1">
         <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="G4" s="5" cm="1">
         <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="H4" s="5" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="I4" s="5" cm="1">
         <f t="array" aca="1" ref="I4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="J4" s="5" cm="1">
         <f t="array" aca="1" ref="J4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="K4" s="5" cm="1">
         <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19250,15 +19727,15 @@
       </c>
       <c r="P4" s="5" cm="1">
         <f t="array" aca="1" ref="P4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="Q4" s="5" cm="1">
         <f t="array" aca="1" ref="Q4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="R4" s="5" cm="1">
         <f t="array" aca="1" ref="R4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="S4" s="5" cm="1">
         <f t="array" aca="1" ref="S4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19266,11 +19743,11 @@
       </c>
       <c r="T4" s="5" cm="1">
         <f t="array" aca="1" ref="T4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="U4" s="5" cm="1">
         <f t="array" aca="1" ref="U4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="V4" s="5" cm="1">
         <f t="array" aca="1" ref="V4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19282,131 +19759,163 @@
       </c>
       <c r="X4" s="5" cm="1">
         <f t="array" aca="1" ref="X4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="Y4" s="5" cm="1">
         <f t="array" aca="1" ref="Y4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="Z4" s="5" cm="1">
         <f t="array" aca="1" ref="Z4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="AA4" s="5" cm="1">
         <f t="array" aca="1" ref="AA4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB4" s="5" cm="1">
+        <f t="array" aca="1" ref="AB4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="5" cm="1">
+        <f t="array" aca="1" ref="AC4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5" cm="1">
+        <f t="array" aca="1" ref="AD4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5" cm="1">
+        <f t="array" aca="1" ref="AE4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="5" cm="1">
         <f t="array" aca="1" ref="B5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.545454545454547</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="C5" s="5" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="D5" s="5" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="E5" s="5" cm="1">
         <f t="array" aca="1" ref="E5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.818181818181817</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="F5" s="5" cm="1">
         <f t="array" aca="1" ref="F5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="G5" s="5" cm="1">
         <f t="array" aca="1" ref="G5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="H5" s="5" cm="1">
         <f t="array" aca="1" ref="H5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="I5" s="5" cm="1">
         <f t="array" aca="1" ref="I5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="J5" s="5" cm="1">
         <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="K5" s="5" cm="1">
         <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="L5" s="5" cm="1">
         <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="M5" s="5" cm="1">
         <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="N5" s="5" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="O5" s="5" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.272727272727273</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="P5" s="5" cm="1">
         <f t="array" aca="1" ref="P5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.272727272727273</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="Q5" s="5" cm="1">
         <f t="array" aca="1" ref="Q5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.272727272727273</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="R5" s="5" cm="1">
         <f t="array" aca="1" ref="R5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="S5" s="5" cm="1">
         <f t="array" aca="1" ref="S5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="T5" s="5" cm="1">
         <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.727272727272727</v>
+        <v>22</v>
       </c>
       <c r="U5" s="5" cm="1">
         <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.818181818181817</v>
+        <v>22</v>
       </c>
       <c r="V5" s="5" cm="1">
         <f t="array" aca="1" ref="V5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.818181818181817</v>
+        <v>22</v>
       </c>
       <c r="W5" s="5" cm="1">
         <f t="array" aca="1" ref="W5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.90909090909091</v>
+        <v>22.181818181818183</v>
       </c>
       <c r="X5" s="5" cm="1">
         <f t="array" aca="1" ref="X5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="Y5" s="5" cm="1">
         <f t="array" aca="1" ref="Y5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="Z5" s="5" cm="1">
         <f t="array" aca="1" ref="Z5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.727272727272727</v>
+        <v>21.90909090909091</v>
       </c>
       <c r="AA5" s="5" cm="1">
         <f t="array" aca="1" ref="AA5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.363636363636363</v>
+      </c>
+      <c r="AB5" s="5" cm="1">
+        <f t="array" aca="1" ref="AB5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.272727272727273</v>
+      </c>
+      <c r="AC5" s="5" cm="1">
+        <f t="array" aca="1" ref="AC5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.727272727272727</v>
+      </c>
+      <c r="AD5" s="5" cm="1">
+        <f t="array" aca="1" ref="AD5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
+        <v>21.272727272727273</v>
+      </c>
+      <c r="AE5" s="5" cm="1">
+        <f t="array" aca="1" ref="AE5" ca="1">INDIRECT("'Young Violets'!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -19452,7 +19961,7 @@
       </c>
       <c r="L6" s="5" cm="1">
         <f t="array" aca="1" ref="L6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="M6" s="5" cm="1">
         <f t="array" aca="1" ref="M6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -19504,84 +20013,100 @@
       </c>
       <c r="Y6" s="5" cm="1">
         <f t="array" aca="1" ref="Y6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="Z6" s="5" cm="1">
         <f t="array" aca="1" ref="Z6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="AA6" s="5" cm="1">
         <f t="array" aca="1" ref="AA6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.818181818181817</v>
+      </c>
+      <c r="AB6" s="5" cm="1">
+        <f t="array" aca="1" ref="AB6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AC6" s="5" cm="1">
+        <f t="array" aca="1" ref="AC6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5" cm="1">
+        <f t="array" aca="1" ref="AD6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5" cm="1">
+        <f t="array" aca="1" ref="AE6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="5" cm="1">
         <f t="array" aca="1" ref="B7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="D7" s="5" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="E7" s="5" cm="1">
         <f t="array" aca="1" ref="E7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="F7" s="5" cm="1">
         <f t="array" aca="1" ref="F7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="G7" s="5" cm="1">
         <f t="array" aca="1" ref="G7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.09090909090909</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="H7" s="5" cm="1">
         <f t="array" aca="1" ref="H7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="I7" s="5" cm="1">
         <f t="array" aca="1" ref="I7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
       <c r="J7" s="5" cm="1">
         <f t="array" aca="1" ref="J7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="K7" s="5" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="L7" s="5" cm="1">
         <f t="array" aca="1" ref="L7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="M7" s="5" cm="1">
         <f t="array" aca="1" ref="M7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="N7" s="5" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="O7" s="5" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>20</v>
       </c>
       <c r="P7" s="5" cm="1">
         <f t="array" aca="1" ref="P7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Q7" s="5" cm="1">
         <f t="array" aca="1" ref="Q7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="R7" s="5" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
@@ -19589,42 +20114,58 @@
       </c>
       <c r="S7" s="5" cm="1">
         <f t="array" aca="1" ref="S7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="T7" s="5" cm="1">
         <f t="array" aca="1" ref="T7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="U7" s="5" cm="1">
         <f t="array" aca="1" ref="U7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.545454545454547</v>
+        <v>18.818181818181817</v>
       </c>
       <c r="V7" s="5" cm="1">
         <f t="array" aca="1" ref="V7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.90909090909091</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="W7" s="5" cm="1">
         <f t="array" aca="1" ref="W7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.09090909090909</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="X7" s="5" cm="1">
         <f t="array" aca="1" ref="X7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>18.727272727272727</v>
+        <v>19.09090909090909</v>
       </c>
       <c r="Y7" s="5" cm="1">
         <f t="array" aca="1" ref="Y7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="Z7" s="5" cm="1">
         <f t="array" aca="1" ref="Z7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="AA7" s="5" cm="1">
         <f t="array" aca="1" ref="AA7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+        <v>19.545454545454547</v>
+      </c>
+      <c r="AB7" s="5" cm="1">
+        <f t="array" aca="1" ref="AB7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.454545454545453</v>
+      </c>
+      <c r="AC7" s="5" cm="1">
+        <f t="array" aca="1" ref="AC7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.545454545454547</v>
+      </c>
+      <c r="AD7" s="5" cm="1">
+        <f t="array" aca="1" ref="AD7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.181818181818183</v>
+      </c>
+      <c r="AE7" s="5" cm="1">
+        <f t="array" aca="1" ref="AE7" ca="1">INDIRECT("Rapid!N" &amp; (COLUMN()-1)*3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -19642,15 +20183,15 @@
       </c>
       <c r="E8" s="5" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="F8" s="5" cm="1">
         <f t="array" aca="1" ref="F8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="G8" s="5" cm="1">
         <f t="array" aca="1" ref="G8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="H8" s="5" cm="1">
         <f t="array" aca="1" ref="H8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19658,7 +20199,7 @@
       </c>
       <c r="I8" s="5" cm="1">
         <f t="array" aca="1" ref="I8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="J8" s="5" cm="1">
         <f t="array" aca="1" ref="J8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19666,11 +20207,11 @@
       </c>
       <c r="K8" s="5" cm="1">
         <f t="array" aca="1" ref="K8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="L8" s="5" cm="1">
         <f t="array" aca="1" ref="L8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="M8" s="5" cm="1">
         <f t="array" aca="1" ref="M8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19690,7 +20231,7 @@
       </c>
       <c r="Q8" s="5" cm="1">
         <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="R8" s="5" cm="1">
         <f t="array" aca="1" ref="R8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19698,11 +20239,11 @@
       </c>
       <c r="S8" s="5" cm="1">
         <f t="array" aca="1" ref="S8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="T8" s="5" cm="1">
         <f t="array" aca="1" ref="T8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="U8" s="5" cm="1">
         <f t="array" aca="1" ref="U8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
@@ -19710,30 +20251,46 @@
       </c>
       <c r="V8" s="5" cm="1">
         <f t="array" aca="1" ref="V8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.545454545454547</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="W8" s="5" cm="1">
         <f t="array" aca="1" ref="W8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="X8" s="5" cm="1">
         <f t="array" aca="1" ref="X8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="Y8" s="5" cm="1">
         <f t="array" aca="1" ref="Y8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="Z8" s="5" cm="1">
         <f t="array" aca="1" ref="Z8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="AA8" s="5" cm="1">
         <f t="array" aca="1" ref="AA8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.363636363636363</v>
+      </c>
+      <c r="AB8" s="5" cm="1">
+        <f t="array" aca="1" ref="AB8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.181818181818183</v>
+      </c>
+      <c r="AC8" s="5" cm="1">
+        <f t="array" aca="1" ref="AC8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.363636363636363</v>
+      </c>
+      <c r="AD8" s="5" cm="1">
+        <f t="array" aca="1" ref="AD8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
+        <v>18.818181818181817</v>
+      </c>
+      <c r="AE8" s="5" cm="1">
+        <f t="array" aca="1" ref="AE8" ca="1">INDIRECT("Liefering!N" &amp; (COLUMN()-1)*3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>50</v>
       </c>
@@ -19747,7 +20304,7 @@
       </c>
       <c r="D9" s="5" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="E9" s="5" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19763,19 +20320,19 @@
       </c>
       <c r="H9" s="5" cm="1">
         <f t="array" aca="1" ref="H9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.272727272727273</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="I9" s="5" cm="1">
         <f t="array" aca="1" ref="I9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="J9" s="5" cm="1">
         <f t="array" aca="1" ref="J9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.636363636363637</v>
+        <v>21.727272727272727</v>
       </c>
       <c r="K9" s="5" cm="1">
         <f t="array" aca="1" ref="K9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="L9" s="5" cm="1">
         <f t="array" aca="1" ref="L9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19787,7 +20344,7 @@
       </c>
       <c r="N9" s="5" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.181818181818183</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="O9" s="5" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19795,23 +20352,23 @@
       </c>
       <c r="P9" s="5" cm="1">
         <f t="array" aca="1" ref="P9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="Q9" s="5" cm="1">
         <f t="array" aca="1" ref="Q9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="R9" s="5" cm="1">
         <f t="array" aca="1" ref="R9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.636363636363637</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="S9" s="5" cm="1">
         <f t="array" aca="1" ref="S9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.727272727272727</v>
+        <v>20.818181818181817</v>
       </c>
       <c r="T9" s="5" cm="1">
         <f t="array" aca="1" ref="T9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="U9" s="5" cm="1">
         <f t="array" aca="1" ref="U9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19819,7 +20376,7 @@
       </c>
       <c r="V9" s="5" cm="1">
         <f t="array" aca="1" ref="V9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.90909090909091</v>
+        <v>21</v>
       </c>
       <c r="W9" s="5" cm="1">
         <f t="array" aca="1" ref="W9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19827,7 +20384,7 @@
       </c>
       <c r="X9" s="5" cm="1">
         <f t="array" aca="1" ref="X9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
-        <v>21.09090909090909</v>
+        <v>21.181818181818183</v>
       </c>
       <c r="Y9" s="5" cm="1">
         <f t="array" aca="1" ref="Y9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
@@ -19841,8 +20398,24 @@
         <f t="array" aca="1" ref="AA9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
         <v>20.545454545454547</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB9" s="5" cm="1">
+        <f t="array" aca="1" ref="AB9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.818181818181817</v>
+      </c>
+      <c r="AC9" s="5" cm="1">
+        <f t="array" aca="1" ref="AC9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.636363636363637</v>
+      </c>
+      <c r="AD9" s="5" cm="1">
+        <f t="array" aca="1" ref="AD9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>19.727272727272727</v>
+      </c>
+      <c r="AE9" s="5" cm="1">
+        <f t="array" aca="1" ref="AE9" ca="1">INDIRECT("Sturm!N" &amp; (COLUMN()-1)*3)</f>
+        <v>20.181818181818183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -19865,7 +20438,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -19888,7 +20461,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -19911,7 +20484,7 @@
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -19934,7 +20507,7 @@
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -19957,7 +20530,7 @@
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -19980,7 +20553,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -20442,7 +21015,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B2:AA9">
+  <conditionalFormatting sqref="B2:AE9">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(B2&lt;&gt;0,B2=MAX(IF(B$2:B$9&lt;&gt;0,B$2:B$9)))</formula>
     </cfRule>
@@ -20457,7 +21030,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECAD747-1599-4E91-8390-8EFBB40A7E91}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -20470,7 +21043,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.889328063241102</v>
+        <v>19.83164983164983</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -21013,7 +21586,7 @@
         <v>36024</v>
       </c>
       <c r="T18">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -22271,7 +22844,7 @@
       </c>
       <c r="E54">
         <f t="shared" ca="1" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F54">
         <f t="shared" ca="1" si="17"/>
@@ -22303,7 +22876,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P54" t="s">
         <v>321</v>
@@ -22412,6 +22985,12 @@
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
         <v>19.454545454545453</v>
+      </c>
+      <c r="P57" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>39824</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -22579,7 +23158,7 @@
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="20"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="20"/>
@@ -22587,7 +23166,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>21.454545454545453</v>
+        <v>21.545454545454547</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -22767,10 +23346,356 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N71" s="1"/>
+      <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" t="s">
+        <v>283</v>
+      </c>
+      <c r="D71" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" t="s">
+        <v>106</v>
+      </c>
+      <c r="F71" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71" t="s">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>190</v>
+      </c>
+      <c r="I71" t="s">
+        <v>282</v>
+      </c>
+      <c r="J71" t="s">
+        <v>82</v>
+      </c>
+      <c r="K71" t="s">
+        <v>107</v>
+      </c>
+      <c r="L71" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N72" s="1"/>
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>24</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>19.818181818181817</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" t="s">
+        <v>293</v>
+      </c>
+      <c r="C74" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" t="s">
+        <v>336</v>
+      </c>
+      <c r="E74" t="s">
+        <v>106</v>
+      </c>
+      <c r="F74" t="s">
+        <v>322</v>
+      </c>
+      <c r="G74" t="s">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>190</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s">
+        <v>107</v>
+      </c>
+      <c r="L74" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>24</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" t="s">
+        <v>277</v>
+      </c>
+      <c r="D77" t="s">
+        <v>336</v>
+      </c>
+      <c r="E77" t="s">
+        <v>106</v>
+      </c>
+      <c r="F77" t="s">
+        <v>322</v>
+      </c>
+      <c r="G77" t="s">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>311</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s">
+        <v>107</v>
+      </c>
+      <c r="L77" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>23</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>24</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>191</v>
+      </c>
+      <c r="B80" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" t="s">
+        <v>336</v>
+      </c>
+      <c r="E80" t="s">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>330</v>
+      </c>
+      <c r="G80" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80" t="s">
+        <v>190</v>
+      </c>
+      <c r="I80" t="s">
+        <v>280</v>
+      </c>
+      <c r="J80" t="s">
+        <v>82</v>
+      </c>
+      <c r="K80" t="s">
+        <v>107</v>
+      </c>
+      <c r="L80" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>17</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>17</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>17</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:M81)</f>
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -22784,7 +23709,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -22797,7 +23722,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.138339920948617</v>
+        <v>20.144781144781145</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -22841,7 +23766,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <f ca="1">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:L3" ca="1" si="0">DATEDIF(VLOOKUP(C2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22873,7 +23798,7 @@
       </c>
       <c r="J3">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
@@ -22885,7 +23810,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -22929,7 +23854,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <f ca="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:L6" ca="1" si="1">DATEDIF(VLOOKUP(C5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -22961,7 +23886,7 @@
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="1"/>
@@ -22973,7 +23898,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.636363636363637</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -23017,7 +23942,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <f ca="1">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <f t="shared" ref="C9:L9" ca="1" si="2">DATEDIF(VLOOKUP(C8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23061,7 +23986,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -23105,7 +24030,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <f ca="1">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23121,7 +24046,7 @@
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
@@ -23149,7 +24074,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -23193,7 +24118,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <f ca="1">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23209,7 +24134,7 @@
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
@@ -23237,7 +24162,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -23281,7 +24206,7 @@
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
         <f ca="1">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23325,7 +24250,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -23336,7 +24261,7 @@
         <v>38475</v>
       </c>
       <c r="T19">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -23386,7 +24311,7 @@
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
         <f ca="1">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="6">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23430,7 +24355,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -23494,7 +24419,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
         <f ca="1">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23522,7 +24447,7 @@
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="7"/>
@@ -23538,7 +24463,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P24" t="s">
         <v>86</v>
@@ -23602,7 +24527,7 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
         <f ca="1">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27">
         <f t="shared" ref="C27:L27" ca="1" si="8">DATEDIF(VLOOKUP(C26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23630,7 +24555,7 @@
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="8"/>
@@ -23646,7 +24571,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P27" t="s">
         <v>35</v>
@@ -23710,7 +24635,7 @@
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30">
         <f ca="1">DATEDIF(VLOOKUP(B29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23738,7 +24663,7 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="9"/>
@@ -23754,7 +24679,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>20.545454545454547</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="P30" t="s">
         <v>104</v>
@@ -23818,7 +24743,7 @@
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
         <f ca="1">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23846,7 +24771,7 @@
       </c>
       <c r="I33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="10"/>
@@ -23862,7 +24787,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P33" t="s">
         <v>151</v>
@@ -23926,7 +24851,7 @@
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
         <f ca="1">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36">
         <f t="shared" ref="C36:L36" ca="1" si="11">DATEDIF(VLOOKUP(C35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -23954,7 +24879,7 @@
       </c>
       <c r="I36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="11"/>
@@ -23970,7 +24895,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P36" t="s">
         <v>168</v>
@@ -24142,7 +25067,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
         <f ca="1">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24186,7 +25111,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P42" t="s">
         <v>264</v>
@@ -24250,7 +25175,7 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
         <f ca="1">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24278,7 +25203,7 @@
       </c>
       <c r="I45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
@@ -24294,7 +25219,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.454545454545453</v>
+        <v>20.636363636363637</v>
       </c>
       <c r="P45" t="s">
         <v>286</v>
@@ -24358,7 +25283,7 @@
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
         <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24402,7 +25327,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20.09090909090909</v>
+        <v>20.181818181818183</v>
       </c>
       <c r="P48" t="s">
         <v>307</v>
@@ -24470,7 +25395,7 @@
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D51">
         <f t="shared" ca="1" si="16"/>
@@ -24510,13 +25435,21 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P51" t="s">
         <v>331</v>
       </c>
       <c r="Q51" s="6">
         <v>39845</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P52" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>38721</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -24555,6 +25488,12 @@
       </c>
       <c r="L53" t="s">
         <v>37</v>
+      </c>
+      <c r="P53" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>39375</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
@@ -24606,6 +25545,12 @@
         <f ca="1">AVERAGE(B54:M54)</f>
         <v>19.181818181818183</v>
       </c>
+      <c r="P54" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>39333</v>
+      </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -24744,7 +25689,7 @@
       </c>
       <c r="D60">
         <f t="shared" ca="1" si="19"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E60">
         <f t="shared" ca="1" si="19"/>
@@ -24780,7 +25725,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -24824,7 +25769,7 @@
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
         <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63">
         <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -24836,7 +25781,7 @@
       </c>
       <c r="E63">
         <f t="shared" ca="1" si="20"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63">
         <f t="shared" ca="1" si="20"/>
@@ -24868,7 +25813,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>20.181818181818183</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -24924,7 +25869,7 @@
       </c>
       <c r="E66">
         <f t="shared" ca="1" si="21"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F66">
         <f t="shared" ca="1" si="21"/>
@@ -24956,7 +25901,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -25000,7 +25945,7 @@
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B69">
         <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C69">
         <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25012,7 +25957,7 @@
       </c>
       <c r="E69">
         <f t="shared" ca="1" si="22"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F69">
         <f t="shared" ca="1" si="22"/>
@@ -25044,6 +25989,358 @@
       </c>
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:M69)</f>
+        <v>19.818181818181817</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>229</v>
+      </c>
+      <c r="B71" t="s">
+        <v>251</v>
+      </c>
+      <c r="C71" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" t="s">
+        <v>35</v>
+      </c>
+      <c r="F71" t="s">
+        <v>86</v>
+      </c>
+      <c r="G71" t="s">
+        <v>284</v>
+      </c>
+      <c r="H71" t="s">
+        <v>333</v>
+      </c>
+      <c r="I71" t="s">
+        <v>300</v>
+      </c>
+      <c r="J71" t="s">
+        <v>331</v>
+      </c>
+      <c r="K71" t="s">
+        <v>286</v>
+      </c>
+      <c r="L71" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>24</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>19.272727272727273</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>284</v>
+      </c>
+      <c r="E74" t="s">
+        <v>337</v>
+      </c>
+      <c r="F74" t="s">
+        <v>86</v>
+      </c>
+      <c r="G74" t="s">
+        <v>199</v>
+      </c>
+      <c r="H74" t="s">
+        <v>300</v>
+      </c>
+      <c r="I74" t="s">
+        <v>333</v>
+      </c>
+      <c r="J74" t="s">
+        <v>338</v>
+      </c>
+      <c r="K74" t="s">
+        <v>152</v>
+      </c>
+      <c r="L74" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>24</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" t="s">
+        <v>252</v>
+      </c>
+      <c r="D77" t="s">
+        <v>284</v>
+      </c>
+      <c r="E77" t="s">
+        <v>337</v>
+      </c>
+      <c r="F77" t="s">
+        <v>86</v>
+      </c>
+      <c r="G77" t="s">
+        <v>331</v>
+      </c>
+      <c r="H77" t="s">
+        <v>300</v>
+      </c>
+      <c r="I77" t="s">
+        <v>333</v>
+      </c>
+      <c r="J77" t="s">
+        <v>338</v>
+      </c>
+      <c r="K77" t="s">
+        <v>152</v>
+      </c>
+      <c r="L77" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>24</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>19.181818181818183</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>251</v>
+      </c>
+      <c r="C80" t="s">
+        <v>252</v>
+      </c>
+      <c r="D80" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" t="s">
+        <v>337</v>
+      </c>
+      <c r="F80" t="s">
+        <v>86</v>
+      </c>
+      <c r="G80" t="s">
+        <v>199</v>
+      </c>
+      <c r="H80" t="s">
+        <v>300</v>
+      </c>
+      <c r="I80" t="s">
+        <v>333</v>
+      </c>
+      <c r="J80" t="s">
+        <v>152</v>
+      </c>
+      <c r="K80" t="s">
+        <v>286</v>
+      </c>
+      <c r="L80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>17</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:M81)</f>
         <v>19.636363636363637</v>
       </c>
     </row>
@@ -25058,7 +26355,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -25069,7 +26366,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.632231404958677</v>
+        <v>19.690909090909095</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -25137,7 +26434,7 @@
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3">
         <f t="shared" ca="1" si="0"/>
@@ -25157,7 +26454,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.09090909090909</v>
+        <v>19.181818181818183</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -25325,7 +26622,7 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -25333,7 +26630,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -25413,7 +26710,7 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
@@ -25421,7 +26718,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -25501,7 +26798,7 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="4"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="4"/>
@@ -25509,7 +26806,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -25589,7 +26886,7 @@
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
@@ -25597,7 +26894,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P18" t="s">
         <v>19</v>
@@ -25606,7 +26903,7 @@
         <v>38815</v>
       </c>
       <c r="T18">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -25700,7 +26997,7 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
@@ -25708,7 +27005,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>20.363636363636363</v>
+        <v>20.454545454545453</v>
       </c>
       <c r="P21" t="s">
         <v>89</v>
@@ -25808,7 +27105,7 @@
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
@@ -25816,7 +27113,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P24" t="s">
         <v>90</v>
@@ -25916,7 +27213,7 @@
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="8"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="8"/>
@@ -25924,7 +27221,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P27" t="s">
         <v>30</v>
@@ -26536,7 +27833,7 @@
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
@@ -26572,7 +27869,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P45" t="s">
         <v>304</v>
@@ -26644,7 +27941,7 @@
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
@@ -26680,7 +27977,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>20.181818181818183</v>
+        <v>20.272727272727273</v>
       </c>
       <c r="P48" t="s">
         <v>323</v>
@@ -26744,7 +28041,7 @@
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -26788,7 +28085,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -26920,7 +28217,7 @@
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -26964,7 +28261,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -27008,7 +28305,7 @@
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C60">
         <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -27052,7 +28349,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -27229,6 +28526,270 @@
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
         <v>18.90909090909091</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" t="s">
+        <v>334</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>89</v>
+      </c>
+      <c r="F68" t="s">
+        <v>257</v>
+      </c>
+      <c r="G68" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" t="s">
+        <v>91</v>
+      </c>
+      <c r="I68" t="s">
+        <v>90</v>
+      </c>
+      <c r="J68" t="s">
+        <v>188</v>
+      </c>
+      <c r="K68" t="s">
+        <v>235</v>
+      </c>
+      <c r="L68" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <f ca="1">DATEDIF(VLOOKUP(B68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>23</v>
+      </c>
+      <c r="C69">
+        <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <f t="shared" ca="1" si="22"/>
+        <v>19</v>
+      </c>
+      <c r="F69">
+        <f t="shared" ca="1" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="G69">
+        <f t="shared" ca="1" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="H69">
+        <f t="shared" ca="1" si="22"/>
+        <v>17</v>
+      </c>
+      <c r="I69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="J69">
+        <f t="shared" ca="1" si="22"/>
+        <v>18</v>
+      </c>
+      <c r="K69">
+        <f t="shared" ca="1" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="L69">
+        <f t="shared" ca="1" si="22"/>
+        <v>22</v>
+      </c>
+      <c r="N69" s="1">
+        <f ca="1">AVERAGE(B69:M69)</f>
+        <v>19.90909090909091</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" t="s">
+        <v>208</v>
+      </c>
+      <c r="E71" t="s">
+        <v>334</v>
+      </c>
+      <c r="F71" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" t="s">
+        <v>257</v>
+      </c>
+      <c r="H71" t="s">
+        <v>211</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>91</v>
+      </c>
+      <c r="K71" t="s">
+        <v>90</v>
+      </c>
+      <c r="L71" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="23"/>
+        <v>22</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="23"/>
+        <v>24</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="23"/>
+        <v>17</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="23"/>
+        <v>18</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="23"/>
+        <v>22</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:M72)</f>
+        <v>19.90909090909091</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" t="s">
+        <v>303</v>
+      </c>
+      <c r="C74" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" t="s">
+        <v>88</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>89</v>
+      </c>
+      <c r="H74" t="s">
+        <v>304</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s">
+        <v>324</v>
+      </c>
+      <c r="L74" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>23</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="24"/>
+        <v>17</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="24"/>
+        <v>22</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:M75)</f>
+        <v>19.363636363636363</v>
       </c>
     </row>
   </sheetData>
@@ -27240,7 +28801,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628DC590-5B70-45B7-BCD6-8ED432E7A1AF}">
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
@@ -27249,7 +28810,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>21.014545454545456</v>
+        <v>21.169278996865202</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -27294,7 +28855,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <f t="shared" ref="B3:L3" ca="1" si="0">DATEDIF(VLOOKUP(B2,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <f t="shared" ca="1" si="0"/>
@@ -27330,15 +28891,15 @@
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>20.545454545454547</v>
+        <v>20.818181818181817</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -27386,7 +28947,7 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <f t="shared" ref="B6:L6" ca="1" si="1">DATEDIF(VLOOKUP(B5,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="1"/>
@@ -27422,15 +28983,15 @@
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -27478,7 +29039,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <f t="shared" ref="B9:L9" ca="1" si="2">DATEDIF(VLOOKUP(B8,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="2"/>
@@ -27490,7 +29051,7 @@
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
@@ -27518,11 +29079,11 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.818181818181817</v>
+        <v>21.09090909090909</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -27570,7 +29131,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <f t="shared" ref="B12:L12" ca="1" si="3">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="3"/>
@@ -27582,7 +29143,7 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
@@ -27594,7 +29155,7 @@
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="3"/>
@@ -27610,11 +29171,11 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="3"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.818181818181817</v>
+        <v>21.181818181818183</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -27659,7 +29220,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <f t="shared" ref="B15:L15" ca="1" si="4">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="4"/>
@@ -27671,7 +29232,7 @@
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
@@ -27683,7 +29244,7 @@
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="4"/>
@@ -27699,11 +29260,11 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="4"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>21</v>
+        <v>21.363636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -27748,7 +29309,7 @@
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
         <f t="shared" ref="B18:L18" ca="1" si="5">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="5"/>
@@ -27760,7 +29321,7 @@
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
@@ -27788,11 +29349,11 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="5"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>21</v>
+        <v>21.272727272727273</v>
       </c>
       <c r="P18" t="s">
         <v>93</v>
@@ -27860,7 +29421,7 @@
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
         <f t="shared" ref="B21:L21" ca="1" si="6">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="6"/>
@@ -27872,7 +29433,7 @@
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
@@ -27896,15 +29457,15 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>21</v>
+        <v>21.363636363636363</v>
       </c>
       <c r="P21" t="s">
         <v>38</v>
@@ -27969,7 +29530,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
         <f t="shared" ref="B24:L24" ca="1" si="7">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="7"/>
@@ -27981,7 +29542,7 @@
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
@@ -28009,11 +29570,11 @@
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="7"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>20.636363636363637</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="P24" t="s">
         <v>32</v>
@@ -28078,7 +29639,7 @@
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B27">
         <f t="shared" ref="B27:L27" ca="1" si="8">DATEDIF(VLOOKUP(B26,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="8"/>
@@ -28090,7 +29651,7 @@
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
@@ -28122,7 +29683,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.727272727272727</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="P27" t="s">
         <v>22</v>
@@ -28187,7 +29748,7 @@
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30">
         <f ca="1">DATEDIF(VLOOKUP(B29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -28203,7 +29764,7 @@
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
@@ -28231,7 +29792,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P30" t="s">
         <v>110</v>
@@ -28296,7 +29857,7 @@
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
         <f t="shared" ref="B33:L33" ca="1" si="10">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="10"/>
@@ -28308,7 +29869,7 @@
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
@@ -28328,7 +29889,7 @@
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="10"/>
@@ -28340,7 +29901,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>21.181818181818183</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="P33" t="s">
         <v>178</v>
@@ -28405,7 +29966,7 @@
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B36">
         <f t="shared" ref="B36:L36" ca="1" si="11">DATEDIF(VLOOKUP(B35,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C36">
         <f t="shared" ca="1" si="11"/>
@@ -28413,11 +29974,11 @@
       </c>
       <c r="D36">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="11"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
@@ -28437,7 +29998,7 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="11"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="11"/>
@@ -28449,7 +30010,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>21.09090909090909</v>
+        <v>21.454545454545453</v>
       </c>
       <c r="P36" t="s">
         <v>227</v>
@@ -28514,7 +30075,7 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
         <f t="shared" ref="B39:L39" ca="1" si="12">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39">
         <f t="shared" ca="1" si="12"/>
@@ -28522,11 +30083,11 @@
       </c>
       <c r="D39">
         <f t="shared" ca="1" si="12"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="12"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
@@ -28546,7 +30107,7 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="12"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="12"/>
@@ -28558,7 +30119,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>21.181818181818183</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="P39" t="s">
         <v>247</v>
@@ -28623,7 +30184,7 @@
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B42">
         <f t="shared" ref="B42:L42" ca="1" si="13">DATEDIF(VLOOKUP(B41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42">
         <f t="shared" ca="1" si="13"/>
@@ -28631,11 +30192,11 @@
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E42">
         <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
@@ -28655,7 +30216,7 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="13"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="13"/>
@@ -28667,7 +30228,7 @@
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>21.272727272727273</v>
+        <v>21.636363636363637</v>
       </c>
       <c r="P42" t="s">
         <v>271</v>
@@ -28732,7 +30293,7 @@
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45">
         <f t="shared" ref="B45:L45" ca="1" si="14">DATEDIF(VLOOKUP(B44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <f t="shared" ca="1" si="14"/>
@@ -28744,7 +30305,7 @@
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
@@ -28764,7 +30325,7 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="14"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="14"/>
@@ -28776,7 +30337,7 @@
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>21.272727272727273</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="P45" t="s">
         <v>189</v>
@@ -28841,7 +30402,7 @@
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
         <f t="shared" ref="B48:L48" ca="1" si="15">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C48">
         <f t="shared" ca="1" si="15"/>
@@ -28853,7 +30414,7 @@
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
@@ -28873,7 +30434,7 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="15"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="15"/>
@@ -28885,7 +30446,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>21.272727272727273</v>
+        <v>21.545454545454547</v>
       </c>
       <c r="P48" t="s">
         <v>317</v>
@@ -28950,7 +30511,7 @@
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f t="shared" ref="B51:L51" ca="1" si="16">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51">
         <f t="shared" ca="1" si="16"/>
@@ -28962,7 +30523,7 @@
       </c>
       <c r="E51">
         <f t="shared" ca="1" si="16"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <f t="shared" ca="1" si="16"/>
@@ -28982,11 +30543,11 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="16"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="16"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="16"/>
@@ -28994,7 +30555,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>20.727272727272727</v>
+        <v>21.09090909090909</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -29039,11 +30600,11 @@
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f t="shared" ref="B54:L54" ca="1" si="17">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54">
         <f t="shared" ca="1" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <f t="shared" ca="1" si="17"/>
@@ -29071,11 +30632,11 @@
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="17"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="17"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="17"/>
@@ -29083,7 +30644,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>21.181818181818183</v>
+        <v>21.545454545454547</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -29128,11 +30689,11 @@
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f t="shared" ref="B57:L57" ca="1" si="18">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C57">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <f t="shared" ca="1" si="18"/>
@@ -29160,7 +30721,7 @@
       </c>
       <c r="J57">
         <f t="shared" ca="1" si="18"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K57">
         <f t="shared" ca="1" si="18"/>
@@ -29172,7 +30733,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>21.727272727272727</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -29217,7 +30778,7 @@
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f t="shared" ref="B60:L60" ca="1" si="19">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60">
         <f t="shared" ca="1" si="19"/>
@@ -29249,7 +30810,7 @@
       </c>
       <c r="J60">
         <f t="shared" ca="1" si="19"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K60">
         <f t="shared" ca="1" si="19"/>
@@ -29261,7 +30822,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>21.818181818181817</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -29306,7 +30867,7 @@
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
         <f t="shared" ref="B63:L63" ca="1" si="20">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C63">
         <f t="shared" ca="1" si="20"/>
@@ -29338,7 +30899,7 @@
       </c>
       <c r="J63">
         <f t="shared" ca="1" si="20"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="20"/>
@@ -29350,7 +30911,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>21.818181818181817</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -29395,7 +30956,7 @@
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B66">
         <f t="shared" ref="B66:L66" ca="1" si="21">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <f t="shared" ca="1" si="21"/>
@@ -29423,11 +30984,11 @@
       </c>
       <c r="I66">
         <f t="shared" ca="1" si="21"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66">
         <f t="shared" ca="1" si="21"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K66">
         <f t="shared" ca="1" si="21"/>
@@ -29439,7 +31000,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>21.90909090909091</v>
+        <v>22.181818181818183</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -29512,11 +31073,11 @@
       </c>
       <c r="I69">
         <f t="shared" ca="1" si="22"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J69">
         <f t="shared" ca="1" si="22"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="22"/>
@@ -29528,7 +31089,7 @@
       </c>
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:M69)</f>
-        <v>20.363636363636363</v>
+        <v>20.545454545454547</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -29585,7 +31146,7 @@
       </c>
       <c r="E72">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F72">
         <f t="shared" ca="1" si="23"/>
@@ -29601,7 +31162,7 @@
       </c>
       <c r="I72">
         <f t="shared" ca="1" si="23"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J72">
         <f t="shared" ca="1" si="23"/>
@@ -29617,7 +31178,7 @@
       </c>
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:M72)</f>
-        <v>21.181818181818183</v>
+        <v>21.363636363636363</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -29674,7 +31235,7 @@
       </c>
       <c r="E75">
         <f t="shared" ca="1" si="24"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F75">
         <f t="shared" ca="1" si="24"/>
@@ -29690,7 +31251,7 @@
       </c>
       <c r="I75">
         <f t="shared" ca="1" si="24"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J75">
         <f t="shared" ca="1" si="24"/>
@@ -29706,7 +31267,363 @@
       </c>
       <c r="N75" s="1">
         <f ca="1">AVERAGE(B75:M75)</f>
-        <v>21.727272727272727</v>
+        <v>21.90909090909091</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" t="s">
+        <v>317</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" t="s">
+        <v>227</v>
+      </c>
+      <c r="F77" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" t="s">
+        <v>318</v>
+      </c>
+      <c r="H77" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77" t="s">
+        <v>247</v>
+      </c>
+      <c r="J77" t="s">
+        <v>241</v>
+      </c>
+      <c r="K77" t="s">
+        <v>271</v>
+      </c>
+      <c r="L77" t="s">
+        <v>59</v>
+      </c>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f t="shared" ref="B78:L78" ca="1" si="25">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>19.363636363636363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" t="s">
+        <v>317</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" t="s">
+        <v>178</v>
+      </c>
+      <c r="E80" t="s">
+        <v>227</v>
+      </c>
+      <c r="F80" t="s">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s">
+        <v>94</v>
+      </c>
+      <c r="H80" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80" t="s">
+        <v>247</v>
+      </c>
+      <c r="J80" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" t="s">
+        <v>271</v>
+      </c>
+      <c r="L80" t="s">
+        <v>302</v>
+      </c>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f t="shared" ref="B81:L81" ca="1" si="26">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>37</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>22</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:M81)</f>
+        <v>21.272727272727273</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" t="s">
+        <v>319</v>
+      </c>
+      <c r="D83" t="s">
+        <v>227</v>
+      </c>
+      <c r="E83" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" t="s">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s">
+        <v>271</v>
+      </c>
+      <c r="H83" t="s">
+        <v>247</v>
+      </c>
+      <c r="I83" t="s">
+        <v>59</v>
+      </c>
+      <c r="J83" t="s">
+        <v>318</v>
+      </c>
+      <c r="K83" t="s">
+        <v>270</v>
+      </c>
+      <c r="L83" t="s">
+        <v>241</v>
+      </c>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f t="shared" ref="B84:L84" ca="1" si="27">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:M84)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B86" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" t="s">
+        <v>227</v>
+      </c>
+      <c r="E86" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s">
+        <v>271</v>
+      </c>
+      <c r="H86" t="s">
+        <v>247</v>
+      </c>
+      <c r="I86" t="s">
+        <v>59</v>
+      </c>
+      <c r="J86" t="s">
+        <v>318</v>
+      </c>
+      <c r="K86" t="s">
+        <v>270</v>
+      </c>
+      <c r="L86" t="s">
+        <v>25</v>
+      </c>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <f t="shared" ref="B87:L87" ca="1" si="28">DATEDIF(VLOOKUP(B86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="E87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="F87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="G87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="H87">
+        <f t="shared" ca="1" si="28"/>
+        <v>21</v>
+      </c>
+      <c r="I87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="J87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="K87">
+        <f t="shared" ca="1" si="28"/>
+        <v>21</v>
+      </c>
+      <c r="L87">
+        <f t="shared" ca="1" si="28"/>
+        <v>37</v>
+      </c>
+      <c r="N87" s="1">
+        <f ca="1">AVERAGE(B87:M87)</f>
+        <v>21.272727272727273</v>
       </c>
     </row>
   </sheetData>
@@ -29718,7 +31635,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -29728,7 +31645,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>21.003952569169957</v>
+        <v>20.98951048951049</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -30767,7 +32684,7 @@
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="11"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="11"/>
@@ -30799,7 +32716,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:L33)</f>
-        <v>21</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="P33" t="s">
         <v>176</v>
@@ -31976,6 +33893,270 @@
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:L69)</f>
         <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>228</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" t="s">
+        <v>265</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" t="s">
+        <v>11</v>
+      </c>
+      <c r="J71" t="s">
+        <v>313</v>
+      </c>
+      <c r="K71" t="s">
+        <v>250</v>
+      </c>
+      <c r="L71" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C72">
+        <f t="shared" ref="C72:L72" ca="1" si="24">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D72">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="G72">
+        <f t="shared" ca="1" si="24"/>
+        <v>21</v>
+      </c>
+      <c r="H72">
+        <f t="shared" ca="1" si="24"/>
+        <v>25</v>
+      </c>
+      <c r="I72">
+        <f t="shared" ca="1" si="24"/>
+        <v>25</v>
+      </c>
+      <c r="J72">
+        <f t="shared" ca="1" si="24"/>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <f t="shared" ca="1" si="24"/>
+        <v>19</v>
+      </c>
+      <c r="L72">
+        <f t="shared" ca="1" si="24"/>
+        <v>18</v>
+      </c>
+      <c r="N72" s="1">
+        <f ca="1">AVERAGE(B72:L72)</f>
+        <v>20.90909090909091</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>229</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>111</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="s">
+        <v>11</v>
+      </c>
+      <c r="J74" t="s">
+        <v>313</v>
+      </c>
+      <c r="K74" t="s">
+        <v>170</v>
+      </c>
+      <c r="L74" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:L75" ca="1" si="25">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D75">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="F75">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ca="1" si="25"/>
+        <v>25</v>
+      </c>
+      <c r="I75">
+        <f t="shared" ca="1" si="25"/>
+        <v>25</v>
+      </c>
+      <c r="J75">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="K75">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="L75">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="N75" s="1">
+        <f ca="1">AVERAGE(B75:L75)</f>
+        <v>20.818181818181817</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>95</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>175</v>
+      </c>
+      <c r="J77" t="s">
+        <v>313</v>
+      </c>
+      <c r="K77" t="s">
+        <v>170</v>
+      </c>
+      <c r="L77" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="26">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="26"/>
+        <v>25</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="26"/>
+        <v>21</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:L78)</f>
+        <v>20.818181818181817</v>
       </c>
     </row>
   </sheetData>
@@ -31989,7 +34170,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D88D7D6-4932-46BC-9430-8F20DDAB89DF}">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -32001,7 +34182,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.47902097902098</v>
+        <v>19.70846394984326</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -32057,7 +34238,7 @@
       </c>
       <c r="E3">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <f t="shared" ca="1" si="0"/>
@@ -32065,7 +34246,7 @@
       </c>
       <c r="G3">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="0"/>
@@ -32089,7 +34270,7 @@
       </c>
       <c r="N3" s="1">
         <f ca="1">AVERAGE(B3:M3)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -32145,7 +34326,7 @@
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
@@ -32153,7 +34334,7 @@
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -32177,7 +34358,7 @@
       </c>
       <c r="N6" s="1">
         <f ca="1">AVERAGE(B6:M6)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -32233,7 +34414,7 @@
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="2"/>
@@ -32241,7 +34422,7 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="2"/>
@@ -32265,7 +34446,7 @@
       </c>
       <c r="N9" s="1">
         <f ca="1">AVERAGE(B9:M9)</f>
-        <v>20.272727272727273</v>
+        <v>20.454545454545453</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -32321,7 +34502,7 @@
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="3"/>
@@ -32329,7 +34510,7 @@
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="3"/>
@@ -32353,7 +34534,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>20.09090909090909</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -32405,11 +34586,11 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="4"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
@@ -32417,7 +34598,7 @@
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="4"/>
@@ -32441,7 +34622,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>20</v>
+        <v>20.272727272727273</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -32493,11 +34674,11 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
@@ -32505,7 +34686,7 @@
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="5"/>
@@ -32529,7 +34710,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>20.09090909090909</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P18" t="s">
         <v>47</v>
@@ -32538,7 +34719,7 @@
         <v>38672</v>
       </c>
       <c r="T18">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -32608,7 +34789,7 @@
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="6"/>
@@ -32616,7 +34797,7 @@
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="6"/>
@@ -32640,7 +34821,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:M21)</f>
-        <v>19.727272727272727</v>
+        <v>19.90909090909091</v>
       </c>
       <c r="P21" t="s">
         <v>45</v>
@@ -32716,7 +34897,7 @@
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="7"/>
@@ -32724,7 +34905,7 @@
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
@@ -32748,7 +34929,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.818181818181817</v>
+        <v>20</v>
       </c>
       <c r="P24" t="s">
         <v>44</v>
@@ -32824,7 +35005,7 @@
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="8"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="8"/>
@@ -32832,7 +35013,7 @@
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="8"/>
@@ -32856,7 +35037,7 @@
       </c>
       <c r="N27" s="1">
         <f ca="1">AVERAGE(B27:M27)</f>
-        <v>19.90909090909091</v>
+        <v>20.09090909090909</v>
       </c>
       <c r="P27" t="s">
         <v>54</v>
@@ -32924,7 +35105,7 @@
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="9"/>
@@ -32932,7 +35113,7 @@
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <f t="shared" ca="1" si="9"/>
@@ -32940,7 +35121,7 @@
       </c>
       <c r="G30">
         <f t="shared" ca="1" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30">
         <f t="shared" ca="1" si="9"/>
@@ -32964,7 +35145,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.545454545454547</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P30" t="s">
         <v>161</v>
@@ -33032,7 +35213,7 @@
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="10"/>
@@ -33040,7 +35221,7 @@
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <f t="shared" ca="1" si="10"/>
@@ -33048,7 +35229,7 @@
       </c>
       <c r="G33">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33">
         <f t="shared" ca="1" si="10"/>
@@ -33072,7 +35253,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.545454545454547</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="P33" t="s">
         <v>180</v>
@@ -33148,7 +35329,7 @@
       </c>
       <c r="E36">
         <f t="shared" ca="1" si="11"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36">
         <f t="shared" ca="1" si="11"/>
@@ -33180,7 +35361,7 @@
       </c>
       <c r="N36" s="1">
         <f ca="1">AVERAGE(B36:M36)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P36" t="s">
         <v>232</v>
@@ -33256,7 +35437,7 @@
       </c>
       <c r="E39">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39">
         <f t="shared" ca="1" si="12"/>
@@ -33284,11 +35465,11 @@
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="12"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
       <c r="P39" t="s">
         <v>275</v>
@@ -33356,7 +35537,7 @@
       </c>
       <c r="C42">
         <f t="shared" ref="C42:L42" ca="1" si="13">DATEDIF(VLOOKUP(C41,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42">
         <f t="shared" ca="1" si="13"/>
@@ -33364,7 +35545,7 @@
       </c>
       <c r="E42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F42">
         <f t="shared" ca="1" si="13"/>
@@ -33392,11 +35573,11 @@
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N42" s="1">
         <f ca="1">AVERAGE(B42:M42)</f>
-        <v>19.727272727272727</v>
+        <v>20</v>
       </c>
       <c r="P42" t="s">
         <v>292</v>
@@ -33464,7 +35645,7 @@
       </c>
       <c r="C45">
         <f t="shared" ref="C45:L45" ca="1" si="14">DATEDIF(VLOOKUP(C44,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45">
         <f t="shared" ca="1" si="14"/>
@@ -33472,7 +35653,7 @@
       </c>
       <c r="E45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F45">
         <f t="shared" ca="1" si="14"/>
@@ -33500,11 +35681,17 @@
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N45" s="1">
         <f ca="1">AVERAGE(B45:M45)</f>
-        <v>19.454545454545453</v>
+        <v>19.727272727272727</v>
+      </c>
+      <c r="P45" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>33808</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -33552,7 +35739,7 @@
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D48">
         <f t="shared" ca="1" si="15"/>
@@ -33560,7 +35747,7 @@
       </c>
       <c r="E48">
         <f t="shared" ca="1" si="15"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48">
         <f t="shared" ca="1" si="15"/>
@@ -33592,7 +35779,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:M48)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -33728,7 +35915,7 @@
       </c>
       <c r="C54">
         <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <f t="shared" ca="1" si="17"/>
@@ -33740,7 +35927,7 @@
       </c>
       <c r="F54">
         <f t="shared" ca="1" si="17"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="17"/>
@@ -33768,7 +35955,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>18.90909090909091</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
@@ -33816,11 +36003,11 @@
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <f t="shared" ca="1" si="18"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E57">
         <f t="shared" ca="1" si="18"/>
@@ -33828,7 +36015,7 @@
       </c>
       <c r="F57">
         <f t="shared" ca="1" si="18"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G57">
         <f t="shared" ca="1" si="18"/>
@@ -33856,7 +36043,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>18.545454545454547</v>
+        <v>18.818181818181817</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -33904,11 +36091,11 @@
       </c>
       <c r="C60">
         <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E60">
         <f t="shared" ca="1" si="19"/>
@@ -33916,7 +36103,7 @@
       </c>
       <c r="F60">
         <f t="shared" ca="1" si="19"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G60">
         <f t="shared" ca="1" si="19"/>
@@ -33944,7 +36131,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>18.545454545454547</v>
+        <v>18.818181818181817</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -33993,11 +36180,11 @@
       </c>
       <c r="C63">
         <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <f t="shared" ca="1" si="20"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E63">
         <f t="shared" ca="1" si="20"/>
@@ -34005,7 +36192,7 @@
       </c>
       <c r="F63">
         <f t="shared" ca="1" si="20"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G63">
         <f t="shared" ca="1" si="20"/>
@@ -34029,11 +36216,11 @@
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:M63)</f>
-        <v>18.90909090909091</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="O63" s="1"/>
     </row>
@@ -34082,11 +36269,11 @@
       </c>
       <c r="C66">
         <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66">
         <f t="shared" ca="1" si="21"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <f t="shared" ca="1" si="21"/>
@@ -34118,11 +36305,11 @@
       </c>
       <c r="L66">
         <f t="shared" ca="1" si="21"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>19.09090909090909</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -34170,11 +36357,11 @@
       </c>
       <c r="C69">
         <f t="shared" ref="C69:L69" ca="1" si="22">DATEDIF(VLOOKUP(C68,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D69">
         <f t="shared" ca="1" si="22"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E69">
         <f t="shared" ca="1" si="22"/>
@@ -34198,7 +36385,7 @@
       </c>
       <c r="J69">
         <f t="shared" ca="1" si="22"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="22"/>
@@ -34206,11 +36393,11 @@
       </c>
       <c r="L69">
         <f t="shared" ca="1" si="22"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:M69)</f>
-        <v>18.727272727272727</v>
+        <v>19.09090909090909</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -34258,11 +36445,11 @@
       </c>
       <c r="C72">
         <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D72">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E72">
         <f t="shared" ca="1" si="23"/>
@@ -34286,7 +36473,7 @@
       </c>
       <c r="J72">
         <f t="shared" ca="1" si="23"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K72">
         <f t="shared" ca="1" si="23"/>
@@ -34298,7 +36485,7 @@
       </c>
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:M72)</f>
-        <v>19.272727272727273</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -34346,11 +36533,11 @@
       </c>
       <c r="C75">
         <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D75">
         <f t="shared" ca="1" si="24"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E75">
         <f t="shared" ca="1" si="24"/>
@@ -34374,7 +36561,7 @@
       </c>
       <c r="J75">
         <f t="shared" ca="1" si="24"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75">
         <f t="shared" ca="1" si="24"/>
@@ -34386,7 +36573,7 @@
       </c>
       <c r="N75" s="1">
         <f ca="1">AVERAGE(B75:M75)</f>
-        <v>19.272727272727273</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
@@ -34434,11 +36621,11 @@
       </c>
       <c r="C78">
         <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D78">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E78">
         <f t="shared" ca="1" si="25"/>
@@ -34462,7 +36649,7 @@
       </c>
       <c r="J78">
         <f t="shared" ca="1" si="25"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78">
         <f t="shared" ca="1" si="25"/>
@@ -34474,7 +36661,271 @@
       </c>
       <c r="N78" s="1">
         <f ca="1">AVERAGE(B78:M78)</f>
-        <v>19.272727272727273</v>
+        <v>19.545454545454547</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>109</v>
+      </c>
+      <c r="B80" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" t="s">
+        <v>52</v>
+      </c>
+      <c r="E80" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" t="s">
+        <v>48</v>
+      </c>
+      <c r="H80" t="s">
+        <v>162</v>
+      </c>
+      <c r="I80" t="s">
+        <v>289</v>
+      </c>
+      <c r="J80" t="s">
+        <v>288</v>
+      </c>
+      <c r="K80" t="s">
+        <v>56</v>
+      </c>
+      <c r="L80" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>22</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:M81)</f>
+        <v>19.454545454545453</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>169</v>
+      </c>
+      <c r="B83" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" t="s">
+        <v>54</v>
+      </c>
+      <c r="D83" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" t="s">
+        <v>52</v>
+      </c>
+      <c r="F83" t="s">
+        <v>44</v>
+      </c>
+      <c r="G83" t="s">
+        <v>288</v>
+      </c>
+      <c r="H83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" t="s">
+        <v>180</v>
+      </c>
+      <c r="J83" t="s">
+        <v>162</v>
+      </c>
+      <c r="K83" t="s">
+        <v>289</v>
+      </c>
+      <c r="L83" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f ca="1">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ref="C84:L84" ca="1" si="27">DATEDIF(VLOOKUP(C83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>22</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:M84)</f>
+        <v>19.545454545454547</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>50</v>
+      </c>
+      <c r="B86" t="s">
+        <v>346</v>
+      </c>
+      <c r="C86" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" t="s">
+        <v>202</v>
+      </c>
+      <c r="E86" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" t="s">
+        <v>45</v>
+      </c>
+      <c r="G86" t="s">
+        <v>288</v>
+      </c>
+      <c r="H86" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" t="s">
+        <v>180</v>
+      </c>
+      <c r="J86" t="s">
+        <v>162</v>
+      </c>
+      <c r="K86" t="s">
+        <v>289</v>
+      </c>
+      <c r="L86" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <f ca="1">DATEDIF(VLOOKUP(B86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>33</v>
+      </c>
+      <c r="C87">
+        <f t="shared" ref="C87:L87" ca="1" si="28">DATEDIF(VLOOKUP(C86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="E87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="F87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="G87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="H87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="I87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="J87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="K87">
+        <f t="shared" ca="1" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="L87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="1">
+        <f ca="1">AVERAGE(B87:M87)</f>
+        <v>20.181818181818183</v>
       </c>
     </row>
   </sheetData>
@@ -34486,7 +36937,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03A6E26-4348-4BD7-A4C3-5653B1514462}">
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -34499,7 +36950,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.541818181818183</v>
+        <v>19.561128526645771</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -34811,7 +37262,7 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <f ca="1">DATEDIF(VLOOKUP(B11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <f t="shared" ref="C12:L12" ca="1" si="3">DATEDIF(VLOOKUP(C11,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -34855,7 +37306,7 @@
       </c>
       <c r="N12" s="1">
         <f ca="1">AVERAGE(B12:M12)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -34900,7 +37351,7 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <f ca="1">DATEDIF(VLOOKUP(B14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:L15" ca="1" si="4">DATEDIF(VLOOKUP(C14,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -34944,7 +37395,7 @@
       </c>
       <c r="N15" s="1">
         <f ca="1">AVERAGE(B15:M15)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -34989,7 +37440,7 @@
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B18">
         <f ca="1">DATEDIF(VLOOKUP(B17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <f t="shared" ref="C18:L18" ca="1" si="5">DATEDIF(VLOOKUP(C17,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -35005,7 +37456,7 @@
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="5"/>
@@ -35033,7 +37484,7 @@
       </c>
       <c r="N18" s="1">
         <f ca="1">AVERAGE(B18:M18)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P18" t="s">
         <v>98</v>
@@ -35042,7 +37493,7 @@
         <v>39078</v>
       </c>
       <c r="T18">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -35210,7 +37661,7 @@
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B24">
         <f ca="1">DATEDIF(VLOOKUP(B23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <f t="shared" ref="C24:L24" ca="1" si="7">DATEDIF(VLOOKUP(C23,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -35254,7 +37705,7 @@
       </c>
       <c r="N24" s="1">
         <f ca="1">AVERAGE(B24:M24)</f>
-        <v>19.545454545454547</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="P24" t="s">
         <v>99</v>
@@ -35428,7 +37879,7 @@
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30">
         <f ca="1">DATEDIF(VLOOKUP(B29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30:L30" ca="1" si="9">DATEDIF(VLOOKUP(C29,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -35456,7 +37907,7 @@
       </c>
       <c r="I30">
         <f t="shared" ca="1" si="9"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="9"/>
@@ -35472,7 +37923,7 @@
       </c>
       <c r="N30" s="1">
         <f ca="1">AVERAGE(B30:M30)</f>
-        <v>19.545454545454547</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P30" t="s">
         <v>115</v>
@@ -35537,7 +37988,7 @@
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B33">
         <f ca="1">DATEDIF(VLOOKUP(B32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <f t="shared" ref="C33:L33" ca="1" si="10">DATEDIF(VLOOKUP(C32,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -35581,7 +38032,7 @@
       </c>
       <c r="N33" s="1">
         <f ca="1">AVERAGE(B33:M33)</f>
-        <v>19.454545454545453</v>
+        <v>19.545454545454547</v>
       </c>
       <c r="P33" t="s">
         <v>205</v>
@@ -36082,7 +38533,7 @@
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48">
         <f ca="1">DATEDIF(VLOOKUP(B47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48">
         <f t="shared" ref="C48:L48" ca="1" si="15">DATEDIF(VLOOKUP(C47,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36126,7 +38577,7 @@
       </c>
       <c r="N48" s="1">
         <f ca="1">AVERAGE(B48:L48)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P48" t="s">
         <v>298</v>
@@ -36181,6 +38632,12 @@
         <v>62</v>
       </c>
       <c r="N50" s="1"/>
+      <c r="P50" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>38928</v>
+      </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
@@ -36231,6 +38688,20 @@
         <f ca="1">AVERAGE(B51:L51)</f>
         <v>19.636363636363637</v>
       </c>
+      <c r="P51" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>39866</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P52" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>39723</v>
+      </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -36274,7 +38745,7 @@
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54">
         <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36294,7 +38765,7 @@
       </c>
       <c r="G54">
         <f t="shared" ca="1" si="17"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H54">
         <f t="shared" ca="1" si="17"/>
@@ -36318,7 +38789,7 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:L54)</f>
-        <v>19.181818181818183</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -36363,7 +38834,7 @@
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36383,7 +38854,7 @@
       </c>
       <c r="G57">
         <f t="shared" ca="1" si="18"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H57">
         <f t="shared" ca="1" si="18"/>
@@ -36407,7 +38878,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:L57)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -36541,7 +39012,7 @@
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B63">
         <f ca="1">DATEDIF(VLOOKUP(B62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <f t="shared" ref="C63:L63" ca="1" si="20">DATEDIF(VLOOKUP(C62,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36557,7 +39028,7 @@
       </c>
       <c r="F63">
         <f t="shared" ca="1" si="20"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G63">
         <f t="shared" ca="1" si="20"/>
@@ -36585,7 +39056,7 @@
       </c>
       <c r="N63" s="1">
         <f ca="1">AVERAGE(B63:L63)</f>
-        <v>19.545454545454547</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -36630,7 +39101,7 @@
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B66">
         <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C66">
         <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36646,7 +39117,7 @@
       </c>
       <c r="F66">
         <f t="shared" ca="1" si="21"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G66">
         <f t="shared" ca="1" si="21"/>
@@ -36674,7 +39145,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:L66)</f>
-        <v>19.363636363636363</v>
+        <v>19.545454545454547</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -36735,7 +39206,7 @@
       </c>
       <c r="F69">
         <f t="shared" ca="1" si="22"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G69">
         <f t="shared" ca="1" si="22"/>
@@ -36763,7 +39234,7 @@
       </c>
       <c r="N69" s="1">
         <f ca="1">AVERAGE(B69:L69)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -36808,7 +39279,7 @@
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B72">
         <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C72">
         <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36824,7 +39295,7 @@
       </c>
       <c r="F72">
         <f t="shared" ca="1" si="23"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72">
         <f t="shared" ca="1" si="23"/>
@@ -36852,7 +39323,7 @@
       </c>
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:L72)</f>
-        <v>19.272727272727273</v>
+        <v>19.454545454545453</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -36897,7 +39368,7 @@
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B75">
         <f ca="1">DATEDIF(VLOOKUP(B74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C75">
         <f t="shared" ref="C75:L75" ca="1" si="24">DATEDIF(VLOOKUP(C74,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -36913,7 +39384,7 @@
       </c>
       <c r="F75">
         <f t="shared" ca="1" si="24"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G75">
         <f t="shared" ca="1" si="24"/>
@@ -36941,7 +39412,363 @@
       </c>
       <c r="N75" s="1">
         <f ca="1">AVERAGE(B75:L75)</f>
-        <v>19.454545454545453</v>
+        <v>19.636363636363637</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" t="s">
+        <v>213</v>
+      </c>
+      <c r="D77" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" t="s">
+        <v>100</v>
+      </c>
+      <c r="F77" t="s">
+        <v>290</v>
+      </c>
+      <c r="G77" t="s">
+        <v>72</v>
+      </c>
+      <c r="H77" t="s">
+        <v>62</v>
+      </c>
+      <c r="I77" t="s">
+        <v>295</v>
+      </c>
+      <c r="J77" t="s">
+        <v>214</v>
+      </c>
+      <c r="K77" t="s">
+        <v>273</v>
+      </c>
+      <c r="L77" t="s">
+        <v>61</v>
+      </c>
+      <c r="N77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:L78)</f>
+        <v>19.363636363636363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>231</v>
+      </c>
+      <c r="B80" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E80" t="s">
+        <v>100</v>
+      </c>
+      <c r="F80" t="s">
+        <v>290</v>
+      </c>
+      <c r="G80" t="s">
+        <v>72</v>
+      </c>
+      <c r="H80" t="s">
+        <v>274</v>
+      </c>
+      <c r="I80" t="s">
+        <v>204</v>
+      </c>
+      <c r="J80" t="s">
+        <v>216</v>
+      </c>
+      <c r="K80" t="s">
+        <v>343</v>
+      </c>
+      <c r="L80" t="s">
+        <v>61</v>
+      </c>
+      <c r="N80" s="1"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="26"/>
+        <v>18</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="26"/>
+        <v>19</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:L81)</f>
+        <v>19.181818181818183</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>153</v>
+      </c>
+      <c r="B83" t="s">
+        <v>98</v>
+      </c>
+      <c r="C83" t="s">
+        <v>213</v>
+      </c>
+      <c r="D83" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" t="s">
+        <v>100</v>
+      </c>
+      <c r="F83" t="s">
+        <v>62</v>
+      </c>
+      <c r="G83" t="s">
+        <v>295</v>
+      </c>
+      <c r="H83" t="s">
+        <v>274</v>
+      </c>
+      <c r="I83" t="s">
+        <v>204</v>
+      </c>
+      <c r="J83" t="s">
+        <v>216</v>
+      </c>
+      <c r="K83" t="s">
+        <v>343</v>
+      </c>
+      <c r="L83" t="s">
+        <v>61</v>
+      </c>
+      <c r="N83" s="1"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f ca="1">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ref="C84:L84" ca="1" si="27">DATEDIF(VLOOKUP(C83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:L84)</f>
+        <v>19.363636363636363</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>109</v>
+      </c>
+      <c r="B86" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" t="s">
+        <v>73</v>
+      </c>
+      <c r="D86" t="s">
+        <v>64</v>
+      </c>
+      <c r="E86" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" t="s">
+        <v>290</v>
+      </c>
+      <c r="G86" t="s">
+        <v>295</v>
+      </c>
+      <c r="H86" t="s">
+        <v>274</v>
+      </c>
+      <c r="I86" t="s">
+        <v>347</v>
+      </c>
+      <c r="J86" t="s">
+        <v>216</v>
+      </c>
+      <c r="K86" t="s">
+        <v>348</v>
+      </c>
+      <c r="L86" t="s">
+        <v>61</v>
+      </c>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B87">
+        <f ca="1">DATEDIF(VLOOKUP(B86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C87">
+        <f t="shared" ref="C87:L87" ca="1" si="28">DATEDIF(VLOOKUP(C86,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>18</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="E87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="F87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="G87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="H87">
+        <f t="shared" ca="1" si="28"/>
+        <v>19</v>
+      </c>
+      <c r="I87">
+        <f t="shared" ca="1" si="28"/>
+        <v>17</v>
+      </c>
+      <c r="J87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="K87">
+        <f t="shared" ca="1" si="28"/>
+        <v>17</v>
+      </c>
+      <c r="L87">
+        <f t="shared" ca="1" si="28"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="1">
+        <f ca="1">AVERAGE(B87:L87)</f>
+        <v>18.818181818181817</v>
       </c>
     </row>
   </sheetData>

--- a/Statistik Altersdurchschnitt.xlsx
+++ b/Statistik Altersdurchschnitt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coc-my.sharepoint.com/personal/mario_demmelbauer_coc-ag_de/Documents/JWR/Analysen/2526/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6952" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8A3306-9951-43F9-8623-F88F47F5CE86}"/>
+  <xr:revisionPtr revIDLastSave="6981" documentId="8_{B13851A0-BF92-44E0-9E4C-BF4EA78055B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CABC28E-DA32-4349-8232-0185F47D249C}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="747" xr2:uid="{71B9BB1E-DBD4-4A3F-B11E-2D74833D57ED}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Gesamtübersicht!$A$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="350">
   <si>
     <t>Scholl</t>
   </si>
@@ -1118,6 +1118,9 @@
   <si>
     <t>Masching</t>
   </si>
+  <si>
+    <t>Presson</t>
+  </si>
 </sst>
 </file>
 
@@ -1711,7 +1714,7 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>20.363636363636363</c:v>
@@ -1723,28 +1726,28 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2640,7 +2643,7 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.727272727272727</c:v>
@@ -5011,7 +5014,7 @@
                   <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>20.363636363636363</c:v>
@@ -5023,28 +5026,28 @@
                   <c:v>20.181818181818183</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.636363636363637</c:v>
+                  <c:v>19.727272727272727</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19.181818181818183</c:v>
+                  <c:v>19.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>20.272727272727273</c:v>
+                  <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19.727272727272727</c:v>
+                  <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>19.818181818181817</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>19.272727272727273</c:v>
+                  <c:v>19.363636363636363</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5694,7 +5697,7 @@
                   <c:v>20.363636363636363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.454545454545453</c:v>
+                  <c:v>20.545454545454547</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>20.727272727272727</c:v>
@@ -16313,7 +16316,7 @@
       </c>
       <c r="B3" s="5">
         <f ca="1">'Altach Juniors'!N1</f>
-        <v>19.690909090909095</v>
+        <v>19.660839160839167</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -16331,7 +16334,7 @@
       </c>
       <c r="B5" s="3">
         <f ca="1">JWR!N1</f>
-        <v>19.83164983164983</v>
+        <v>19.798701298701296</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -16340,7 +16343,7 @@
       </c>
       <c r="B6" s="5">
         <f ca="1">LASK!N1</f>
-        <v>20.144781144781145</v>
+        <v>20.155844155844161</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -16358,7 +16361,7 @@
       </c>
       <c r="B8" s="5">
         <f ca="1">WAC!N1</f>
-        <v>20.98951048951049</v>
+        <v>20.98989898989899</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -19529,7 +19532,7 @@
       </c>
       <c r="AC2" s="8" cm="1">
         <f t="array" aca="1" ref="AC2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="AD2" s="8" cm="1">
         <f t="array" aca="1" ref="AD2" ca="1">INDIRECT("JWR!N" &amp; (COLUMN()-1)*3)</f>
@@ -19594,7 +19597,7 @@
       </c>
       <c r="N3" s="8" cm="1">
         <f t="array" aca="1" ref="N3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="O3" s="8" cm="1">
         <f t="array" aca="1" ref="O3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19610,19 +19613,19 @@
       </c>
       <c r="R3" s="8" cm="1">
         <f t="array" aca="1" ref="R3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="S3" s="8" cm="1">
         <f t="array" aca="1" ref="S3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="T3" s="8" cm="1">
         <f t="array" aca="1" ref="T3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="U3" s="8" cm="1">
         <f t="array" aca="1" ref="U3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="V3" s="8" cm="1">
         <f t="array" aca="1" ref="V3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19630,7 +19633,7 @@
       </c>
       <c r="W3" s="8" cm="1">
         <f t="array" aca="1" ref="W3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
       <c r="X3" s="8" cm="1">
         <f t="array" aca="1" ref="X3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19638,7 +19641,7 @@
       </c>
       <c r="Y3" s="8" cm="1">
         <f t="array" aca="1" ref="Y3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
       <c r="Z3" s="8" cm="1">
         <f t="array" aca="1" ref="Z3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19646,15 +19649,15 @@
       </c>
       <c r="AA3" s="8" cm="1">
         <f t="array" aca="1" ref="AA3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="AB3" s="8" cm="1">
         <f t="array" aca="1" ref="AB3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="AC3" s="8" cm="1">
         <f t="array" aca="1" ref="AC3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>19.636363636363637</v>
       </c>
       <c r="AD3" s="8" cm="1">
         <f t="array" aca="1" ref="AD3" ca="1">INDIRECT("LASK!N" &amp; (COLUMN()-1)*3)</f>
@@ -19771,7 +19774,7 @@
       </c>
       <c r="AA4" s="5" cm="1">
         <f t="array" aca="1" ref="AA4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="AB4" s="5" cm="1">
         <f t="array" aca="1" ref="AB4" ca="1">INDIRECT("'Altach Juniors'!N" &amp; (COLUMN()-1)*3)</f>
@@ -19945,7 +19948,7 @@
       </c>
       <c r="H6" s="5" cm="1">
         <f t="array" aca="1" ref="H6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="I6" s="5" cm="1">
         <f t="array" aca="1" ref="I6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -20025,7 +20028,7 @@
       </c>
       <c r="AB6" s="5" cm="1">
         <f t="array" aca="1" ref="AB6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
-        <v>0</v>
+        <v>20.90909090909091</v>
       </c>
       <c r="AC6" s="5" cm="1">
         <f t="array" aca="1" ref="AC6" ca="1">INDIRECT("WAC!N" &amp; (COLUMN()-1)*3)</f>
@@ -21030,7 +21033,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECAD747-1599-4E91-8390-8EFBB40A7E91}">
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -21043,7 +21046,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>19.83164983164983</v>
+        <v>19.798701298701296</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -23647,7 +23650,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B81">
         <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
         <v>19</v>
@@ -23695,6 +23698,94 @@
       <c r="N81" s="1">
         <f ca="1">AVERAGE(B81:M81)</f>
         <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>198</v>
+      </c>
+      <c r="B83" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" t="s">
+        <v>81</v>
+      </c>
+      <c r="D83" t="s">
+        <v>336</v>
+      </c>
+      <c r="E83" t="s">
+        <v>106</v>
+      </c>
+      <c r="F83" t="s">
+        <v>330</v>
+      </c>
+      <c r="G83" t="s">
+        <v>2</v>
+      </c>
+      <c r="H83" t="s">
+        <v>190</v>
+      </c>
+      <c r="I83" t="s">
+        <v>280</v>
+      </c>
+      <c r="J83" t="s">
+        <v>82</v>
+      </c>
+      <c r="K83" t="s">
+        <v>107</v>
+      </c>
+      <c r="L83" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f ca="1">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ref="C84:L84" ca="1" si="27">DATEDIF(VLOOKUP(C83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>19</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>24</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:M84)</f>
+        <v>18.90909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -23709,7 +23800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE832A2-00C7-4FEB-881B-6BCBCF658A7A}">
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -23722,7 +23813,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.144781144781145</v>
+        <v>20.155844155844161</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -24261,7 +24352,7 @@
         <v>38475</v>
       </c>
       <c r="T19">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -24959,7 +25050,7 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39">
         <f ca="1">DATEDIF(VLOOKUP(B38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39">
         <f t="shared" ref="C39:L39" ca="1" si="12">DATEDIF(VLOOKUP(C38,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25003,7 +25094,7 @@
       </c>
       <c r="N39" s="1">
         <f ca="1">AVERAGE(B39:M39)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
       <c r="P39" t="s">
         <v>251</v>
@@ -25391,7 +25482,7 @@
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B51">
         <f ca="1">DATEDIF(VLOOKUP(B50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51">
         <f t="shared" ref="C51:L51" ca="1" si="16">DATEDIF(VLOOKUP(C50,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25435,7 +25526,7 @@
       </c>
       <c r="N51" s="1">
         <f ca="1">AVERAGE(B51:M51)</f>
-        <v>19.636363636363637</v>
+        <v>19.727272727272727</v>
       </c>
       <c r="P51" t="s">
         <v>331</v>
@@ -25499,7 +25590,7 @@
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B54">
         <f ca="1">DATEDIF(VLOOKUP(B53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54">
         <f t="shared" ref="C54:L54" ca="1" si="17">DATEDIF(VLOOKUP(C53,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25543,13 +25634,21 @@
       </c>
       <c r="N54" s="1">
         <f ca="1">AVERAGE(B54:M54)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
       <c r="P54" t="s">
         <v>338</v>
       </c>
       <c r="Q54" s="6">
         <v>39333</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P55" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>39460</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -25593,7 +25692,7 @@
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B57">
         <f ca="1">DATEDIF(VLOOKUP(B56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57">
         <f t="shared" ref="C57:L57" ca="1" si="18">DATEDIF(VLOOKUP(C56,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25637,7 +25736,7 @@
       </c>
       <c r="N57" s="1">
         <f ca="1">AVERAGE(B57:M57)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -25681,7 +25780,7 @@
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B60">
         <f ca="1">DATEDIF(VLOOKUP(B59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60">
         <f t="shared" ref="C60:L60" ca="1" si="19">DATEDIF(VLOOKUP(C59,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25725,7 +25824,7 @@
       </c>
       <c r="N60" s="1">
         <f ca="1">AVERAGE(B60:M60)</f>
-        <v>20.272727272727273</v>
+        <v>20.363636363636363</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -25857,7 +25956,7 @@
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B66">
         <f ca="1">DATEDIF(VLOOKUP(B65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C66">
         <f t="shared" ref="C66:L66" ca="1" si="21">DATEDIF(VLOOKUP(C65,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -25901,7 +26000,7 @@
       </c>
       <c r="N66" s="1">
         <f ca="1">AVERAGE(B66:M66)</f>
-        <v>19.727272727272727</v>
+        <v>19.818181818181817</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -26033,7 +26132,7 @@
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B72">
         <f ca="1">DATEDIF(VLOOKUP(B71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C72">
         <f t="shared" ref="C72:L72" ca="1" si="23">DATEDIF(VLOOKUP(C71,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -26077,7 +26176,7 @@
       </c>
       <c r="N72" s="1">
         <f ca="1">AVERAGE(B72:M72)</f>
-        <v>19.272727272727273</v>
+        <v>19.363636363636363</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
@@ -26209,7 +26308,7 @@
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B78">
         <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C78">
         <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -26253,7 +26352,7 @@
       </c>
       <c r="N78" s="1">
         <f ca="1">AVERAGE(B78:M78)</f>
-        <v>19.181818181818183</v>
+        <v>19.272727272727273</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
@@ -26294,10 +26393,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B81">
         <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81">
         <f t="shared" ref="C81:L81" ca="1" si="26">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -26341,6 +26440,94 @@
       </c>
       <c r="N81" s="1">
         <f ca="1">AVERAGE(B81:M81)</f>
+        <v>19.727272727272727</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>85</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s">
+        <v>284</v>
+      </c>
+      <c r="E83" t="s">
+        <v>337</v>
+      </c>
+      <c r="F83" t="s">
+        <v>86</v>
+      </c>
+      <c r="G83" t="s">
+        <v>199</v>
+      </c>
+      <c r="H83" t="s">
+        <v>300</v>
+      </c>
+      <c r="I83" t="s">
+        <v>333</v>
+      </c>
+      <c r="J83" t="s">
+        <v>349</v>
+      </c>
+      <c r="K83" t="s">
+        <v>37</v>
+      </c>
+      <c r="L83" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B84">
+        <f ca="1">DATEDIF(VLOOKUP(B83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <f t="shared" ref="C84:L84" ca="1" si="27">DATEDIF(VLOOKUP(C83,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>21</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="F84">
+        <f t="shared" ca="1" si="27"/>
+        <v>24</v>
+      </c>
+      <c r="G84">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="H84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="I84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="J84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="K84">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="L84">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="N84" s="1">
+        <f ca="1">AVERAGE(B84:M84)</f>
         <v>19.636363636363637</v>
       </c>
     </row>
@@ -26355,7 +26542,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AE484A-7472-48CF-8DEF-9C09E1FFDA18}">
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
@@ -26366,7 +26553,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N2:N99)</f>
-        <v>19.690909090909095</v>
+        <v>19.660839160839167</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -28790,6 +28977,94 @@
       <c r="N75" s="1">
         <f ca="1">AVERAGE(B75:M75)</f>
         <v>19.363636363636363</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>242</v>
+      </c>
+      <c r="B77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" t="s">
+        <v>235</v>
+      </c>
+      <c r="D77" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s">
+        <v>304</v>
+      </c>
+      <c r="I77" t="s">
+        <v>188</v>
+      </c>
+      <c r="J77" t="s">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s">
+        <v>324</v>
+      </c>
+      <c r="L77" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <f ca="1">DATEDIF(VLOOKUP(B77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C78">
+        <f t="shared" ref="C78:L78" ca="1" si="25">DATEDIF(VLOOKUP(C77,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="D78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="E78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="F78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="G78">
+        <f t="shared" ca="1" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <f t="shared" ca="1" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="I78">
+        <f t="shared" ca="1" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="J78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="K78">
+        <f t="shared" ca="1" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="L78">
+        <f t="shared" ca="1" si="25"/>
+        <v>22</v>
+      </c>
+      <c r="N78" s="1">
+        <f ca="1">AVERAGE(B78:M78)</f>
+        <v>18.90909090909091</v>
       </c>
     </row>
   </sheetData>
@@ -31635,7 +31910,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3E1E7-4E05-419E-8824-98C6A5690768}">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -31645,7 +31920,7 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N1" s="1">
         <f ca="1">AVERAGE(N3:N99)</f>
-        <v>20.98951048951049</v>
+        <v>20.98989898989899</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -32240,7 +32515,7 @@
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B21">
         <f ca="1">DATEDIF(VLOOKUP(B20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:L21" ca="1" si="7">DATEDIF(VLOOKUP(C20,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
@@ -32284,7 +32559,7 @@
       </c>
       <c r="N21" s="1">
         <f ca="1">AVERAGE(B21:L21)</f>
-        <v>20.454545454545453</v>
+        <v>20.545454545454547</v>
       </c>
       <c r="P21" t="s">
         <v>11</v>
@@ -34157,6 +34432,94 @@
       <c r="N78" s="1">
         <f ca="1">AVERAGE(B78:L78)</f>
         <v>20.818181818181817</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" t="s">
+        <v>95</v>
+      </c>
+      <c r="G80" t="s">
+        <v>29</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" t="s">
+        <v>11</v>
+      </c>
+      <c r="J80" t="s">
+        <v>313</v>
+      </c>
+      <c r="K80" t="s">
+        <v>170</v>
+      </c>
+      <c r="L80" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <f ca="1">DATEDIF(VLOOKUP(B80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <f t="shared" ref="C81:L81" ca="1" si="27">DATEDIF(VLOOKUP(C80,$P$18:$Q$100,2,FALSE),TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D81">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="E81">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="F81">
+        <f t="shared" ca="1" si="27"/>
+        <v>21</v>
+      </c>
+      <c r="G81">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <f t="shared" ca="1" si="27"/>
+        <v>25</v>
+      </c>
+      <c r="I81">
+        <f t="shared" ca="1" si="27"/>
+        <v>25</v>
+      </c>
+      <c r="J81">
+        <f t="shared" ca="1" si="27"/>
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <f t="shared" ca="1" si="27"/>
+        <v>18</v>
+      </c>
+      <c r="L81">
+        <f t="shared" ca="1" si="27"/>
+        <v>19</v>
+      </c>
+      <c r="N81" s="1">
+        <f ca="1">AVERAGE(B81:L81)</f>
+        <v>20.90909090909091</v>
       </c>
     </row>
   </sheetData>
